--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thailand details 100bn-baht drug research goal and local production talks with global drugmakers on Sept 12</t>
+          <t>Sandoz bets big on biosimilars and targets $22 billion+ in sales by 2035</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nation Thailand</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.nationthailand.com/news/policy/40070956</t>
+          <t>https://www.indianpharmapost.com/news/sandoz-bets-big-on-biosimilars-and-targets-22-billion-in-sales-by-2035-21812</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12-09-2026 09:21 UTC</t>
+          <t>12-09-2026 16:39 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company (Sandoz) and potential biologic manufacturing/supply chain news (Category 5, 8)</t>
+          <t>Monitored company Sandoz biosimilars strategy</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Endometriosis Market Analysis 2036: Industry Trends, Market Size, and Emerging Therapeutic Developments – DelveInsight | AbbVie, Kissei Pharma, Theramex, Hope Medicine, TiumBio, Viramal, Organon</t>
+          <t>Biogen Sees Pivotal Pipeline Moment as It Expands Beyond Neurology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4567845/endometriosis-market-analysis-2036-industry-trends-market-size-and-emerging-therapeutic-developments-delveinsight-abbvie-kissei-pharma-theramex-hope-medicine-tiumbio-viramal-organon</t>
+          <t>https://finance.yahoo.com/healthcare/articles/biogen-sees-pivotal-pipeline-moment-210158269.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-09-2026 03:30 UTC</t>
+          <t>12-09-2026 21:01 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company (Organon) in market analysis for autoimmune/inflammatory condition with therapeutic developments (Category 7, 8)</t>
+          <t>Monitored company Biogen pipeline strategy</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bionovis</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Biocon secures 10-Year supply contract for Pertuzumab in Brazil</t>
+          <t>Lupin eyes $500 mn biosimilars revenue in medium term, to ramp capacity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/25/28365/biocon-secures-10-year-supply-contract-for-pertuzumab-in-brazil.html</t>
+          <t>https://www.business-standard.com/industry/news/companies-news-lupin-eyes-500-mn-biosimilars-revenue-in-medium-term-126091300205_1.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11-09-2026 17:07 UTC</t>
+          <t>13-09-2026 06:57 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company (Biocon) secures supply contract for a biologic (Pertuzumab) (Category 5, 6, 8)</t>
+          <t>Biosimilars &amp; Biologics market strategy and manufacturing capacity ramp by biosimilar competitor</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Mexico API facility gets two observations from USFDA</t>
+          <t>Aurobindo Pharma Injects $1 Million into New U.S. R&amp;D Arm After A1 Biochem Deal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/dr-reddys-mexico-api-facility-gets-two-observations-from-usfda/article71458976.ece</t>
+          <t>https://www.tipranks.com/news/company-announcements/aurobindo-pharma-injects-1-million-into-new-u-s-rd-arm-after-a1-biochem-deal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-09-2026 00:16 UTC</t>
+          <t>12-09-2026 09:03 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company (Dr. Reddy's) FDA manufacturing inspection with observations (Category 3, 5, 8)</t>
+          <t>Monitored company Aurobindo Pharma R&amp;D investment and deal</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Polpharma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma acquires 100% stake in A1 Biochem USA for $1 million</t>
+          <t>Biosimilar race: Sandoz expands pipeline with Henlius, Teva secures ocrelizumab candidate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Generics and Biosimilars Initiative</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-acquires-100-stake-a1-biochem-usa-1-million/50744648</t>
+          <t>https://gabionline.net/es/noticias-farmaceuticas/biosimilar-race-sandoz-expands-pipeline-with-henlius-teva-secures-ocrelizumab-candidate</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12-09-2026 07:47 UTC</t>
+          <t>12-09-2026 13:19 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company (Aurobindo Pharma) acquisition of a biotech subsidiary (Category 6, 8)</t>
+          <t>Biosimilars &amp; Biologics pipeline development involving monitored companies Sandoz and Teva</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -668,246 +668,6 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Stocktwits</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>12-09-2026 08:12 UTC</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Monitored company (Kyowa Kirin) and policy/market news affecting drug pricing and manufacturing investment for US plants (Category 5, 8)</t>
-        </is>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>JCR Pharma</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MEDIPAL HOLDINGS CORPORATION and JCR Pharmaceuticals Dose First Patient in Global Phase I/II Trial of JR-446 for Mucopolysaccharidosis Type IIIB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/healthcare/articles/medipal-holdings-corporation-jcr-pharmaceuticals-161100817.html</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>11-09-2026 16:11 UTC</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Monitored company (JCR Pharma) clinical trial for a biologic (JR-446) in a rare disease (Category 7, 8)</t>
-        </is>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Migraine Market: Pharma Pipeline Fuels Rapid Expansion by 2036 – DelveInsight | Eli Lilly, Teva Pharma, Axsome Therapeutics, AEON Biopharma, Charleston Lab, Amgen, Teva Pharma, Anne Lindblad</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>barchart.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.barchart.com/press-releases/4567842/migraine-market-pharma-pipeline-fuels-rapid-expansion-by-2036-delveinsight-eli-lilly-teva-pharma-axsome-therapeutics-aeon-biopharma-charleston-lab-amgen-teva-pharma-anne-lindblad</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>12-09-2026 03:30 UTC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Monitored companies (Teva, Amgen) and pharma pipeline news for migraine, a therapy area that includes biologics (Category 7, 8)</t>
-        </is>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Lack of biosimilar development could cost billions in lost savings, report warns</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Endpoints News</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://endpoints.news/new-report-may-spell-trouble-for-future-cheaper-biologics/</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>11-09-2026 15:22 UTC</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Monitored company (Samsung Bioepis) and report on biosimilar development and market savings (Category 2, 8)</t>
-        </is>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Samsung Biologics Signs $262 Million Manufacturing Agreement with European Pharma Firm</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>genengnews.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://www.genengnews.com/topics/bioprocessing/samsung-biologics-signs-262-million-manufacturing-agreement-with-european-pharma-firm/</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>11-09-2026 14:59 UTC</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Monitored company (Samsung Biologics) signs biologics manufacturing deal (Category 5, 6, 8)</t>
-        </is>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Transcenta Therapeutics and WuXi Biologics Team Up to Accelerate Commercialization of HiCB Technology</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>genengnews.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://www.genengnews.com/topics/bioprocessing/transcenta-therapeutics-and-wuxi-biologics-team-up-to-accelerate-commercialization-of-hicb-technology/</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>11-09-2026 15:10 UTC</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Partnership for biologics technology (CDMO) (Category 6)</t>
-        </is>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
@@ -935,7 +695,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12-09-2026 19:56:01</t>
+          <t>13-09-2026 13:27:14</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company Sandoz biosimilars strategy</t>
+          <t>Monitored company, business-relevant biosimilar strategy</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biogen Sees Pivotal Pipeline Moment as It Expands Beyond Neurology</t>
+          <t>Pfizer Makes an Unusual Enemy in $2 Billion Fight Over Unwanted Covid-19 Vaccines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/biogen-sees-pivotal-pipeline-moment-210158269.html</t>
+          <t>https://www.wsj.com/business/pfizer-makes-an-unusual-enemy-in-2-billion-fight-over-unwanted-covid-19-vaccines-a5ad7c8d</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-09-2026 21:01 UTC</t>
+          <t>13-09-2026 14:39 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company Biogen pipeline strategy</t>
+          <t>Monitored company, commercial event for a biologic (vaccine)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lupin eyes $500 mn biosimilars revenue in medium term, to ramp capacity</t>
+          <t>Medicus Pharma advances SkinJect and Pfizer par...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/companies-news-lupin-eyes-500-mn-biosimilars-revenue-in-medium-term-126091300205_1.html</t>
+          <t>https://pluang.com/en/news-feed/ceo-medicus-pharma-bahas-kemajuan-skinject-dan-kerjasama-pfizer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13-09-2026 06:57 UTC</t>
+          <t>12-09-2026 15:09 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics market strategy and manufacturing capacity ramp by biosimilar competitor</t>
+          <t>Monitored company, potential partnership/pipeline news</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Injects $1 Million into New U.S. R&amp;D Arm After A1 Biochem Deal</t>
+          <t>Biogen Sees Pivotal Pipeline Moment as It Expands Beyond Neurology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/aurobindo-pharma-injects-1-million-into-new-u-s-rd-arm-after-a1-biochem-deal</t>
+          <t>https://finance.yahoo.com/healthcare/articles/biogen-sees-pivotal-pipeline-moment-210158269.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-09-2026 09:03 UTC</t>
+          <t>12-09-2026 21:01 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company Aurobindo Pharma R&amp;D investment and deal</t>
+          <t>Monitored company, business-relevant pipeline strategy</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Biosimilar race: Sandoz expands pipeline with Henlius, Teva secures ocrelizumab candidate</t>
+          <t>Dr Reddy’s Mexico API Facility Gets Two Observations From USFDA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Generics and Biosimilars Initiative</t>
+          <t>Daily Pioneer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://gabionline.net/es/noticias-farmaceuticas/biosimilar-race-sandoz-expands-pipeline-with-henlius-teva-secures-ocrelizumab-candidate</t>
+          <t>https://dailypioneer.com/news/slug-lite/usfda-conducts-assessment-of-dr-reddys-mexico-facility?year=2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12-09-2026 13:19 UTC</t>
+          <t>13-09-2026 08:55 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics pipeline development involving monitored companies Sandoz and Teva</t>
+          <t>Monitored company, FDA inspection/Form 483 observations</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,7 +667,127 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lupin eyes $500 mn biosimilars revenue in medium term, to ramp capacity</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/industry/news/companies-news-lupin-eyes-500-mn-biosimilars-revenue-in-medium-term-126091300205_1.html</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>13-09-2026 06:57 UTC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Biosimilar market event, includes manufacturing capacity, company active in biosimilars</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12-09-2026 17:29 UTC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Healthcare policy affecting drug prices and manufacturing</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Samsung Biologics (KRX: 207940) Secures $262M Manufacturing Deal With European Pharma As Peptide Push Advances</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>londoninsider.co.uk</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://londoninsider.co.uk/samsung-biologics-krx-207940-secures-262m-manufacturing-deal-with-european-pharma-as-peptide-push-advances/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13-09-2026 10:49 UTC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Monitored company (Samsung Biologics), biologic manufacturing deal (CDMO)</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -695,7 +815,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13-09-2026 13:27:14</t>
+          <t>13-09-2026 20:35:00</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz bets big on biosimilars and targets $22 billion+ in sales by 2035</t>
+          <t>Thailand moves from buying medicines to building them</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Pattaya Mail</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/sandoz-bets-big-on-biosimilars-and-targets-22-billion-in-sales-by-2035-21812</t>
+          <t>https://www.pattayamail.com/latestnews/news/thailand-moves-from-buying-medicines-to-building-them-564872</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12-09-2026 16:39 UTC</t>
+          <t>13-09-2026 19:19 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company, business-relevant biosimilar strategy</t>
+          <t>Monitored Company (Sandoz) - Manufacturing, Supply Chain &amp; Capacity (pharmaceutical capacity building)</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pfizer Makes an Unusual Enemy in $2 Billion Fight Over Unwanted Covid-19 Vaccines</t>
+          <t>Advancing Innovation in Small Cell Lung Cancer at WCLC 2026 – Amgen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/business/pfizer-makes-an-unusual-enemy-in-2-billion-fight-over-unwanted-covid-19-vaccines-a5ad7c8d</t>
+          <t>https://oncodaily.com/industry/amgen-585539</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13-09-2026 14:39 UTC</t>
+          <t>13-09-2026 19:00 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company, commercial event for a biologic (vaccine)</t>
+          <t>Monitored Company (Amgen) - Clinical Trials &amp; Pipeline News (biologics in oncology)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Medicus Pharma advances SkinJect and Pfizer par...</t>
+          <t>Pfizer Makes an Unusual Enemy in $2 Billion Fight Over Unwanted Covid-19 Vaccines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/ceo-medicus-pharma-bahas-kemajuan-skinject-dan-kerjasama-pfizer</t>
+          <t>https://www.wsj.com/business/pfizer-makes-an-unusual-enemy-in-2-billion-fight-over-unwanted-covid-19-vaccines-a5ad7c8d</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12-09-2026 15:09 UTC</t>
+          <t>13-09-2026 14:39 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company, potential partnership/pipeline news</t>
+          <t>Monitored Company (Pfizer) - Biologics market event (vaccine dispute)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Biogen Sees Pivotal Pipeline Moment as It Expands Beyond Neurology</t>
+          <t>Viatris names Kim Sun-A head of Japan-Korea cluster</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/biogen-sees-pivotal-pipeline-moment-210158269.html</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33156</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-09-2026 21:01 UTC</t>
+          <t>14-09-2026 04:17 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company, business-relevant pipeline strategy</t>
+          <t>Monitored Company (Viatris) - Commercial event (leadership appointment impacting regional commercial strategy for biosimilars)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Mexico API Facility Gets Two Observations From USFDA</t>
+          <t>After a brief storm of political headwinds, mRNA is back with strong momentum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Daily Pioneer</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://dailypioneer.com/news/slug-lite/usfda-conducts-assessment-of-dr-reddys-mexico-facility?year=2026</t>
+          <t>https://www.biospace.com/drug-development/after-a-brief-storm-of-political-headwinds-mrna-is-back-with-strong-momentum</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13-09-2026 08:55 UTC</t>
+          <t>14-09-2026 04:10 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company, FDA inspection/Form 483 observations</t>
+          <t>Biologics &amp; Biosimilars - general mRNA technology trend relevant to biologic drug development</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lupin eyes $500 mn biosimilars revenue in medium term, to ramp capacity</t>
+          <t>USFDA Issues Two Observations After Records Assessment of Dr. Reddy's Mexico API Facility</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/companies-news-lupin-eyes-500-mn-biosimilars-revenue-in-medium-term-126091300205_1.html</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/usfda-issues-two-observations-after-records-assessment-of-dr-reddys-mexico-api-facility-179163</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13-09-2026 06:57 UTC</t>
+          <t>13-09-2026 12:30 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biosimilar market event, includes manufacturing capacity, company active in biosimilars</t>
+          <t>Monitored Company (Dr. Reddy's) - Manufacturing, Supply Chain &amp; Capacity (FDA observations)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>C-CAMP National Bio Entrepreneurship competition 2026 recognises 15 startups and four student teams</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>indianpharmapost.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://www.indianpharmapost.com/startup/c-camp-national-bio-entrepreneurship-competition-2026-recognises-15-startups-and-four-student-teams-21825</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12-09-2026 17:29 UTC</t>
+          <t>14-09-2026 02:44 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Healthcare policy affecting drug prices and manufacturing</t>
+          <t>Monitored Company (Biocon) - Biologics &amp; Biosimilars (industry ecosystem news)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,47 +747,287 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma's Apitoria clears US FDA inspection with zero observations</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>indianpharmapost.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.indianpharmapost.com/news/aurobindo-pharmas-apitoria-clears-us-fda-inspection-with-zero-observations-21829</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>14-09-2026 04:19 UTC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Monitored Company (Aurobindo Pharma) - Manufacturing, Supply Chain &amp; Capacity (FDA inspection with zero observations)</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ENHERTU® (fam-trastuzumab deruxtecan-nxki) demonstrated a median progression-free survival of 14.3 months as 1st-line therapy in patients with HER2-mutant advanced non-small cell lung cancer in DESTINY-Lung04 Phase III trial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FinancialContent</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.financialcontent.com/article/bizwire-2026-9-14-enhertu-fam-trastuzumab-deruxtecan-nxki-demonstrated-a-median-progression-free-survival-of-143-months-as-1st-line-therapy-in-patients-with-her2-mutant-advanced-non-small-cell-lung-cancer-in-destiny-lung04-phase-iii-trial</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>14-09-2026 01:55 UTC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Monitored Company (Daiichi Sankyo) - Clinical Trials &amp; Pipeline News (biologic in oncology)</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>13-09-2026 21:54 UTC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FDA / Regulatory Actions (drug pricing policy) and Manufacturing, Supply Chain &amp; Capacity</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JCR Pharma</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MEDIPAL HOLDINGS CORPORATION and JCR Pharmaceuticals Dose First Patient in Global Phase I/II Trial of JR-446 for Mucopolysaccharidosis Type IIIB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BioSpace</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/medipal-holdings-corporation-and-jcr-pharmaceuticals-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-mucopolysaccharidosis-type-iiib</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>14-09-2026 02:46 UTC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Monitored Company (JCR Pharma) - Clinical Trials &amp; Pipeline News (biologic for rare disease)</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Samsung Biologics (KRX: 207940) Secures $262M Manufacturing Deal With European Pharma As Peptide Push Advances</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>londoninsider.co.uk</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://londoninsider.co.uk/samsung-biologics-krx-207940-secures-262m-manufacturing-deal-with-european-pharma-as-peptide-push-advances/</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>13-09-2026 10:49 UTC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Monitored company (Samsung Biologics), biologic manufacturing deal (CDMO)</t>
-        </is>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Samsung Biologics signs $262M manufacturing deal through 2033, pushing longer CDMO bookings</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MarketScale</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.marketscale.com/industries/sciences/samsung-biologics-signs-262m-manufacturing-deal-through-2033-pushing-longer-cdmo-bookings</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>13-09-2026 11:54 UTC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Monitored Company (Samsung Biologics) - Manufacturing, Supply Chain &amp; Capacity (CDMO deal)</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Songdo Opens Bio Training Center to Ease Talent Shortage</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/society/2026/09/14/songdo-opens-bio-training-center-to-ease-talent-shortage</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>14-09-2026 00:29 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (biotech talent development in key region)</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sphericalinsights.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>13-09-2026 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Biologics &amp; Biosimilars - general industry trend (CDMO)</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -815,7 +1055,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13-09-2026 20:35:00</t>
+          <t>14-09-2026 14:00:20</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thailand moves from buying medicines to building them</t>
+          <t>Lupin targets $500 million biosimilar revenue in five years</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pattaya Mail</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pattayamail.com/latestnews/news/thailand-moves-from-buying-medicines-to-building-them-564872</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13-09-2026 19:19 UTC</t>
+          <t>14-09-2026 15:22 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored Company (Sandoz) - Manufacturing, Supply Chain &amp; Capacity (pharmaceutical capacity building)</t>
+          <t>Biosimilars &amp; Biologics - biosimilar revenue target</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Advancing Innovation in Small Cell Lung Cancer at WCLC 2026 – Amgen</t>
+          <t>Takeda R&amp;D President Andy Plump to Retire in 2027</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/industry/amgen-585539</t>
+          <t>https://www.contractpharma.com/breaking-news/takeda-rd-president-andy-plump-to-retire-in-2027/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13-09-2026 19:00 UTC</t>
+          <t>14-09-2026 14:45 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored Company (Amgen) - Clinical Trials &amp; Pipeline News (biologics in oncology)</t>
+          <t>Monitored Companies - high-level R&amp;D leadership change at Takeda (Entyvio originator)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pfizer Makes an Unusual Enemy in $2 Billion Fight Over Unwanted Covid-19 Vaccines</t>
+          <t>CAR-T therapies, bispecific antibodies, and antifibrotics in development open a new avenue against scleroderma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Demócrata</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/business/pfizer-makes-an-unusual-enemy-in-2-billion-fight-over-unwanted-covid-19-vaccines-a5ad7c8d</t>
+          <t>https://www.democrata.es/en/health/car-t-therapies-bispecific-antibodies-and-antifibrotics-in-development-open-a-new-avenue-against-scleroderma/amp/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13-09-2026 14:39 UTC</t>
+          <t>14-09-2026 14:44 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored Company (Pfizer) - Biologics market event (vaccine dispute)</t>
+          <t>Clinical Trials &amp; Pipeline News - biologics development for autoimmune disease</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viatris names Kim Sun-A head of Japan-Korea cluster</t>
+          <t>Amgen Leads The Pack With First Filing For US Opdivo Biosimilar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33156</t>
+          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/amgen-leads-the-pack-with-first-filing-for-us-opdivo-biosimilar-PD6ZNDEA2VA4XKUQ44XCXQCZHI/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14-09-2026 04:17 UTC</t>
+          <t>14-09-2026 10:30 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored Company (Viatris) - Commercial event (leadership appointment impacting regional commercial strategy for biosimilars)</t>
+          <t>Biosimilars &amp; Biologics - biosimilar FDA filing</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>After a brief storm of political headwinds, mRNA is back with strong momentum</t>
+          <t>Amgen Gets FDA Approval to Reduce Monitoring Time for First Two Imdelltra Doses</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/drug-development/after-a-brief-storm-of-political-headwinds-mrna-is-back-with-strong-momentum</t>
+          <t>https://www.marketscreener.com/news/amgen-gets-fda-approval-to-reduce-monitoring-time-for-first-two-imdelltra-doses-ce785bdcdc81f62d</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14-09-2026 04:10 UTC</t>
+          <t>14-09-2026 14:00 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biologics &amp; Biosimilars - general mRNA technology trend relevant to biologic drug development</t>
+          <t>FDA / Regulatory Actions - FDA approval for a biologic</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USFDA Issues Two Observations After Records Assessment of Dr. Reddy's Mexico API Facility</t>
+          <t>Lonza deepens US bet with commercial plant in Oregon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/usfda-issues-two-observations-after-records-assessment-of-dr-reddys-mexico-api-facility-179163</t>
+          <t>https://www.thepharmaletter.com/pharma-news/lonza-deepens-us-bet-with-commercial-spray-drying-plant-in-oregon</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13-09-2026 12:30 UTC</t>
+          <t>14-09-2026 10:48 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored Company (Dr. Reddy's) - Manufacturing, Supply Chain &amp; Capacity (FDA observations)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity - commercial plant for biologics CDMO</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C-CAMP National Bio Entrepreneurship competition 2026 recognises 15 startups and four student teams</t>
+          <t>Can Pfizer Overcome Its COVID and Patent Cliff Headwinds?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>indianpharmapost.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/startup/c-camp-national-bio-entrepreneurship-competition-2026-recognises-15-startups-and-four-student-teams-21825</t>
+          <t>https://finance.yahoo.com/healthcare/articles/pfizer-overcome-covid-patent-cliff-133700992.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14-09-2026 02:44 UTC</t>
+          <t>14-09-2026 13:37 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored Company (Biocon) - Biologics &amp; Biosimilars (industry ecosystem news)</t>
+          <t>Earnings &amp; Financial Reports - strategic discussion mentioning patent cliff and growth</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma's Apitoria clears US FDA inspection with zero observations</t>
+          <t>Transcript : Pfizer Inc. Presents at Morgan Stanley 24th Annual Global Healthcare Conference, Sep-14-2026 10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>indianpharmapost.com</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/aurobindo-pharmas-apitoria-clears-us-fda-inspection-with-zero-observations-21829</t>
+          <t>https://www.marketscreener.com/news/transcript-pfizer-inc-presents-at-morgan-stanley-24th-annual-global-healthcare-conference-sep-14-ce785bdcdf81f720</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-09-2026 04:19 UTC</t>
+          <t>14-09-2026 15:50 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored Company (Aurobindo Pharma) - Manufacturing, Supply Chain &amp; Capacity (FDA inspection with zero observations)</t>
+          <t>Industry Meetings &amp; Conferences - investor presentation by monitored company, potential for biosimilar/biologic strategy discussion</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENHERTU® (fam-trastuzumab deruxtecan-nxki) demonstrated a median progression-free survival of 14.3 months as 1st-line therapy in patients with HER2-mutant advanced non-small cell lung cancer in DESTINY-Lung04 Phase III trial</t>
+          <t>Pfizer Says Major Headwinds Are Easing as Pipeline, Obesity Plans Take Center Stage</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FinancialContent</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.financialcontent.com/article/bizwire-2026-9-14-enhertu-fam-trastuzumab-deruxtecan-nxki-demonstrated-a-median-progression-free-survival-of-143-months-as-1st-line-therapy-in-patients-with-her2-mutant-advanced-non-small-cell-lung-cancer-in-destiny-lung04-phase-iii-trial</t>
+          <t>https://finance.yahoo.com/healthcare/articles/pfizer-says-major-headwinds-easing-160235029.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14-09-2026 01:55 UTC</t>
+          <t>14-09-2026 16:02 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored Company (Daiichi Sankyo) - Clinical Trials &amp; Pipeline News (biologic in oncology)</t>
+          <t>Earnings &amp; Financial Reports - strategic discussion mentioning pipeline and obesity plans</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>Dr Reddy's halts semaglutide supplies on impurity issue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-laboratories-delays-semaglutide-supplies-due-to-api-issue/45115417</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13-09-2026 21:54 UTC</t>
+          <t>13-09-2026 19:05 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions (drug pricing policy) and Manufacturing, Supply Chain &amp; Capacity</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity - impurity issue affecting supply</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MEDIPAL HOLDINGS CORPORATION and JCR Pharmaceuticals Dose First Patient in Global Phase I/II Trial of JR-446 for Mucopolysaccharidosis Type IIIB</t>
+          <t>Dr. Reddy’s Reports FDA Records Assessment at Mexican API Plant Concluding with Two Observations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/medipal-holdings-corporation-and-jcr-pharmaceuticals-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-mucopolysaccharidosis-type-iiib</t>
+          <t>https://www.tipranks.com/news/company-announcements/dr-reddys-reports-fda-records-assessment-at-mexican-api-plant-concluding-with-two-observations</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14-09-2026 02:46 UTC</t>
+          <t>14-09-2026 11:12 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitored Company (JCR Pharma) - Clinical Trials &amp; Pipeline News (biologic for rare disease)</t>
+          <t>FDA / Regulatory Actions - FDA assessment at API plant</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsung Biologics signs $262M manufacturing deal through 2033, pushing longer CDMO bookings</t>
+          <t>C-CAMP National Bio Entrepreneurship competition 2026 recognises 15 startups and four student teams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MarketScale</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.marketscale.com/industries/sciences/samsung-biologics-signs-262m-manufacturing-deal-through-2033-pushing-longer-cdmo-bookings</t>
+          <t>https://www.indianpharmapost.com/news/c-camp-national-bio-entrepreneurship-competition-2026-recognises-15-startups-and-four-student-teams-21825</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13-09-2026 11:54 UTC</t>
+          <t>14-09-2026 03:18 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monitored Company (Samsung Biologics) - Manufacturing, Supply Chain &amp; Capacity (CDMO deal)</t>
+          <t>Industry Meetings &amp; Conferences - bio-entrepreneurship competition relevant to biotech ecosystem</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Songdo Opens Bio Training Center to Ease Talent Shortage</t>
+          <t>SKUAST-K scholar wins national bio-entrepreneurship award</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>thekashmirimages.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/society/2026/09/14/songdo-opens-bio-training-center-to-ease-talent-shortage</t>
+          <t>https://thekashmirimages.com/2026/09/14/skuast-k-scholar-wins-national-bio-entrepreneurship-award/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14-09-2026 00:29 UTC</t>
+          <t>13-09-2026 18:41 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (biotech talent development in key region)</t>
+          <t>Monitored Companies - bio-entrepreneurship award relevant to biotech ecosystem</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -994,38 +994,318 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma's Apitoria clears US FDA inspection with zero observations</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Indian Pharma Post</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.indianpharmapost.com/news/aurobindo-pharmas-apitoria-clears-us-fda-inspection-with-zero-observations-21829</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>14-09-2026 04:32 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FDA / Regulatory Actions - FDA inspection of API facility for monitored company</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Spherical Insights</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>13-09-2026 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity - CDMO industry analysis</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ENHERTU® (fam-trastuzumab deruxtecan-nxki) demonstrated a median progression-free survival of 14.3 months as 1st-line therapy in patients with HER2-mutant advanced non-small cell lung cancer in DESTINY-Lung04 Phase III trial</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BioSpace</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/enhertu-fam-trastuzumab-deruxtecan-nxki-demonstrated-a-median-progression-free-survival-of-14-3-months-as-1st-line-therapy-in-patients-with-her2-mutant-advanced-non-small-cell-lung-cancer-in-destiny-lung04-phase-iii-trial</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>14-09-2026 04:21 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Clinical Trials &amp; Pipeline News - clinical data for biologic product</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>13-09-2026 21:54 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity - policy affecting US plants and drug pricing</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JCR Pharma</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MEDIPAL, JCR Dose First Patient in Global Phase I/II Trial of JR-446 for Sanfilippo Syndrome</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BioPharma APAC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://biopharmaapac.com/news/86/8425/medipal-jcr-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-sanfilippo-syndrome.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>13-09-2026 18:36 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Clinical Trials &amp; Pipeline News - clinical trial start for monitored company</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AbelZeta Receives FDA IND Clearance for Phase 1b/2 Clinical Trial of C-CAR168 in Progressive Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/abelzeta-receives-fda-ind-clearance-for-phase-1b2-clinical-trial-of-c-car168-in-progressive-multiple-sclerosis-302877555.html</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>14-09-2026 11:30 UTC</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>FDA / Regulatory Actions - FDA IND clearance for autoimmune advanced therapy</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceuticals Sees Pivot to Growth Accelerating on Branded Drugs, Biosimilars</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/teva-pharmaceuticals-sees-pivot-growth-140227795.html</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>14-09-2026 14:02 UTC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics - company strategy mentions biosimilars</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>sphericalinsights.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Biologics &amp; Biosimilars - general industry trend (CDMO)</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Songdo Opens Bio Training Center to Ease Talent Shortage</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/society/2026/09/14/songdo-opens-bio-training-center-to-ease-talent-shortage</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>14-09-2026 00:29 UTC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity - bio training center supporting biologics industry</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1055,7 +1335,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-09-2026 14:00:20</t>
+          <t>14-09-2026 22:44:15</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,12 +494,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14-09-2026 15:22 UTC</t>
+          <t>14-09-2026 15:29 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics - biosimilar revenue target</t>
+          <t>Biosimilars &amp; Biologics: biosimilar revenue targets/strategy</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -524,7 +524,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored Companies - high-level R&amp;D leadership change at Takeda (Entyvio originator)</t>
+          <t>Vedolizumab / Entyvio primary signal: Takeda R&amp;D leadership change</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAR-T therapies, bispecific antibodies, and antifibrotics in development open a new avenue against scleroderma</t>
+          <t>Amgen Leads The Pack With First Filing For US Opdivo Biosimilar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Demócrata</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.democrata.es/en/health/car-t-therapies-bispecific-antibodies-and-antifibrotics-in-development-open-a-new-avenue-against-scleroderma/amp/</t>
+          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/amgen-leads-the-pack-with-first-filing-for-us-opdivo-biosimilar-PD6ZNDEA2VA4XKUQ44XCXQCZHI/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14-09-2026 14:44 UTC</t>
+          <t>14-09-2026 10:30 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News - biologics development for autoimmune disease</t>
+          <t>Biosimilars &amp; Biologics: biosimilar FDA filing by monitored company</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,7 +587,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -599,27 +599,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amgen Leads The Pack With First Filing For US Opdivo Biosimilar</t>
+          <t>Amgen Gets FDA Approval to Reduce Monitoring Time for First Two Imdelltra Doses</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/amgen-leads-the-pack-with-first-filing-for-us-opdivo-biosimilar-PD6ZNDEA2VA4XKUQ44XCXQCZHI/</t>
+          <t>https://www.marketscreener.com/news/amgen-gets-fda-approval-to-reduce-monitoring-time-for-first-two-imdelltra-doses-ce785bdcdc81f62d</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14-09-2026 10:30 UTC</t>
+          <t>14-09-2026 14:00 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics - biosimilar FDA filing</t>
+          <t>FDA / Regulatory Actions: FDA approval for a biologic from a monitored company</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amgen Gets FDA Approval to Reduce Monitoring Time for First Two Imdelltra Doses</t>
+          <t>Why the EU Biotech Act must deliver practical improvements for clinical trials in Europe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>The Parliament Magazine</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/amgen-gets-fda-approval-to-reduce-monitoring-time-for-first-two-imdelltra-doses-ce785bdcdc81f62d</t>
+          <t>https://www.theparliamentmagazine.eu/partner/article/why-the-eu-biotech-act-must-deliver-practical-improvements-for-clinical-trials-in-europe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14-09-2026 14:00 UTC</t>
+          <t>15-09-2026 06:55 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions - FDA approval for a biologic</t>
+          <t>FDA / Regulatory Actions: healthcare policy affecting biotech/clinical trials</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lonza deepens US bet with commercial plant in Oregon</t>
+          <t>Transcript : Pfizer Inc. Presents at Morgan Stanley 24th Annual Global Healthcare Conference, Sep-14-2026 10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/lonza-deepens-us-bet-with-commercial-spray-drying-plant-in-oregon</t>
+          <t>https://www.marketscreener.com/news/transcript-pfizer-inc-presents-at-morgan-stanley-24th-annual-global-healthcare-conference-sep-14-ce785bdcdf81f720</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14-09-2026 10:48 UTC</t>
+          <t>14-09-2026 15:50 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - commercial plant for biologics CDMO</t>
+          <t>Industry Meetings &amp; Conferences: monitored company presenting at healthcare conference</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -719,27 +719,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Can Pfizer Overcome Its COVID and Patent Cliff Headwinds?</t>
+          <t>Pfizer loses patent case over Enbrel generic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Lawyerly</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/pfizer-overcome-covid-patent-cliff-133700992.html</t>
+          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14-09-2026 13:37 UTC</t>
+          <t>15-09-2026 07:27 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Earnings &amp; Financial Reports - strategic discussion mentioning patent cliff and growth</t>
+          <t>Biosimilars &amp; Biologics: biologic patent litigation involving monitored company</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Transcript : Pfizer Inc. Presents at Morgan Stanley 24th Annual Global Healthcare Conference, Sep-14-2026 10</t>
+          <t>Biogen Eyes Wave of Phase III Readouts as It Expands Beyond Neuroscience</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/transcript-pfizer-inc-presents-at-morgan-stanley-24th-annual-global-healthcare-conference-sep-14-ce785bdcdf81f720</t>
+          <t>https://finance.yahoo.com/healthcare/articles/biogen-eyes-wave-phase-iii-040205385.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-09-2026 15:50 UTC</t>
+          <t>15-09-2026 04:02 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Industry Meetings &amp; Conferences - investor presentation by monitored company, potential for biosimilar/biologic strategy discussion</t>
+          <t>Clinical Trials &amp; Pipeline News: monitored company pipeline strategy and expansion</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pfizer Says Major Headwinds Are Easing as Pipeline, Obesity Plans Take Center Stage</t>
+          <t>Trump's Drug Pricing Policy Could Drive Up Prices in South Korea and Other Overseas Markets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/pfizer-says-major-headwinds-easing-160235029.html</t>
+          <t>https://finance.biggo.com/news/65eb6133-9aae-4a67-ac88-0eff477771bb</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14-09-2026 16:02 UTC</t>
+          <t>14-09-2026 10:35 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Earnings &amp; Financial Reports - strategic discussion mentioning pipeline and obesity plans</t>
+          <t>Market Launches, Approvals &amp; Commercial Events: general drug pricing policy affecting market access for biologics/biosimilars</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -839,27 +839,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr Reddy's halts semaglutide supplies on impurity issue</t>
+          <t>Dr. Reddy’s Reports FDA Records Assessment at Mexican API Plant Concluding with Two Observations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-laboratories-delays-semaglutide-supplies-due-to-api-issue/45115417</t>
+          <t>https://www.tipranks.com/news/company-announcements/dr-reddys-reports-fda-records-assessment-at-mexican-api-plant-concluding-with-two-observations</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13-09-2026 19:05 UTC</t>
+          <t>14-09-2026 11:12 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - impurity issue affecting supply</t>
+          <t>FDA / Regulatory Actions: FDA inspection/observations at manufacturing plant of monitored company</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Reports FDA Records Assessment at Mexican API Plant Concluding with Two Observations</t>
+          <t>Aurobindo Pharma Unit-IV API Facility Concludes US FDA Inspection With Zero Observations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/dr-reddys-reports-fda-records-assessment-at-mexican-api-plant-concluding-with-two-observations</t>
+          <t>https://www.sahi.com/news/aurobindo-pharma-unit-iv-api-facility-concludes-us-fda-inspection-with-zero-observations</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14-09-2026 11:12 UTC</t>
+          <t>15-09-2026 00:55 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions - FDA assessment at API plant</t>
+          <t>FDA / Regulatory Actions: FDA inspection at manufacturing plant of monitored company</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C-CAMP National Bio Entrepreneurship competition 2026 recognises 15 startups and four student teams</t>
+          <t>High-Concentration, Low-Volume Subcutaneous Formulation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>PharmTech.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/c-camp-national-bio-entrepreneurship-competition-2026-recognises-15-startups-and-four-student-teams-21825</t>
+          <t>https://www.pharmtech.com/view/high-concentration-low-volume-subcutaneous-formulation</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14-09-2026 03:18 UTC</t>
+          <t>14-09-2026 19:11 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Industry Meetings &amp; Conferences - bio-entrepreneurship competition relevant to biotech ecosystem</t>
+          <t>Biosimilars &amp; Biologics: biologic formulation development from a monitored company</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SKUAST-K scholar wins national bio-entrepreneurship award</t>
+          <t>Celltrion files for US phase 4 trial of 240 mg Zymfentra dose</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>thekashmirimages.com</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2026/09/14/skuast-k-scholar-wins-national-bio-entrepreneurship-award/</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33176</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13-09-2026 18:41 UTC</t>
+          <t>15-09-2026 04:58 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monitored Companies - bio-entrepreneurship award relevant to biotech ecosystem</t>
+          <t>Clinical Trials &amp; Pipeline News: Phase 4 trial for a biologic (Zymfentra) from a monitored company</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,39 +987,39 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma's Apitoria clears US FDA inspection with zero observations</t>
+          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/aurobindo-pharmas-apitoria-clears-us-fda-inspection-with-zero-observations-21829</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14-09-2026 04:32 UTC</t>
+          <t>15-09-2026 01:35 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions - FDA inspection of API facility for monitored company</t>
+          <t>Biosimilars &amp; Biologics: SC formulation competition (lifecycle management) impacting market</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1027,39 +1027,39 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
+          <t>Enhertu EU Milestone And Legal Win Might Change The Case For Investing In Daiichi Sankyo (TSE:4568)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spherical Insights</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
+          <t>https://uk.finance.yahoo.com/news/enhertu-eu-milestone-legal-win-151207313.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51 UTC</t>
+          <t>14-09-2026 15:12 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - CDMO industry analysis</t>
+          <t>Clinical Trials &amp; Pipeline News: EU milestone and legal aspects for a biologic from a monitored company</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1079,27 +1079,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENHERTU® (fam-trastuzumab deruxtecan-nxki) demonstrated a median progression-free survival of 14.3 months as 1st-line therapy in patients with HER2-mutant advanced non-small cell lung cancer in DESTINY-Lung04 Phase III trial</t>
+          <t>Trastuzumab Deruxtecan Improves PFS in First-Line HER2-Mutant NSCLC in DESTINY-Lung04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/enhertu-fam-trastuzumab-deruxtecan-nxki-demonstrated-a-median-progression-free-survival-of-14-3-months-as-1st-line-therapy-in-patients-with-her2-mutant-advanced-non-small-cell-lung-cancer-in-destiny-lung04-phase-iii-trial</t>
+          <t>https://oncodaily.com/trial-updates/trastuzumab-deruxtecan-585631</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14-09-2026 04:21 UTC</t>
+          <t>14-09-2026 09:36 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News - clinical data for biologic product</t>
+          <t>Clinical Trials &amp; Pipeline News: clinical data for a biologic (ADC) from a monitored company</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1107,39 +1107,39 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>We're turning into a more innovative company: Teva Pharmaceuticals CEO Richard Francis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://www.cnbc.com/video/2026/09/14/were-turning-into-a-more-innovative-company-teva-pharmaceuticals-ceo-richard-francis.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13-09-2026 21:54 UTC</t>
+          <t>14-09-2026 18:58 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - policy affecting US plants and drug pricing</t>
+          <t>Monitored Companies: monitored company's strategic business update</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1147,39 +1147,39 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEDIPAL, JCR Dose First Patient in Global Phase I/II Trial of JR-446 for Sanfilippo Syndrome</t>
+          <t>Teva Pharmaceuticals Sees Pivot to Growth Accelerating on Branded Drugs, Biosimilars</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/86/8425/medipal-jcr-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-sanfilippo-syndrome.html</t>
+          <t>https://finance.yahoo.com/healthcare/articles/teva-pharmaceuticals-sees-pivot-growth-140227795.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-09-2026 18:36 UTC</t>
+          <t>14-09-2026 14:02 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News - clinical trial start for monitored company</t>
+          <t>Biosimilars &amp; Biologics: biosimilar business strategy from a monitored company</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1187,39 +1187,39 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AbelZeta Receives FDA IND Clearance for Phase 1b/2 Clinical Trial of C-CAR168 in Progressive Multiple Sclerosis</t>
+          <t>Pearce IP BioBlast® for the fortnight ending 11 September 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Pearce IP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/abelzeta-receives-fda-ind-clearance-for-phase-1b2-clinical-trial-of-c-car168-in-progressive-multiple-sclerosis-302877555.html</t>
+          <t>https://www.pearceip.law/2026/09/15/pearce-ip-bioblast-for-the-fortnight-ending-11-september-2026/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14-09-2026 11:30 UTC</t>
+          <t>15-09-2026 05:30 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions - FDA IND clearance for autoimmune advanced therapy</t>
+          <t>Biosimilars &amp; Biologics: biotech/biologics IP news from a monitored company</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1227,39 +1227,39 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Teva Pharmaceuticals Sees Pivot to Growth Accelerating on Branded Drugs, Biosimilars</t>
+          <t>Samsung Biologics signs USD 262 million manufacturing agreement with European pharmaceutical company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Drug Discovery News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/teva-pharmaceuticals-sees-pivot-growth-140227795.html</t>
+          <t>https://www.drugdiscoverynews.com/samsung-biologics-signs-usd-262-million-manufacturing-agreement-with-european-pharmaceutical-company-17527</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14-09-2026 14:02 UTC</t>
+          <t>14-09-2026 19:48 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics - company strategy mentions biosimilars</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: biologic manufacturing deal from a monitored company</t>
         </is>
       </c>
       <c r="G21" t="b">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -1279,27 +1279,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Songdo Opens Bio Training Center to Ease Talent Shortage</t>
+          <t>An Integrated Analytical Approach To Lipase Risk Management In Biologics Development</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Bioprocess Online</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/society/2026/09/14/songdo-opens-bio-training-center-to-ease-talent-shortage</t>
+          <t>https://www.bioprocessonline.com/doc/an-integrated-analytical-approach-to-lipase-risk-management-in-biologics-development-0001</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14-09-2026 00:29 UTC</t>
+          <t>15-09-2026 00:39 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - bio training center supporting biologics industry</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: biologic manufacturing/development technical topic</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1307,7 +1307,47 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Controlling Complexity In ADC Formulation Development</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bioprocess Online</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.bioprocessonline.com/doc/controlling-complexity-in-adc-formulation-development-0001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>15-09-2026 00:38 UTC</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity: biologic manufacturing/development technical topic</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1375,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-09-2026 22:44:15</t>
+          <t>15-09-2026 13:54:29</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lupin targets $500 million biosimilar revenue in five years</t>
+          <t>FDA reduces monitoring time for Amgen’s Imdelltra infusions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>pharmaceutical-technology.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
+          <t>https://www.pharmaceutical-technology.com/news/fda-reduces-monitoring-time-amgens-imdelltra/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14-09-2026 15:29 UTC</t>
+          <t>15-09-2026 10:49 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: biosimilar revenue targets/strategy</t>
+          <t>FDA regulatory action for a biologic</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Takeda R&amp;D President Andy Plump to Retire in 2027</t>
+          <t>Why the EU Biotech Act must deliver practical improvements for clinical trials in Europe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>The Parliament Magazine</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/takeda-rd-president-andy-plump-to-retire-in-2027/</t>
+          <t>https://www.theparliamentmagazine.eu/partner/article/why-the-eu-biotech-act-must-deliver-practical-improvements-for-clinical-trials-in-europe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14-09-2026 14:45 UTC</t>
+          <t>15-09-2026 06:55 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedolizumab / Entyvio primary signal: Takeda R&amp;D leadership change</t>
+          <t>FDA / Regulatory actions impacting biologics policy</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amgen Leads The Pack With First Filing For US Opdivo Biosimilar</t>
+          <t>Pfizer loses patent case over Enbrel generic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>Lawyerly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/amgen-leads-the-pack-with-first-filing-for-us-opdivo-biosimilar-PD6ZNDEA2VA4XKUQ44XCXQCZHI/</t>
+          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14-09-2026 10:30 UTC</t>
+          <t>15-09-2026 07:27 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: biosimilar FDA filing by monitored company</t>
+          <t>Biosimilars &amp; Biologics patent litigation</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amgen Gets FDA Approval to Reduce Monitoring Time for First Two Imdelltra Doses</t>
+          <t>Dr Reddy’s launches Opdivo biosimilar Nivorz in India, enters immuno-oncology segment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/amgen-gets-fda-approval-to-reduce-monitoring-time-for-first-two-imdelltra-doses-ce785bdcdc81f62d</t>
+          <t>https://www.moneycontrol.com/news/business/dr-reddy-s-launches-opdivo-biosimilar-nivorz-in-india-enters-immuno-oncology-segment-14030366.html/amp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14-09-2026 14:00 UTC</t>
+          <t>15-09-2026 12:06 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions: FDA approval for a biologic from a monitored company</t>
+          <t>Biosimilars &amp; Biologics biosimilar launch</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why the EU Biotech Act must deliver practical improvements for clinical trials in Europe</t>
+          <t>C-CAMP National Bio Entrepreneurship Competition 2026 sees 15 startups, 4 student teams bag top honours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The Parliament Magazine</t>
+          <t>Pharmabiz.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.theparliamentmagazine.eu/partner/article/why-the-eu-biotech-act-must-deliver-practical-improvements-for-clinical-trials-in-europe</t>
+          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=190587&amp;sid=2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-09-2026 06:55 UTC</t>
+          <t>15-09-2026 10:59 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions: healthcare policy affecting biotech/clinical trials</t>
+          <t>Industry meetings &amp; conferences related to biologics/biotech</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Transcript : Pfizer Inc. Presents at Morgan Stanley 24th Annual Global Healthcare Conference, Sep-14-2026 10</t>
+          <t>High-Concentration, Low-Volume Subcutaneous Formulation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>PharmTech.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/transcript-pfizer-inc-presents-at-morgan-stanley-24th-annual-global-healthcare-conference-sep-14-ce785bdcdf81f720</t>
+          <t>https://www.pharmtech.com/view/high-concentration-low-volume-subcutaneous-formulation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14-09-2026 15:50 UTC</t>
+          <t>14-09-2026 19:11 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Industry Meetings &amp; Conferences: monitored company presenting at healthcare conference</t>
+          <t>Biologic lifecycle management: formulation change</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pfizer loses patent case over Enbrel generic</t>
+          <t>Celltrion files for US phase 4 trial of 240 mg Zymfentra dose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lawyerly</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33176</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-09-2026 07:27 UTC</t>
+          <t>15-09-2026 05:33 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: biologic patent litigation involving monitored company</t>
+          <t>IBD clinical pipeline news for a biologic</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Biogen Eyes Wave of Phase III Readouts as It Expands Beyond Neuroscience</t>
+          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/biogen-eyes-wave-phase-iii-040205385.html</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15-09-2026 04:02 UTC</t>
+          <t>15-09-2026 01:35 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News: monitored company pipeline strategy and expansion</t>
+          <t>Biosimilars &amp; Biologics lifecycle management and patent competition</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trump's Drug Pricing Policy Could Drive Up Prices in South Korea and Other Overseas Markets</t>
+          <t>Enhertu Shows Six-Month PFS Gain In HER2-Mutant Lung Cancer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>BW Healthcare World</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/65eb6133-9aae-4a67-ac88-0eff477771bb</t>
+          <t>https://www.bwhealthcareworld.com/article/enhertu-shows-six-month-pfs-gain-in-her2-mutant-lung-cancer-623644</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14-09-2026 10:35 UTC</t>
+          <t>15-09-2026 04:53 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events: general drug pricing policy affecting market access for biologics/biosimilars</t>
+          <t>Clinical trials &amp; pipeline news for a biologic (ADC)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Reports FDA Records Assessment at Mexican API Plant Concluding with Two Observations</t>
+          <t>Evoke-03’s miss raises bar for TROP2 ADCs in front-line NSCLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>bioworld.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/dr-reddys-reports-fda-records-assessment-at-mexican-api-plant-concluding-with-two-observations</t>
+          <t>https://www.bioworld.com/articles/734037-evoke-03s-miss-raises-bar-for-trop2-adcs-in-front-line-nsclc</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14-09-2026 11:12 UTC</t>
+          <t>14-09-2026 16:00 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions: FDA inspection/observations at manufacturing plant of monitored company</t>
+          <t>Clinical trials &amp; pipeline news for a biologic (ADC)</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Unit-IV API Facility Concludes US FDA Inspection With Zero Observations</t>
+          <t>China phase III trials make case for B7-H3 ADCs in relapsed SCLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>bioworld.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/aurobindo-pharma-unit-iv-api-facility-concludes-us-fda-inspection-with-zero-observations</t>
+          <t>https://www.bioworld.com/articles/734038-china-phase-iii-trials-make-case-for-b7-h3-adcs-in-relapsed-sclc</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15-09-2026 00:55 UTC</t>
+          <t>14-09-2026 16:00 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions: FDA inspection at manufacturing plant of monitored company</t>
+          <t>Clinical trials &amp; pipeline news for a biologic (ADC)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>High-Concentration, Low-Volume Subcutaneous Formulation</t>
+          <t>Pearce IP BioBlast® for the fortnight ending 11 September 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PharmTech.com</t>
+          <t>Pearce IP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pharmtech.com/view/high-concentration-low-volume-subcutaneous-formulation</t>
+          <t>https://www.pearceip.law/2026/09/15/pearce-ip-bioblast-for-the-fortnight-ending-11-september-2026/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14-09-2026 19:11 UTC</t>
+          <t>15-09-2026 05:30 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: biologic formulation development from a monitored company</t>
+          <t>Biosimilars &amp; Biologics patent/IP news</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -954,32 +954,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Celltrion files for US phase 4 trial of 240 mg Zymfentra dose</t>
+          <t>Samsung Biologics signs USD 262 million manufacturing agreement with European pharmaceutical company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Drug Discovery News</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33176</t>
+          <t>https://www.drugdiscoverynews.com/samsung-biologics-signs-usd-262-million-manufacturing-agreement-with-european-pharmaceutical-company-17527</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15-09-2026 04:58 UTC</t>
+          <t>14-09-2026 19:48 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News: Phase 4 trial for a biologic (Zymfentra) from a monitored company</t>
+          <t>Biologics manufacturing agreement / CDMO deal</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,39 +987,39 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
+          <t>An Integrated Analytical Approach To Lipase Risk Management In Biologics Development</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Bioprocess Online</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
+          <t>https://www.bioprocessonline.com/doc/an-integrated-analytical-approach-to-lipase-risk-management-in-biologics-development-0001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15-09-2026 01:35 UTC</t>
+          <t>15-09-2026 00:39 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: SC formulation competition (lifecycle management) impacting market</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity for biologics</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1027,325 +1027,45 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Enhertu EU Milestone And Legal Win Might Change The Case For Investing In Daiichi Sankyo (TSE:4568)</t>
+          <t>Controlling Complexity In ADC Formulation Development</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>Bioprocess Online</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/enhertu-eu-milestone-legal-win-151207313.html</t>
+          <t>https://www.bioprocessonline.com/doc/controlling-complexity-in-adc-formulation-development-0001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14-09-2026 15:12 UTC</t>
+          <t>15-09-2026 00:38 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News: EU milestone and legal aspects for a biologic from a monitored company</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity for biologics</t>
         </is>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Trastuzumab Deruxtecan Improves PFS in First-Line HER2-Mutant NSCLC in DESTINY-Lung04</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Oncodaily</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://oncodaily.com/trial-updates/trastuzumab-deruxtecan-585631</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>14-09-2026 09:36 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Clinical Trials &amp; Pipeline News: clinical data for a biologic (ADC) from a monitored company</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>We're turning into a more innovative company: Teva Pharmaceuticals CEO Richard Francis</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.cnbc.com/video/2026/09/14/were-turning-into-a-more-innovative-company-teva-pharmaceuticals-ceo-richard-francis.html</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>14-09-2026 18:58 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Monitored Companies: monitored company's strategic business update</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceuticals Sees Pivot to Growth Accelerating on Branded Drugs, Biosimilars</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/healthcare/articles/teva-pharmaceuticals-sees-pivot-growth-140227795.html</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>14-09-2026 14:02 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Biosimilars &amp; Biologics: biosimilar business strategy from a monitored company</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Pearce IP BioBlast® for the fortnight ending 11 September 2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Pearce IP</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.pearceip.law/2026/09/15/pearce-ip-bioblast-for-the-fortnight-ending-11-september-2026/</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>15-09-2026 05:30 UTC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Biosimilars &amp; Biologics: biotech/biologics IP news from a monitored company</t>
-        </is>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Samsung Biologics signs USD 262 million manufacturing agreement with European pharmaceutical company</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Drug Discovery News</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.drugdiscoverynews.com/samsung-biologics-signs-usd-262-million-manufacturing-agreement-with-european-pharmaceutical-company-17527</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>14-09-2026 19:48 UTC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: biologic manufacturing deal from a monitored company</t>
-        </is>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>An Integrated Analytical Approach To Lipase Risk Management In Biologics Development</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bioprocess Online</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessonline.com/doc/an-integrated-analytical-approach-to-lipase-risk-management-in-biologics-development-0001</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>15-09-2026 00:39 UTC</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: biologic manufacturing/development technical topic</t>
-        </is>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Controlling Complexity In ADC Formulation Development</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bioprocess Online</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessonline.com/doc/controlling-complexity-in-adc-formulation-development-0001</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>15-09-2026 00:38 UTC</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: biologic manufacturing/development technical topic</t>
-        </is>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
@@ -1375,7 +1095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-09-2026 13:54:29</t>
+          <t>15-09-2026 21:19:08</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FDA reduces monitoring time for Amgen’s Imdelltra infusions</t>
+          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pharmaceutical-technology.com</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-technology.com/news/fda-reduces-monitoring-time-amgens-imdelltra/</t>
+          <t>https://www.reuters.com/legal/litigation/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar-2026-09-15/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15-09-2026 10:49 UTC</t>
+          <t>15-09-2026 20:25 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FDA regulatory action for a biologic</t>
+          <t>2. BIOSIMILARS &amp; BIOLOGICS - Patent litigation involving a biosimilar from a monitored company</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why the EU Biotech Act must deliver practical improvements for clinical trials in Europe</t>
+          <t>FDA reduces initial monitoring time for Amgen’s Imdelltra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Parliament Magazine</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.theparliamentmagazine.eu/partner/article/why-the-eu-biotech-act-must-deliver-practical-improvements-for-clinical-trials-in-europe</t>
+          <t>https://www.indianpharmapost.com/regulatory/fda-reduces-initial-monitoring-time-for-amgens-imdelltra-21863</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15-09-2026 06:55 UTC</t>
+          <t>16-09-2026 02:37 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FDA / Regulatory actions impacting biologics policy</t>
+          <t>3. FDA / REGULATORY ACTIONS - FDA decision for a biologic from a monitored company</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pfizer loses patent case over Enbrel generic</t>
+          <t>Amgen Highlights MariTide, IMDELLTRA Pipeline Progress and Growth Priorities</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lawyerly</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
+          <t>https://finance.yahoo.com/healthcare/articles/amgen-highlights-maritide-imdelltra-pipeline-050213898.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15-09-2026 07:27 UTC</t>
+          <t>16-09-2026 05:02 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics patent litigation</t>
+          <t>8. MONITORED COMPANIES - Biologics pipeline strategy and milestones from monitored company</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches Opdivo biosimilar Nivorz in India, enters immuno-oncology segment</t>
+          <t>Eisai and Biogen Announce Japan Approval of LEQEMBI Pen, a Once-Weekly Subcutaneous Alzheimer’s Treatment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Quiver Quantitative</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/dr-reddy-s-launches-opdivo-biosimilar-nivorz-in-india-enters-immuno-oncology-segment-14030366.html/amp</t>
+          <t>https://www.quiverquant.com/news/Eisai+and+Biogen+Announce+Japan+Approval+of+LEQEMBI+Pen%2C+a+Once-Weekly+Subcutaneous+Alzheimer%E2%80%99s+Treatment</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15-09-2026 12:06 UTC</t>
+          <t>16-09-2026 06:10 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics biosimilar launch</t>
+          <t>4. MARKET LAUNCHES, APPROVALS &amp; COMMERCIAL EVENTS - Biologic approval from monitored company</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C-CAMP National Bio Entrepreneurship Competition 2026 sees 15 startups, 4 student teams bag top honours</t>
+          <t>Canada agrees to help pay for Alzheimer’s drug LEQEMBI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pharmabiz.com</t>
+          <t>Longevity.Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=190587&amp;sid=2</t>
+          <t>https://longevity.technology/news/canada-agrees-to-help-pay-for-alzheimers-drug-leqembi/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-09-2026 10:59 UTC</t>
+          <t>15-09-2026 23:10 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Industry meetings &amp; conferences related to biologics/biotech</t>
+          <t>4. MARKET LAUNCHES, APPROVALS &amp; COMMERCIAL EVENTS - Biologic market access/payer coverage from monitored company</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,32 +674,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>High-Concentration, Low-Volume Subcutaneous Formulation</t>
+          <t>Dr Reddy’s launches Opdivo biosimilar Nivorz in India, enters immuno-oncology segment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PharmTech.com</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pharmtech.com/view/high-concentration-low-volume-subcutaneous-formulation</t>
+          <t>https://www.moneycontrol.com/news/business/dr-reddy-s-launches-opdivo-biosimilar-nivorz-in-india-enters-immuno-oncology-segment-14030366.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14-09-2026 19:11 UTC</t>
+          <t>15-09-2026 12:06 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biologic lifecycle management: formulation change</t>
+          <t>2. BIOSIMILARS &amp; BIOLOGICS - Biosimilar launch in immuno-oncology by a monitored company</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celltrion files for US phase 4 trial of 240 mg Zymfentra dose</t>
+          <t>Aurobindo Pharma US FDA inspection at Telangana API facility concludes with 1 procedural observation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33176</t>
+          <t>https://www.cnbctv18.com/business/companies/aurobindo-pharma-us-fda-inspection-at-telangana-api-facility-concludes-with-1-procedural-observation-19991204.htm</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-09-2026 05:33 UTC</t>
+          <t>15-09-2026 14:14 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IBD clinical pipeline news for a biologic</t>
+          <t>5. MANUFACTURING, SUPPLY CHAIN &amp; CAPACITY - FDA inspection at monitored company's API facility</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
+          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
+          <t>https://www.biospectrumasia.com/news/25/28379/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15-09-2026 01:35 UTC</t>
+          <t>16-09-2026 03:54 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics lifecycle management and patent competition</t>
+          <t>6. PARTNERSHIPS, DEALS, LICENSING &amp; ACQUISITION - Biosimilar licensing deal from monitored company</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Enhertu Shows Six-Month PFS Gain In HER2-Mutant Lung Cancer</t>
+          <t>Complex-Molecule Specialist Shilpa CDMO Launches at CPHI Milan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BW Healthcare World</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/enhertu-shows-six-month-pfs-gain-in-her2-mutant-lung-cancer-623644</t>
+          <t>https://www.contractpharma.com/live_from_shows/complex-molecule-specialist-shilpa-cdmo-launches-at-cphi-milan/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15-09-2026 04:53 UTC</t>
+          <t>15-09-2026 19:33 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news for a biologic (ADC)</t>
+          <t>5. MANUFACTURING, SUPPLY CHAIN &amp; CAPACITY - CDMO launch for complex molecules from monitored company</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Evoke-03’s miss raises bar for TROP2 ADCs in front-line NSCLC</t>
+          <t>Zymfentra, Xcopri projected to become Korea’s 1st $1 billion blockbuster drugs in 2027</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bioworld.com</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/734037-evoke-03s-miss-raises-bar-for-trop2-adcs-in-front-line-nsclc</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33200</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14-09-2026 16:00 UTC</t>
+          <t>16-09-2026 06:19 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news for a biologic (ADC)</t>
+          <t>2. BIOSIMILARS &amp; BIOLOGICS - Commercial projection for biosimilar from monitored company</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>China phase III trials make case for B7-H3 ADCs in relapsed SCLC</t>
+          <t>Celltrion Submits Phase 4 Trial Plan for Zymfentra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bioworld.com</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/734038-china-phase-iii-trials-make-case-for-b7-h3-adcs-in-relapsed-sclc</t>
+          <t>https://www.thelec.net/news/articleView.html?idxno=13949</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14-09-2026 16:00 UTC</t>
+          <t>15-09-2026 22:49 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news for a biologic (ADC)</t>
+          <t>7. CLINICAL TRIALS &amp; PIPELINE NEWS - Biosimilar clinical trial update from monitored company</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,32 +914,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pearce IP BioBlast® for the fortnight ending 11 September 2026</t>
+          <t>AstraZeneca, Daiichi Sankyo’s ENHERTU Cuts Disease Progression Risk by 37% in HER2-Mutant Lung Cancer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pearce IP</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pearceip.law/2026/09/15/pearce-ip-bioblast-for-the-fortnight-ending-11-september-2026/</t>
+          <t>https://biopharmaapac.com/news/31/8438/astrazeneca-daiichi-sankyos-enhertu-cuts-disease-progression-risk-by-37-in-her2-mutant-lung-cancer.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15-09-2026 05:30 UTC</t>
+          <t>16-09-2026 00:32 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics patent/IP news</t>
+          <t>7. CLINICAL TRIALS &amp; PIPELINE NEWS - Biologic clinical data from monitored company</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -954,32 +954,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Samsung Biologics signs USD 262 million manufacturing agreement with European pharmaceutical company</t>
+          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Drug Discovery News</t>
+          <t>Kompasiana.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.drugdiscoverynews.com/samsung-biologics-signs-usd-262-million-manufacturing-agreement-with-european-pharmaceutical-company-17527</t>
+          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14-09-2026 19:48 UTC</t>
+          <t>16-09-2026 05:53 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Biologics manufacturing agreement / CDMO deal</t>
+          <t>2. BIOSIMILARS &amp; BIOLOGICS - Biosimilar market report</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,87 +987,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>An Integrated Analytical Approach To Lipase Risk Management In Biologics Development</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bioprocess Online</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessonline.com/doc/an-integrated-analytical-approach-to-lipase-risk-management-in-biologics-development-0001</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>15-09-2026 00:39 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity for biologics</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Controlling Complexity In ADC Formulation Development</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bioprocess Online</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessonline.com/doc/controlling-complexity-in-adc-formulation-development-0001</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>15-09-2026 00:38 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity for biologics</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1015,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-09-2026 21:19:08</t>
+          <t>16-09-2026 13:49:08</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
+          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Kompasiana.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar-2026-09-15/</t>
+          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15-09-2026 20:25 UTC</t>
+          <t>16-09-2026 05:53 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2. BIOSIMILARS &amp; BIOLOGICS - Patent litigation involving a biosimilar from a monitored company</t>
+          <t>Biosimilars &amp; Biologics - biosimilar market report</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FDA reduces initial monitoring time for Amgen’s Imdelltra</t>
+          <t>BMS, Ono take Amgen to task as FDA's Opdivo biosimilar decision looms</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>fiercepharma.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/regulatory/fda-reduces-initial-monitoring-time-for-amgens-imdelltra-21863</t>
+          <t>https://www.fiercepharma.com/pharma/bms-ono-take-amgen-task-fdas-opdivo-biosimilar-decision-looms</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16-09-2026 02:37 UTC</t>
+          <t>16-09-2026 15:08 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3. FDA / REGULATORY ACTIONS - FDA decision for a biologic from a monitored company</t>
+          <t>Biosimilars &amp; Biologics - biosimilar patent litigation for monitored company</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amgen Highlights MariTide, IMDELLTRA Pipeline Progress and Growth Priorities</t>
+          <t>FDA cuts monitoring time for first two doses of Amgen’s IMDELLTRA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/amgen-highlights-maritide-imdelltra-pipeline-050213898.html</t>
+          <t>https://www.indianpharmapost.com/regulatory/fda-cuts-monitoring-time-for-first-two-doses-of-amgens-imdelltra-21872</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16-09-2026 05:02 UTC</t>
+          <t>16-09-2026 12:26 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8. MONITORED COMPANIES - Biologics pipeline strategy and milestones from monitored company</t>
+          <t>FDA / Regulatory Actions - FDA action for monitored company's biologic</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eisai and Biogen Announce Japan Approval of LEQEMBI Pen, a Once-Weekly Subcutaneous Alzheimer’s Treatment</t>
+          <t>Amgen Highlights MariTide, IMDELLTRA Pipeline Progress and Growth Priorities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quiver Quantitative</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.quiverquant.com/news/Eisai+and+Biogen+Announce+Japan+Approval+of+LEQEMBI+Pen%2C+a+Once-Weekly+Subcutaneous+Alzheimer%E2%80%99s+Treatment</t>
+          <t>https://finance.yahoo.com/healthcare/articles/amgen-highlights-maritide-imdelltra-pipeline-050213898.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16-09-2026 06:10 UTC</t>
+          <t>16-09-2026 05:02 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4. MARKET LAUNCHES, APPROVALS &amp; COMMERCIAL EVENTS - Biologic approval from monitored company</t>
+          <t>Clinical Trials &amp; Pipeline News - pipeline progress for monitored company's biologic</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Canada agrees to help pay for Alzheimer’s drug LEQEMBI</t>
+          <t>In 2017, a fully automated facility for plant bioscience research was launched to the International Space</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Longevity.Technology</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://longevity.technology/news/canada-agrees-to-help-pay-for-alzheimers-drug-leqembi/</t>
+          <t>https://m.economictimes.com/news/international/us/science-in-2017-a-fully-automated-facility-for-plant-bioscience-research-was-launched-to-the-international-space-station-what-nasa-studied-in-space/articleshow/134275632.cms</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-09-2026 23:10 UTC</t>
+          <t>16-09-2026 00:13 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4. MARKET LAUNCHES, APPROVALS &amp; COMMERCIAL EVENTS - Biologic market access/payer coverage from monitored company</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity - plant bioscience research facility for monitored company</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,32 +674,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches Opdivo biosimilar Nivorz in India, enters immuno-oncology segment</t>
+          <t>Pfizer follows AstraZeneca in pulling EU bladder cancer filing after CHMP concerns</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>allsci.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/dr-reddy-s-launches-opdivo-biosimilar-nivorz-in-india-enters-immuno-oncology-segment-14030366.html</t>
+          <t>https://allsci.com/news/regulatory/zumrad-eu-application-pfizer-withdraws-zumrads/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15-09-2026 12:06 UTC</t>
+          <t>16-09-2026 11:12 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2. BIOSIMILARS &amp; BIOLOGICS - Biosimilar launch in immuno-oncology by a monitored company</t>
+          <t>FDA / Regulatory Actions - regulatory withdrawal for monitored company's biologic oncology drug</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma US FDA inspection at Telangana API facility concludes with 1 procedural observation</t>
+          <t>IP Group: NAV Reaches £1 Billion As Pfizer Obesity Royalty Value Rises To £152 Million</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>Pulse 2.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/business/companies/aurobindo-pharma-us-fda-inspection-at-telangana-api-facility-concludes-with-1-procedural-observation-19991204.htm</t>
+          <t>https://pulse2.com/ip-group-nav-reaches-1-billion-as-pfizer-obesity-royalty-value-rises-to-152-million/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-09-2026 14:14 UTC</t>
+          <t>16-09-2026 13:10 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5. MANUFACTURING, SUPPLY CHAIN &amp; CAPACITY - FDA inspection at monitored company's API facility</t>
+          <t>Earnings &amp; Financial Reports - specific drug royalty value (likely biologic) for monitored company</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
+          <t>LEQEMBI® Pen (Subcutaneous Formulation of LEQEMBI®)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/25/28379/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market.html</t>
+          <t>https://www.globenewswire.com/news-release/2026/09/16/3362836/0/en/leqembi-pen-subcutaneous-formulation-of-leqembi-approved-in-japan-for-the-treatment-of-early-alzheimer-s-disease.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16-09-2026 03:54 UTC</t>
+          <t>16-09-2026 06:00 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6. PARTNERSHIPS, DEALS, LICENSING &amp; ACQUISITION - Biosimilar licensing deal from monitored company</t>
+          <t>Biosimilars &amp; Biologics - biologic lifecycle management/new formulation approval for monitored company</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Complex-Molecule Specialist Shilpa CDMO Launches at CPHI Milan</t>
+          <t>Canada agrees to help pay for Alzheimer’s drug LEQEMBI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>Longevity.Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/live_from_shows/complex-molecule-specialist-shilpa-cdmo-launches-at-cphi-milan/</t>
+          <t>https://longevity.technology/news/canada-agrees-to-help-pay-for-alzheimers-drug-leqembi/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15-09-2026 19:33 UTC</t>
+          <t>15-09-2026 23:10 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5. MANUFACTURING, SUPPLY CHAIN &amp; CAPACITY - CDMO launch for complex molecules from monitored company</t>
+          <t>Market Launches, Approvals &amp; Commercial Events - market access for monitored company's biologic</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri projected to become Korea’s 1st $1 billion blockbuster drugs in 2027</t>
+          <t>Dr. Reddy’s forays into India’s biosimilar immuno-oncology market, launches Nivorz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33200</t>
+          <t>https://www.thehindu.com/business/Industry/dr-reddys-forays-into-indias-biosimilar-immuno-oncology-market-launches-nivorz/article71469381.ece</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16-09-2026 06:19 UTC</t>
+          <t>15-09-2026 16:03 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2. BIOSIMILARS &amp; BIOLOGICS - Commercial projection for biosimilar from monitored company</t>
+          <t>Market Launches, Approvals &amp; Commercial Events - biosimilar launch for monitored company</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Celltrion Submits Phase 4 Trial Plan for Zymfentra</t>
+          <t>Aurobindo arm Apitoria gets USFDA observation for Telangana API unit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.thelec.net/news/articleView.html?idxno=13949</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/aurobindo-arm-apitoria-gets-usfda-observation-for-telangana-api-unit/articleshow/134268517.cms</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15-09-2026 22:49 UTC</t>
+          <t>15-09-2026 16:04 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7. CLINICAL TRIALS &amp; PIPELINE NEWS - Biosimilar clinical trial update from monitored company</t>
+          <t>FDA / Regulatory Actions - FDA inspection observation for monitored company</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo’s ENHERTU Cuts Disease Progression Risk by 37% in HER2-Mutant Lung Cancer</t>
+          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/31/8438/astrazeneca-daiichi-sankyos-enhertu-cuts-disease-progression-risk-by-37-in-her2-mutant-lung-cancer.html</t>
+          <t>https://www.expresspharma.in/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16-09-2026 00:32 UTC</t>
+          <t>16-09-2026 07:32 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7. CLINICAL TRIALS &amp; PIPELINE NEWS - Biologic clinical data from monitored company</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition - biosimilar licensing deal for monitored company</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,45 +947,365 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Shilpa Biologicals</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Complex-Molecule Specialist Shilpa CDMO Launches at CPHI Milan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Contract Pharma</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.contractpharma.com/live_from_shows/complex-molecule-specialist-shilpa-cdmo-launches-at-cphi-milan/</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>15-09-2026 19:33 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity - CDMO launch/capacity for monitored company</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Zymfentra, Xcopri projected to become Korea’s 1st $1 billion blockbuster drugs in 2027</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Korea Biomedical Review</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33200</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>16-09-2026 06:19 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Market Launches, Approvals &amp; Commercial Events - blockbuster projection for monitored company's biologic</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Celltrion Submits Phase 4 Trial Plan for Zymfentra</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>thelec.net</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.thelec.net/news/articleView.html?idxno=13949</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>15-09-2026 22:49 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Clinical Trials &amp; Pipeline News - Phase 4 trial plan for monitored company's biologic</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AstraZeneca, Daiichi Sankyo’s ENHERTU Cuts Disease Progression Risk by 37% in HER2-Mutant Lung Cancer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BioPharma APAC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://biopharmaapac.com/news/31/8438/astrazeneca-daiichi-sankyos-enhertu-cuts-disease-progression-risk-by-37-in-her2-mutant-lung-cancer.html</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16-09-2026 00:32 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Clinical Trials &amp; Pipeline News - clinical data for monitored company's biologic</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Daiichi and AstraZeneca cancer drugs secure further approvals in Japan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/news/daiichi-and-astrazeneca-cancer-drugs-secure-further-approvals-in-japan-ce785bd2da8bff24</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>16-09-2026 08:47 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FDA / Regulatory Actions - drug approvals for monitored company's biologics</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Kompasiana.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>16-09-2026 05:53 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2. BIOSIMILARS &amp; BIOLOGICS - Biosimilar market report</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BIX 2026 Names Canada as Country of Honor, Showcasing Bioindustry Trends from BCI to Biotech Foods</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>더바이오</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28154</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>15-09-2026 23:49 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Industry Meetings &amp; Conferences - bioindustry trends conference</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Corrugated Vial Shipping Trays Market Forecast to 2035: Biologics Demand Drives Expansion - News and Statistics</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/corrugated-vial-shipping-trays-market-to-accelerate-on-biologics-demand-reaching-2035-growth/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>16-09-2026 13:31 UTC</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity - biologics demand market report</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CDMO Capacity: Stainless by Volume, Single-Use by Number</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Contract Pharma</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.contractpharma.com/exclusives/cdmo-capacity-stainless-by-volume-single-use-by-number/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>15-09-2026 18:03 UTC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity - CDMO capacity report</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Biologics Contract Manufacturing Market to Reach US$ 83.47</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4633375/biologics-contract-manufacturing-market-to-reach-us-83-47</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>16-09-2026 13:24 UTC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity - biologics contract manufacturing market report</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1015,7 +1335,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16-09-2026 13:49:08</t>
+          <t>16-09-2026 21:11:54</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
+          <t>‘It’s Incredibly Rare In A Career To Be In This Position’ – Sandoz CFO On Bio100 And The Path Ahead</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kompasiana.com</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
+          <t>https://insights.citeline.com/generics-bulletin/leadership/interviews/its-incredibly-rare-in-a-career-to-be-in-this-position-sandoz-cfo-on-bio100-and-the-path-ahead-XYNMGOM3BNEXXBNG4RDWBV3U3Y/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16-09-2026 05:53 UTC</t>
+          <t>16-09-2026 12:23 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics - biosimilar market report</t>
+          <t>Monitored company Sandoz discusses biosimilar strategy</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -524,7 +524,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fiercepharma.com</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics - biosimilar patent litigation for monitored company</t>
+          <t>Biosimilar patent litigation involving monitored company Amgen</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -579,7 +579,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions - FDA action for monitored company's biologic</t>
+          <t>FDA action for a biologic from monitored company Amgen</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amgen Highlights MariTide, IMDELLTRA Pipeline Progress and Growth Priorities</t>
+          <t>Pfizer follows AstraZeneca in pulling EU bladder cancer filing after CHMP concerns</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/amgen-highlights-maritide-imdelltra-pipeline-050213898.html</t>
+          <t>https://allsci.com/news/regulatory/zumrad-eu-application-pfizer-withdraws-zumrads/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16-09-2026 05:02 UTC</t>
+          <t>16-09-2026 11:12 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News - pipeline progress for monitored company's biologic</t>
+          <t>FDA/regulatory action for a monitored company (Pfizer)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>In 2017, a fully automated facility for plant bioscience research was launched to the International Space</t>
+          <t>Japan approves subcutaneous formulation of LEQEMBI® for treatment of early Alzheimer’s Disease</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/international/us/science-in-2017-a-fully-automated-facility-for-plant-bioscience-research-was-launched-to-the-international-space-station-what-nasa-studied-in-space/articleshow/134275632.cms</t>
+          <t>https://www.biospectrumasia.com/news/30/28386/japan-approves-subcutaneous-formulation-of-leqembi-for-treatment-of-early-alzheimers-disease-.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16-09-2026 00:13 UTC</t>
+          <t>17-09-2026 07:26 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - plant bioscience research facility for monitored company</t>
+          <t>Biologics lifecycle management: Japan approval for new formulation of Biogen's monoclonal antibody</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,32 +674,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pfizer follows AstraZeneca in pulling EU bladder cancer filing after CHMP concerns</t>
+          <t>Sjögren's Syndrome Market to Witness Sustained Growth During the Forecast Period (2026-2036) Due to the Development of Targeted Immunotherapies, FcRn Inhibitors, TYK2 Inhibitors, and Cell Therapies | DelveInsight</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>allsci.com</t>
+          <t>prnewswire.co.uk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/regulatory/zumrad-eu-application-pfizer-withdraws-zumrads/</t>
+          <t>https://www.prnewswire.co.uk/news-releases/sjogrens-syndrome-market-to-witness-sustained-growth-during-the-forecast-period-20262036-due-to-the-development-of-targeted-immunotherapies-fcrn-inhibitors-tyk2-inhibitors-and-cell-therapies--delveinsight-302880061.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16-09-2026 11:12 UTC</t>
+          <t>16-09-2026 14:31 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions - regulatory withdrawal for monitored company's biologic oncology drug</t>
+          <t>Clinical pipeline news: market report on immunology/autoimmune therapies (Sjögren's Syndrome)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IP Group: NAV Reaches £1 Billion As Pfizer Obesity Royalty Value Rises To £152 Million</t>
+          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pulse 2.0</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pulse2.com/ip-group-nav-reaches-1-billion-as-pfizer-obesity-royalty-value-rises-to-152-million/</t>
+          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-09-2026 13:10 UTC</t>
+          <t>16-09-2026 13:24 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Earnings &amp; Financial Reports - specific drug royalty value (likely biologic) for monitored company</t>
+          <t>Partnerships &amp; Deals: monitored company Shilpa Biologicals inks biosimilar deal</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LEQEMBI® Pen (Subcutaneous Formulation of LEQEMBI®)</t>
+          <t>Celltrion captures Japan lead with Remsima biosimilar, eyes SC launch - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/09/16/3362836/0/en/leqembi-pen-subcutaneous-formulation-of-leqembi-approved-in-japan-for-the-treatment-of-early-alzheimer-s-disease.html</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/17/EBUUYC3ILVC6THC2NCM5WFOSQU/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16-09-2026 06:00 UTC</t>
+          <t>16-09-2026 23:56 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics - biologic lifecycle management/new formulation approval for monitored company</t>
+          <t>Market Launch &amp; Commercial Events: Celltrion's Remsima (infliximab biosimilar, IBD competitor) achieves market lead in Japan, eyes SC launch</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Canada agrees to help pay for Alzheimer’s drug LEQEMBI</t>
+          <t>Zymfentra, Xcopri Near $1 Billion Sales Mark</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Longevity.Technology</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://longevity.technology/news/canada-agrees-to-help-pay-for-alzheimers-drug-leqembi/</t>
+          <t>https://en.sedaily.com/finance/2026/09/17/zymfentra-xcopri-near-1-billion-sales-mark</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15-09-2026 23:10 UTC</t>
+          <t>16-09-2026 22:00 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events - market access for monitored company's biologic</t>
+          <t>Market Launch &amp; Commercial Events: Celltrion's Zymfentra (infliximab biosimilar, IBD competitor) approaching sales milestone</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s forays into India’s biosimilar immuno-oncology market, launches Nivorz</t>
+          <t>AZ, Daiichi's Enhertu scores long-awaited NICE blessing in HER2-low breast cancer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/dr-reddys-forays-into-indias-biosimilar-immuno-oncology-market-launches-nivorz/article71469381.ece</t>
+          <t>https://www.fiercepharma.com/pharma/az-daiichis-enhertu-wins-long-awaited-nice-blessing</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15-09-2026 16:03 UTC</t>
+          <t>16-09-2026 23:30 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events - biosimilar launch for monitored company</t>
+          <t>Market Launch &amp; Commercial Events: Regulatory/market access approval for a biologic from monitored company Daiichi Sankyo</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aurobindo arm Apitoria gets USFDA observation for Telangana API unit</t>
+          <t>Daiichi and AstraZeneca cancer drugs secure further approvals in Japan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/aurobindo-arm-apitoria-gets-usfda-observation-for-telangana-api-unit/articleshow/134268517.cms</t>
+          <t>https://www.marketscreener.com/news/daiichi-and-astrazeneca-cancer-drugs-secure-further-approvals-in-japan-ce785bd2da8bff24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15-09-2026 16:04 UTC</t>
+          <t>16-09-2026 08:47 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions - FDA inspection observation for monitored company</t>
+          <t>FDA / Regulatory Actions: Regulatory approvals for biologics from monitored company Daiichi Sankyo</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
+          <t>Teva’s Lab-Made Antibody Shot for Celiac Shows Hopeful Results</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>allergicliving.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market/</t>
+          <t>https://www.allergicliving.com/2026/09/16/tevas-lab-made-antibody-shot-for-celiac-shows-hopeful-results/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16-09-2026 07:32 UTC</t>
+          <t>16-09-2026 22:36 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition - biosimilar licensing deal for monitored company</t>
+          <t>Clinical Trials &amp; Pipeline News: Teva's antibody (biologic) for celiac disease (immunology/autoimmune) shows hopeful results</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Complex-Molecule Specialist Shilpa CDMO Launches at CPHI Milan</t>
+          <t>Corrugated Vial Shipping Trays Market Forecast to 2035: Biologics Demand Drives Expansion - News and Statistics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/live_from_shows/complex-molecule-specialist-shilpa-cdmo-launches-at-cphi-milan/</t>
+          <t>https://www.indexbox.io/blog/corrugated-vial-shipping-trays-market-to-accelerate-on-biologics-demand-reaching-2035-growth/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15-09-2026 19:33 UTC</t>
+          <t>16-09-2026 13:31 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - CDMO launch/capacity for monitored company</t>
+          <t>Biosimilars &amp; Biologics: market forecast explicitly driven by biologics demand</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,327 +987,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Zymfentra, Xcopri projected to become Korea’s 1st $1 billion blockbuster drugs in 2027</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Korea Biomedical Review</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33200</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>16-09-2026 06:19 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Market Launches, Approvals &amp; Commercial Events - blockbuster projection for monitored company's biologic</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Celltrion Submits Phase 4 Trial Plan for Zymfentra</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>thelec.net</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.thelec.net/news/articleView.html?idxno=13949</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>15-09-2026 22:49 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Clinical Trials &amp; Pipeline News - Phase 4 trial plan for monitored company's biologic</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AstraZeneca, Daiichi Sankyo’s ENHERTU Cuts Disease Progression Risk by 37% in HER2-Mutant Lung Cancer</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BioPharma APAC</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://biopharmaapac.com/news/31/8438/astrazeneca-daiichi-sankyos-enhertu-cuts-disease-progression-risk-by-37-in-her2-mutant-lung-cancer.html</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>16-09-2026 00:32 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Clinical Trials &amp; Pipeline News - clinical data for monitored company's biologic</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Daiichi and AstraZeneca cancer drugs secure further approvals in Japan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/news/daiichi-and-astrazeneca-cancer-drugs-secure-further-approvals-in-japan-ce785bd2da8bff24</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>16-09-2026 08:47 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>FDA / Regulatory Actions - drug approvals for monitored company's biologics</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BIX 2026 Names Canada as Country of Honor, Showcasing Bioindustry Trends from BCI to Biotech Foods</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>더바이오</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28154</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>15-09-2026 23:49 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Industry Meetings &amp; Conferences - bioindustry trends conference</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
           <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Corrugated Vial Shipping Trays Market Forecast to 2035: Biologics Demand Drives Expansion - News and Statistics</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>IndexBox</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/corrugated-vial-shipping-trays-market-to-accelerate-on-biologics-demand-reaching-2035-growth/</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>16-09-2026 13:31 UTC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - biologics demand market report</t>
-        </is>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CDMO Capacity: Stainless by Volume, Single-Use by Number</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Contract Pharma</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.contractpharma.com/exclusives/cdmo-capacity-stainless-by-volume-single-use-by-number/</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>15-09-2026 18:03 UTC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - CDMO capacity report</t>
-        </is>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Biologics Contract Manufacturing Market to Reach US$ 83.47</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://www.openpr.com/news/4633375/biologics-contract-manufacturing-market-to-reach-us-83-47</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>16-09-2026 13:24 UTC</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity - biologics contract manufacturing market report</t>
-        </is>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1015,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16-09-2026 21:11:54</t>
+          <t>17-09-2026 13:55:49</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>‘It’s Incredibly Rare In A Career To Be In This Position’ – Sandoz CFO On Bio100 And The Path Ahead</t>
+          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>thepharmaletter.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/leadership/interviews/its-incredibly-rare-in-a-career-to-be-in-this-position-sandoz-cfo-on-bio100-and-the-path-ahead-XYNMGOM3BNEXXBNG4RDWBV3U3Y/</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16-09-2026 12:23 UTC</t>
+          <t>17-09-2026 12:50 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company Sandoz discusses biosimilar strategy</t>
+          <t>monitored company (Amgen) biosimilar patent litigation</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BMS, Ono take Amgen to task as FDA's Opdivo biosimilar decision looms</t>
+          <t>Amneal expands India operations after Kashiv buy, builds biosimilars portfolio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/bms-ono-take-amgen-task-fdas-opdivo-biosimilar-decision-looms</t>
+          <t>https://www.businesstoday.in/amp/latest/corporate/story/amneal-expands-india-operations-after-kashiv-buy-builds-biosimilars-portfolio-556089-2026-09-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16-09-2026 15:08 UTC</t>
+          <t>17-09-2026 07:02 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Biosimilar patent litigation involving monitored company Amgen</t>
+          <t>monitored company (Amneal Kashiv Biosciences) building biosimilars portfolio through acquisition</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FDA cuts monitoring time for first two doses of Amgen’s IMDELLTRA</t>
+          <t>Fire Breaks Out At Pfizer Facility In Andover</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>andovermanews.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/regulatory/fda-cuts-monitoring-time-for-first-two-doses-of-amgens-imdelltra-21872</t>
+          <t>https://andovermanews.com/fire-breaks-out-at-pfizer-facility-in-andover/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16-09-2026 12:26 UTC</t>
+          <t>17-09-2026 13:50 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FDA action for a biologic from monitored company Amgen</t>
+          <t>manufacturing event at a monitored company (Pfizer), potentially affecting biologic supply</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pfizer follows AstraZeneca in pulling EU bladder cancer filing after CHMP concerns</t>
+          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AllSci</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/regulatory/zumrad-eu-application-pfizer-withdraws-zumrads/</t>
+          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16-09-2026 11:12 UTC</t>
+          <t>17-09-2026 13:41 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FDA/regulatory action for a monitored company (Pfizer)</t>
+          <t>manufacturing approval for sterile injectable site, relevant to biologics/biosimilars supply chain</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Japan approves subcutaneous formulation of LEQEMBI® for treatment of early Alzheimer’s Disease</t>
+          <t>Celltrion captures Japan lead with Remsima biosimilar, eyes SC launch - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/30/28386/japan-approves-subcutaneous-formulation-of-leqembi-for-treatment-of-early-alzheimers-disease-.html</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/17/EBUUYC3ILVC6THC2NCM5WFOSQU/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17-09-2026 07:26 UTC</t>
+          <t>16-09-2026 23:56 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biologics lifecycle management: Japan approval for new formulation of Biogen's monoclonal antibody</t>
+          <t>monitored company (Celltrion) biosimilar (Remsima, infliximab) achieves market leadership and plans SC launch in a key market; direct IBD competitor</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,32 +674,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sjögren's Syndrome Market to Witness Sustained Growth During the Forecast Period (2026-2036) Due to the Development of Targeted Immunotherapies, FcRn Inhibitors, TYK2 Inhibitors, and Cell Therapies | DelveInsight</t>
+          <t>Zymfentra, Xcopri Near $1 Billion Sales Mark</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>prnewswire.co.uk</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.co.uk/news-releases/sjogrens-syndrome-market-to-witness-sustained-growth-during-the-forecast-period-20262036-due-to-the-development-of-targeted-immunotherapies-fcrn-inhibitors-tyk2-inhibitors-and-cell-therapies--delveinsight-302880061.html</t>
+          <t>https://en.sedaily.com/finance/2026/09/17/zymfentra-xcopri-near-1-billion-sales-mark</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16-09-2026 14:31 UTC</t>
+          <t>16-09-2026 22:00 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Clinical pipeline news: market report on immunology/autoimmune therapies (Sjögren's Syndrome)</t>
+          <t>monitored company (Celltrion) biologics revenue update (Zymfentra is SC infliximab, an IBD relevant biologic)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
+          <t>Teva’s Lab-Made Antibody Shot for Celiac Shows Hopeful Results</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Allergic Living</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
+          <t>https://www.allergicliving.com/2026/09/16/tevas-lab-made-antibody-shot-for-celiac-shows-hopeful-results/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-09-2026 13:24 UTC</t>
+          <t>16-09-2026 22:36 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Partnerships &amp; Deals: monitored company Shilpa Biologicals inks biosimilar deal</t>
+          <t>monitored company (Teva) clinical pipeline news for an autoimmune disease biologic (antibody)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,247 +747,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Celltrion captures Japan lead with Remsima biosimilar, eyes SC launch - CHOSUNBIZ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/17/EBUUYC3ILVC6THC2NCM5WFOSQU/</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>16-09-2026 23:56 UTC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Market Launch &amp; Commercial Events: Celltrion's Remsima (infliximab biosimilar, IBD competitor) achieves market lead in Japan, eyes SC launch</t>
-        </is>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
           <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Zymfentra, Xcopri Near $1 Billion Sales Mark</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Seoul Economic Daily</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://en.sedaily.com/finance/2026/09/17/zymfentra-xcopri-near-1-billion-sales-mark</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>16-09-2026 22:00 UTC</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Market Launch &amp; Commercial Events: Celltrion's Zymfentra (infliximab biosimilar, IBD competitor) approaching sales milestone</t>
-        </is>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AZ, Daiichi's Enhertu scores long-awaited NICE blessing in HER2-low breast cancer</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Fierce Pharma</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://www.fiercepharma.com/pharma/az-daiichis-enhertu-wins-long-awaited-nice-blessing</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>16-09-2026 23:30 UTC</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Market Launch &amp; Commercial Events: Regulatory/market access approval for a biologic from monitored company Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Daiichi and AstraZeneca cancer drugs secure further approvals in Japan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/news/daiichi-and-astrazeneca-cancer-drugs-secure-further-approvals-in-japan-ce785bd2da8bff24</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>16-09-2026 08:47 UTC</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>FDA / Regulatory Actions: Regulatory approvals for biologics from monitored company Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Teva’s Lab-Made Antibody Shot for Celiac Shows Hopeful Results</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>allergicliving.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://www.allergicliving.com/2026/09/16/tevas-lab-made-antibody-shot-for-celiac-shows-hopeful-results/</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>16-09-2026 22:36 UTC</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Clinical Trials &amp; Pipeline News: Teva's antibody (biologic) for celiac disease (immunology/autoimmune) shows hopeful results</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Corrugated Vial Shipping Trays Market Forecast to 2035: Biologics Demand Drives Expansion - News and Statistics</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>IndexBox</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/corrugated-vial-shipping-trays-market-to-accelerate-on-biologics-demand-reaching-2035-growth/</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>16-09-2026 13:31 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Biosimilars &amp; Biologics: market forecast explicitly driven by biologics demand</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -1015,7 +775,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-09-2026 13:55:49</t>
+          <t>17-09-2026 21:18:08</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
+          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>thepharmaletter.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
+          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17-09-2026 12:50 UTC</t>
+          <t>18-09-2026 05:36 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>monitored company (Amgen) biosimilar patent litigation</t>
+          <t>Biosimilars &amp; Biologics: Sandoz biosimilar development deal</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amneal expands India operations after Kashiv buy, builds biosimilars portfolio</t>
+          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/amp/latest/corporate/story/amneal-expands-india-operations-after-kashiv-buy-builds-biosimilars-portfolio-556089-2026-09-17</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17-09-2026 07:02 UTC</t>
+          <t>17-09-2026 12:54 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>monitored company (Amneal Kashiv Biosciences) building biosimilars portfolio through acquisition</t>
+          <t>Biosimilars &amp; Biologics: biosimilar patent litigation</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fire Breaks Out At Pfizer Facility In Andover</t>
+          <t>FDA Reduces Monitoring Time for First Two Tarlatamab Doses</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>andovermanews.com</t>
+          <t>Pharmacy Times</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://andovermanews.com/fire-breaks-out-at-pfizer-facility-in-andover/</t>
+          <t>https://www.pharmacytimes.com/view/fda-reduces-monitoring-time-for-first-two-tarlatamab-doses</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17-09-2026 13:50 UTC</t>
+          <t>17-09-2026 17:34 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>manufacturing event at a monitored company (Pfizer), potentially affecting biologic supply</t>
+          <t>FDA / Regulatory Actions: FDA decision for a biologic (monoclonal antibody)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
+          <t>Pfizer, BioNTech Secure Health Canada Authorization for Omicron XFG-Adapted COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
+          <t>https://www.marketscreener.com/news/pfizer-biontech-secure-health-canada-authorization-for-omicron-xfg-adapted-covid-19-vaccine-ce785bd3de8cf62c</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17-09-2026 13:41 UTC</t>
+          <t>17-09-2026 19:04 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>manufacturing approval for sterile injectable site, relevant to biologics/biosimilars supply chain</t>
+          <t>FDA / Regulatory Actions: approval of a biologic vaccine from a monitored company</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Celltrion captures Japan lead with Remsima biosimilar, eyes SC launch - CHOSUNBIZ</t>
+          <t>Phase 3 Pediatric EMPAVELI Data Published in Clinical Journal of the American Society of Nephrology Show Reduction in Proteinuria and Stabilized Kidney Function in Adolescents with C3G or Primary IC-MPGN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/17/EBUUYC3ILVC6THC2NCM5WFOSQU/</t>
+          <t>https://investors.biogen.com/news-releases/news-release-details/phase-3-pediatric-empaveli-data-published-clinical-journal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16-09-2026 23:56 UTC</t>
+          <t>17-09-2026 20:16 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>monitored company (Celltrion) biosimilar (Remsima, infliximab) achieves market leadership and plans SC launch in a key market; direct IBD competitor</t>
+          <t>Clinical Trials &amp; Pipeline News: clinical data for a biologic in immunology/autoimmune disease</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri Near $1 Billion Sales Mark</t>
+          <t>Dr Reddy's signs India distribution deal for Takeda's Qdenga dengue vaccine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/17/zymfentra-xcopri-near-1-billion-sales-mark</t>
+          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/indias-dr-reddys-inks-distribution-agreement-with-takeda-dengue-vaccine-india-2026-09-18/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16-09-2026 22:00 UTC</t>
+          <t>18-09-2026 03:41 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>monitored company (Celltrion) biologics revenue update (Zymfentra is SC infliximab, an IBD relevant biologic)</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition: distribution deal for a biologic</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Teva’s Lab-Made Antibody Shot for Celiac Shows Hopeful Results</t>
+          <t>Celltrion’s Remsima takes No. 1 spot in Japan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allergic Living</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.allergicliving.com/2026/09/16/tevas-lab-made-antibody-shot-for-celiac-shows-hopeful-results/</t>
+          <t>https://pulse.mk.co.kr/news/english/12156269</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-09-2026 22:36 UTC</t>
+          <t>18-09-2026 01:48 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>monitored company (Teva) clinical pipeline news for an autoimmune disease biologic (antibody)</t>
+          <t>Market Launches, Approvals &amp; Commercial Events: market performance of an IBD biosimilar</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -748,6 +748,286 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Prestige Biopharma</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Prestige Biopharma Obtains Marketing Authorization for 'Tuzuneu' in Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.asiae.co.kr/en/article/2026091809382068983</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>18-09-2026 00:38 UTC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Market Launches, Approvals &amp; Commercial Events: marketing authorization for a biosimilar</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/legal/litigation/astrazeneca-daiichi-breast-cancer-drug-cleared-nhs-use-england-2026-09-17/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17-09-2026 15:07 UTC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Market Launches, Approvals &amp; Commercial Events: regulatory approval of a biologic (monoclonal antibody)</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FDA Clears Phase 1b/2 Trial of CAR T-Cell Therapy C-CAR168 for Refractory Progressive Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NeurologyLive</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.neurologylive.com/view/fda-clears-c-car168-trial-refractory-progressive-multiple-sclerosis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>17-09-2026 19:55 UTC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Clinical Trials &amp; Pipeline News: trial for biologic in autoimmune disease, FDA action</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bloomberg Law News</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://news.bloomberglaw.com/health-law-and-business/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>17-09-2026 15:20 UTC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics: biosimilar patent litigation</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Japan approves under-the-skin Keytruda made with Alteogen enzyme</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Korea Biomedical Review</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33229</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>18-09-2026 03:33 UTC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics: biologic lifecycle management (new formulation)</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A decade leading retinal care, Eylea 8mg now lasts even longer and better, expert says</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Korea Biomedical Review</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33231</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>18-09-2026 03:47 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics: biologic lifecycle management (new strength)</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Single-Use Bioprocess Connectors Market Forecast to 2035: Cell and Gene Therapy Demand Drives 12-16% CAGR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/single-use-bioprocess-connectors-market-forecast-to-2035-cell-and-gene-therapy-demand-drives-12-16-cagr/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>17-09-2026 13:06 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity: market report for bioprocess manufacturing segment</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -775,7 +1055,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-09-2026 21:18:08</t>
+          <t>18-09-2026 13:30:13</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
+          <t>The Evolving Law of Enablement: Federal Circuit Decisions in Wyeth and Teva Form a “Yin and Yang” Framework</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>JD Supra</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
+          <t>https://www.jdsupra.com/legalnews/the-evolving-law-of-enablement-federal-5015742/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18-09-2026 05:36 UTC</t>
+          <t>17-09-2026 17:51 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: Sandoz biosimilar development deal</t>
+          <t>Patent litigation - general patent law relevant to biologics/biosimilars</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
+          <t>PhytoFoundry emerges from stealth with plant cell culture platform targeting high value bioactives</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>AgFunderNews</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
+          <t>https://agfundernews.com/phytofoundry-targets-cosmetics-with-plant-cell-culture-platform-shaped-by-past-lessons</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17-09-2026 12:54 UTC</t>
+          <t>17-09-2026 16:27 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: biosimilar patent litigation</t>
+          <t>Manufacturing, supply chain &amp; capacity - plant cell culture platform for bioactives</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FDA Reduces Monitoring Time for First Two Tarlatamab Doses</t>
+          <t>[Market Movers Analysis] MedicusPharma surges on September 17: Pfizer ADC collaboration and SkinJect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pharmacy Times</t>
+          <t>Bitget</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pharmacytimes.com/view/fda-reduces-monitoring-time-for-first-two-tarlatamab-doses</t>
+          <t>https://www.bitget.com/amp/news/detail/12560605843347</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17-09-2026 17:34 UTC</t>
+          <t>17-09-2026 21:59 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions: FDA decision for a biologic (monoclonal antibody)</t>
+          <t>Partnerships, deals, licensing &amp; acquisition - Pfizer ADC collaboration (biologics)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pfizer, BioNTech Secure Health Canada Authorization for Omicron XFG-Adapted COVID-19 Vaccine</t>
+          <t>Indian patent office drafts new pharma guidelines to tighten scrutiny</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/pfizer-biontech-secure-health-canada-authorization-for-omicron-xfg-adapted-covid-19-vaccine-ce785bd3de8cf62c</t>
+          <t>https://www.thepharmaletter.com/pharma-news/indian-patent-office-drafts-new-pharma-guidelines-to-tighten-scrutiny</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17-09-2026 19:04 UTC</t>
+          <t>18-09-2026 13:55 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions: approval of a biologic vaccine from a monitored company</t>
+          <t>FDA / regulatory actions - general patent policy relevant to biologics/biosimilars</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phase 3 Pediatric EMPAVELI Data Published in Clinical Journal of the American Society of Nephrology Show Reduction in Proteinuria and Stabilized Kidney Function in Adolescents with C3G or Primary IC-MPGN</t>
+          <t>WuXi XDC to Out-License Proprietary Payload-Linker Technology Platform to Ona Therapeutics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://investors.biogen.com/news-releases/news-release-details/phase-3-pediatric-empaveli-data-published-clinical-journal</t>
+          <t>https://www.contractpharma.com/breaking-news/wuxi-xdc-to-out-license-proprietary-payload-linker-technology-platform-to-ona-therapeutics/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17-09-2026 20:16 UTC</t>
+          <t>17-09-2026 20:01 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News: clinical data for a biologic in immunology/autoimmune disease</t>
+          <t>Partnerships, deals, licensing &amp; acquisition - biologic technology licensing (CDMO)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr Reddy's signs India distribution deal for Takeda's Qdenga dengue vaccine</t>
+          <t>Celltrion’s Remsima takes No. 1 spot in Japan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/indias-dr-reddys-inks-distribution-agreement-with-takeda-dengue-vaccine-india-2026-09-18/</t>
+          <t>https://pulse.mk.co.kr/news/all/12156269</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18-09-2026 03:41 UTC</t>
+          <t>18-09-2026 01:48 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition: distribution deal for a biologic</t>
+          <t>Market launches, approvals &amp; commercial events - Celltrion Remsima market performance</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celltrion’s Remsima takes No. 1 spot in Japan</t>
+          <t>Prestige Biopharma Obtains Marketing Authorization for 'Tuzuneu' in Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pulse.mk.co.kr/news/english/12156269</t>
+          <t>https://www.asiae.co.kr/en/article/stock-disclosure/2026091809382068983</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18-09-2026 01:48 UTC</t>
+          <t>18-09-2026 00:38 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events: market performance of an IBD biosimilar</t>
+          <t>Biosimilars &amp; biologics - Prestige Biopharma international biosimilar approval</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prestige Biopharma Obtains Marketing Authorization for 'Tuzuneu' in Trinidad and Tobago</t>
+          <t>FDA Clears Phase 1b/2 Trial of CAR T-Cell Therapy C-CAR168 for Refractory Progressive Multiple Sclerosis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>NeurologyLive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/2026091809382068983</t>
+          <t>https://www.neurologylive.com/view/fda-clears-c-car168-trial-refractory-progressive-multiple-sclerosis</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-09-2026 00:38 UTC</t>
+          <t>17-09-2026 19:55 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events: marketing authorization for a biosimilar</t>
+          <t>Clinical trials &amp; pipeline news - biologic (CAR-T) for autoimmune disease (MS)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/astrazeneca-daiichi-breast-cancer-drug-cleared-nhs-use-england-2026-09-17/</t>
+          <t>https://news.bloomberglaw.com/health-law-and-business/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17-09-2026 15:07 UTC</t>
+          <t>17-09-2026 15:20 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events: regulatory approval of a biologic (monoclonal antibody)</t>
+          <t>Biosimilars &amp; biologics - Simponi biosimilar patent litigation</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FDA Clears Phase 1b/2 Trial of CAR T-Cell Therapy C-CAR168 for Refractory Progressive Multiple Sclerosis</t>
+          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NeurologyLive</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.neurologylive.com/view/fda-clears-c-car168-trial-refractory-progressive-multiple-sclerosis</t>
+          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17-09-2026 19:55 UTC</t>
+          <t>18-09-2026 05:36 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News: trial for biologic in autoimmune disease, FDA action</t>
+          <t>Partnerships, deals, licensing &amp; acquisition - Sandoz to develop emicizumab biosimilar</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Polpharma Biologics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
+          <t>CHMP recommends EU approval of Roche’s Ocrevus for children and adolescents with relapsing multiple sclerosis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bloomberg Law News</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.bloomberglaw.com/health-law-and-business/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
+          <t>https://finance.yahoo.com/healthcare/articles/chmp-recommends-eu-approval-roche-104500076.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17-09-2026 15:20 UTC</t>
+          <t>18-09-2026 10:45 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: biosimilar patent litigation</t>
+          <t>FDA / regulatory actions - biologic approval recommendation for autoimmune disease (MS)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,32 +914,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Japan approves under-the-skin Keytruda made with Alteogen enzyme</t>
+          <t>CDMOs/CMOs: The Key Moves in 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>CHEManager</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33229</t>
+          <t>https://chemanager-online.com/en/news/cdmos-cmos-the-key-moves-in-2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18-09-2026 03:33 UTC</t>
+          <t>18-09-2026 05:00 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: biologic lifecycle management (new formulation)</t>
+          <t>Manufacturing, supply chain &amp; capacity - CDMO industry report</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -948,86 +948,6 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>A decade leading retinal care, Eylea 8mg now lasts even longer and better, expert says</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Korea Biomedical Review</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33231</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>18-09-2026 03:47 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Biosimilars &amp; Biologics: biologic lifecycle management (new strength)</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Single-Use Bioprocess Connectors Market Forecast to 2035: Cell and Gene Therapy Demand Drives 12-16% CAGR</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>IndexBox</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/single-use-bioprocess-connectors-market-forecast-to-2035-cell-and-gene-therapy-demand-drives-12-16-cagr/</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>17-09-2026 13:06 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: market report for bioprocess manufacturing segment</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -1055,7 +975,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-09-2026 13:30:13</t>
+          <t>18-09-2026 20:46:29</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Evolving Law of Enablement: Federal Circuit Decisions in Wyeth and Teva Form a “Yin and Yang” Framework</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JD Supra</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.jdsupra.com/legalnews/the-evolving-law-of-enablement-federal-5015742/</t>
+          <t>https://www.prnewswire.com/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883156.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17-09-2026 17:51 UTC</t>
+          <t>18-09-2026 10:16 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Patent litigation - general patent law relevant to biologics/biosimilars</t>
+          <t>biosimilars &amp; biologics partnership involving a monitored company</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PhytoFoundry emerges from stealth with plant cell culture platform targeting high value bioactives</t>
+          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AgFunderNews</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://agfundernews.com/phytofoundry-targets-cosmetics-with-plant-cell-culture-platform-shaped-by-past-lessons</t>
+          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17-09-2026 16:27 UTC</t>
+          <t>18-09-2026 10:30 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Manufacturing, supply chain &amp; capacity - plant cell culture platform for bioactives</t>
+          <t>biosimilars &amp; biologics market activity for a monitored company</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Market Movers Analysis] MedicusPharma surges on September 17: Pfizer ADC collaboration and SkinJect</t>
+          <t>CHMP's September meeting highlights</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bitget</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bitget.com/amp/news/detail/12560605843347</t>
+          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17-09-2026 21:59 UTC</t>
+          <t>18-09-2026 16:46 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Partnerships, deals, licensing &amp; acquisition - Pfizer ADC collaboration (biologics)</t>
+          <t>FDA / regulatory action: CHMP opinion for a biologic</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Indian patent office drafts new pharma guidelines to tighten scrutiny</t>
+          <t>Rheumatoid Arthritis Pipeline Insight 2026: 75+ Companies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/indian-patent-office-drafts-new-pharma-guidelines-to-tighten-scrutiny</t>
+          <t>https://www.openpr.com/news/4636200/rheumatoid-arthritis-pipeline-insight-2026-75-companies</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-09-2026 13:55 UTC</t>
+          <t>18-09-2026 20:30 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FDA / regulatory actions - general patent policy relevant to biologics/biosimilars</t>
+          <t>clinical trials &amp; pipeline news: pipeline insight for autoimmune disease (rheumatoid arthritis)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WuXi XDC to Out-License Proprietary Payload-Linker Technology Platform to Ona Therapeutics</t>
+          <t>The Drugs and Devices Have Been on the Market for Years. But FDA-Ordered Studies Still Aren’t Done.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>KFF Health News</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/wuxi-xdc-to-out-license-proprietary-payload-linker-technology-platform-to-ona-therapeutics/</t>
+          <t>https://kffhealthnews.org/health-industry/fda-approval-drugs-medical-devices-postmarket-studies-safety-delays-amgen-tavneos/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17-09-2026 20:01 UTC</t>
+          <t>18-09-2026 09:03 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partnerships, deals, licensing &amp; acquisition - biologic technology licensing (CDMO)</t>
+          <t>FDA / regulatory actions: FDA-ordered post-marketing studies for a monitored company</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Celltrion’s Remsima takes No. 1 spot in Japan</t>
+          <t>Sun Pharma to acquire US-based Organon in nearly $11.75 billion deal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>DD News</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pulse.mk.co.kr/news/all/12156269</t>
+          <t>https://ddnews.gov.in/en/sun-pharma-to-acquire-us-based-organon-in-nearly-11-75-billion-deal/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18-09-2026 01:48 UTC</t>
+          <t>18-09-2026 18:35 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Market launches, approvals &amp; commercial events - Celltrion Remsima market performance</t>
+          <t>partnerships, deals, licensing &amp; acquisition: acquisition of a biosimilar-active company</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prestige Biopharma Obtains Marketing Authorization for 'Tuzuneu' in Trinidad and Tobago</t>
+          <t>From Padcev to PF-08634404: Pfizer's Oncology Growth Push</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>qz.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/stock-disclosure/2026091809382068983</t>
+          <t>https://qz.com/from-padcev-to-pf-08634404-pfizer-s-oncology-growth-push</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18-09-2026 00:38 UTC</t>
+          <t>18-09-2026 14:11 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics - Prestige Biopharma international biosimilar approval</t>
+          <t>clinical trials &amp; pipeline news: oncology biologic pipeline news for a monitored company</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FDA Clears Phase 1b/2 Trial of CAR T-Cell Therapy C-CAR168 for Refractory Progressive Multiple Sclerosis</t>
+          <t>EPO revokes key Moderna patent for mRNA vaccines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NeurologyLive</t>
+          <t>JUVE Patent</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.neurologylive.com/view/fda-clears-c-car168-trial-refractory-progressive-multiple-sclerosis</t>
+          <t>https://www.juve-patent.com/people-and-business/epo-revokes-key-moderna-patent-for-mrna-vaccines/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17-09-2026 19:55 UTC</t>
+          <t>18-09-2026 13:37 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news - biologic (CAR-T) for autoimmune disease (MS)</t>
+          <t>biosimilars &amp; biologics patent litigation/dispute for a biologic technology</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
+          <t>Japan approves LEQEMBI Pen for at-home treatment of early Alzheimer’s disease</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bloomberg Law News</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.bloomberglaw.com/health-law-and-business/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
+          <t>https://www.biospectrumasia.com/news/26/28399/japan-approves-leqembi-pen-for-at-home-treatment-of-early-alzheimers-disease.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17-09-2026 15:20 UTC</t>
+          <t>18-09-2026 15:50 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics - Simponi biosimilar patent litigation</t>
+          <t>market launches, approvals &amp; commercial events: approval of a biologic for autoimmune disease</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
+          <t>Dr. Reddy's, Takeda Pharma ink pact to distribute India's first dengue vaccine QDENGA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
+          <t>https://www.thehindu.com/business/Industry/dr-reddys-takeda-pharma-ink-pact-to-distribute-indias-first-dengue-vaccine-qdenga/article71479880.ece</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18-09-2026 05:36 UTC</t>
+          <t>18-09-2026 09:22 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Partnerships, deals, licensing &amp; acquisition - Sandoz to develop emicizumab biosimilar</t>
+          <t>partnerships, deals, licensing &amp; acquisition: licensing deal involving a Takeda product</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Polpharma Biologics</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHMP recommends EU approval of Roche’s Ocrevus for children and adolescents with relapsing multiple sclerosis</t>
+          <t>Shilpa Medicare Unit VII inspection ends with one procedural observation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/chmp-recommends-eu-approval-roche-104500076.html</t>
+          <t>https://www.business-standard.com/amp/markets/capital-market-news/shilpa-medicare-unit-vii-inspection-ends-with-one-procedural-observation-126091900148_1.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18-09-2026 10:45 UTC</t>
+          <t>19-09-2026 04:01 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FDA / regulatory actions - biologic approval recommendation for autoimmune disease (MS)</t>
+          <t>manufacturing, supply chain &amp; capacity: FDA inspection at monitored company's biologics manufacturing site</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,45 +907,165 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CDMOs/CMOs: The Key Moves in 2026</t>
+          <t>South Korea Cuts Prices on 80 Reimbursed Drugs by Average 4.6% Amid Prescription Surge, Saving ₩33.9 Billion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CHEManager</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://chemanager-online.com/en/news/cdmos-cmos-the-key-moves-in-2026</t>
+          <t>https://finance.biggo.com/news/77cf763b-c390-445d-9dca-6236ddd6902e</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18-09-2026 05:00 UTC</t>
+          <t>18-09-2026 09:35 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Manufacturing, supply chain &amp; capacity - CDMO industry report</t>
+          <t>biosimilars &amp; biologics: drug pricing policy affecting biosimilar market landscape</t>
         </is>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Enhertu® Recommended for Approval in the EU by CHMP as Adjuvant Treatment for Patients with Residual Disease After Neoadjuvant Treatment for HER2 Positive Early Breast Cancer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260917458618/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-as-Adjuvant-Treatment-for-Patients-with-Residual-Disease-After-Neoadjuvant-Treatment-for-HER2-Positive-Early-Breast-Cancer</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>18-09-2026 12:00 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>market launches, approvals &amp; commercial events: EU approval recommendation for a biologic involving a monitored company</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FDA approves first gene therapy for pediatric patients with Sanfilippo syndrome type A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PharmaLive</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.pharmalive.com/fda-approves-first-gene-therapy-for-pediatric-patients-with-sanfilippo-syndrome-type-a/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>18-09-2026 13:21 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FDA / regulatory actions: FDA approval of a gene therapy (advanced biologic therapy)</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Polpharma Biologics</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CHMP recommends EU approval of Roche’s Ocrevus for children and adolescents with relapsing multiple sclerosis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/chmp-recommends-eu-approval-roche-104500076.html</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>18-09-2026 10:45 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FDA / regulatory actions: CHMP recommendation for a biologic for autoimmune disease</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -975,7 +1095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-09-2026 20:46:29</t>
+          <t>19-09-2026 13:21:58</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
+          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Pharmacy Business</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883156.html</t>
+          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18-09-2026 10:16 UTC</t>
+          <t>19-09-2026 12:15 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>biosimilars &amp; biologics partnership involving a monitored company</t>
+          <t>biosimilar partnership and deal with monitored company Sandoz</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
+          <t>CHMP's September meeting highlights</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
+          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18-09-2026 10:30 UTC</t>
+          <t>18-09-2026 16:46 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>biosimilars &amp; biologics market activity for a monitored company</t>
+          <t>FDA / regulatory action for a biologic</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHMP's September meeting highlights</t>
+          <t>Rheumatoid Arthritis Pipeline Insight 2026: 75+ Companies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AllSci</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
+          <t>https://www.openpr.com/news/4636200/rheumatoid-arthritis-pipeline-insight-2026-75-companies</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18-09-2026 16:46 UTC</t>
+          <t>18-09-2026 20:30 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FDA / regulatory action: CHMP opinion for a biologic</t>
+          <t>clinical trials &amp; pipeline news in relevant therapeutic area (rheumatology/autoimmune)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rheumatoid Arthritis Pipeline Insight 2026: 75+ Companies</t>
+          <t>All 50 States Join Medicaid Drug Pricing Program: Trump</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>NTD News</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4636200/rheumatoid-arthritis-pipeline-insight-2026-75-companies</t>
+          <t>https://www.ntd.com/all-50-states-join-medicaid-drug-pricing-program-trump_1173670.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-09-2026 20:30 UTC</t>
+          <t>18-09-2026 21:17 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>clinical trials &amp; pipeline news: pipeline insight for autoimmune disease (rheumatoid arthritis)</t>
+          <t>FDA / regulatory action and market access news affecting drug pricing</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -639,27 +639,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Drugs and Devices Have Been on the Market for Years. But FDA-Ordered Studies Still Aren’t Done.</t>
+          <t>AstraZeneca, Amgen TEZSPIRE meets Phase III EoE trial endpoints</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KFF Health News</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://kffhealthnews.org/health-industry/fda-approval-drugs-medical-devices-postmarket-studies-safety-delays-amgen-tavneos/</t>
+          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-amgen-tezspire-meets-phase-iii-eoe-trial-endpoints/49376112</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18-09-2026 09:03 UTC</t>
+          <t>19-09-2026 01:34 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FDA / regulatory actions: FDA-ordered post-marketing studies for a monitored company</t>
+          <t>clinical trial results for a biologic from a monitored company in immunology</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,7 +667,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>partnerships, deals, licensing &amp; acquisition: acquisition of a biosimilar-active company</t>
+          <t>acquisition of a monitored company active in biosimilars</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -719,27 +719,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>From Padcev to PF-08634404: Pfizer's Oncology Growth Push</t>
+          <t>Secret contracts reveal undisclosed terms in Trump’s drug-pricing deals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>qz.com</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://qz.com/from-padcev-to-pf-08634404-pfizer-s-oncology-growth-push</t>
+          <t>https://www.washingtonpost.com/politics/2026/09/19/secret-contracts-reveal-undisclosed-terms-trumps-drug-pricing-deals/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18-09-2026 14:11 UTC</t>
+          <t>19-09-2026 14:32 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>clinical trials &amp; pipeline news: oncology biologic pipeline news for a monitored company</t>
+          <t>FDA / regulatory action and market access news affecting drug pricing</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,7 +747,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -759,27 +759,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EPO revokes key Moderna patent for mRNA vaccines</t>
+          <t>ARDD 2026 brings global pharma, FDA leaders and longevity science pioneers to Harvard October 1–3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JUVE Patent</t>
+          <t>EurekAlert!</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.juve-patent.com/people-and-business/epo-revokes-key-moderna-patent-for-mrna-vaccines/</t>
+          <t>https://www.eurekalert.org/news-releases/1144599</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-09-2026 13:37 UTC</t>
+          <t>18-09-2026 17:31 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>biosimilars &amp; biologics patent litigation/dispute for a biologic technology</t>
+          <t>industry meeting involving FDA leaders and pharma</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -819,7 +819,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>market launches, approvals &amp; commercial events: approval of a biologic for autoimmune disease</t>
+          <t>approval of a biologic from a monitored company</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -839,27 +839,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr. Reddy's, Takeda Pharma ink pact to distribute India's first dengue vaccine QDENGA</t>
+          <t>Dr Reddy's to sell Takeda's German-made dengue vaccine, Takeda-Biological E manufacturing pact targets national immunisation programmes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/dr-reddys-takeda-pharma-ink-pact-to-distribute-indias-first-dengue-vaccine-qdenga/article71479880.ece</t>
+          <t>https://www.fortuneindia.com/business-news/dr-reddys-to-sell-takedas-german-made-dengue-vaccine-takeda-biological-e-manufacturing-pact-targets-national-immunisation-programmes/160079</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18-09-2026 09:22 UTC</t>
+          <t>18-09-2026 15:39 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>partnerships, deals, licensing &amp; acquisition: licensing deal involving a Takeda product</t>
+          <t>partnership/licensing deal involving monitored company Dr. Reddy's and Takeda (Entyvio manufacturer), including manufacturing aspect</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Unit VII inspection ends with one procedural observation</t>
+          <t>Aurobindo Pharma Gets US FDA Approval for Asthma Inhaler</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Indian Practitioner</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/shilpa-medicare-unit-vii-inspection-ends-with-one-procedural-observation-126091900148_1.html</t>
+          <t>https://theindianpractitioner.com/aurobindo-pharma-gets-us-fda-approval-for-asthma-inhaler/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19-09-2026 04:01 UTC</t>
+          <t>19-09-2026 12:28 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>manufacturing, supply chain &amp; capacity: FDA inspection at monitored company's biologics manufacturing site</t>
+          <t>FDA approval for an immunology drug from a monitored company</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>South Korea Cuts Prices on 80 Reimbursed Drugs by Average 4.6% Amid Prescription Surge, Saving ₩33.9 Billion</t>
+          <t>Shilpa Medicare Unit VII inspection ends with one procedural observation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>business-standard.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/77cf763b-c390-445d-9dca-6236ddd6902e</t>
+          <t>https://www.business-standard.com/amp/markets/capital-market-news/shilpa-medicare-unit-vii-inspection-ends-with-one-procedural-observation-126091900148_1.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18-09-2026 09:35 UTC</t>
+          <t>19-09-2026 04:01 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>biosimilars &amp; biologics: drug pricing policy affecting biosimilar market landscape</t>
+          <t>FDA inspection observation at a monitored company's biologics manufacturing unit</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Enhertu® Recommended for Approval in the EU by CHMP as Adjuvant Treatment for Patients with Residual Disease After Neoadjuvant Treatment for HER2 Positive Early Breast Cancer</t>
+          <t>Sharp Expands Autoinjector and Pen Assembly Capacity in U.S. and EU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260917458618/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-as-Adjuvant-Treatment-for-Patients-with-Residual-Disease-After-Neoadjuvant-Treatment-for-HER2-Positive-Early-Breast-Cancer</t>
+          <t>https://www.contractpharma.com/live_from_shows/sharp-expands-autoinjector-and-pen-assembly-capacity-in-u-s-and-eu/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18-09-2026 12:00 UTC</t>
+          <t>19-09-2026 08:08 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>market launches, approvals &amp; commercial events: EU approval recommendation for a biologic involving a monitored company</t>
+          <t>manufacturing capacity expansion for devices used with biologics/biosimilars</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -994,32 +994,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FDA approves first gene therapy for pediatric patients with Sanfilippo syndrome type A</t>
+          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PharmaLive</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pharmalive.com/fda-approves-first-gene-therapy-for-pediatric-patients-with-sanfilippo-syndrome-type-a/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18-09-2026 13:21 UTC</t>
+          <t>18-09-2026 16:40 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FDA / regulatory actions: FDA approval of a gene therapy (advanced biologic therapy)</t>
+          <t>market launch/approval of a biologic from a monitored company (Enhertu)</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1034,38 +1034,238 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Polpharma Biologics</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHMP recommends EU approval of Roche’s Ocrevus for children and adolescents with relapsing multiple sclerosis</t>
+          <t>Japan Approves T-DXd Combo and Dato-DXd for First-Line Metastatic Breast Cancer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>CancerNetwork</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/chmp-recommends-eu-approval-roche-104500076.html</t>
+          <t>https://www.cancernetwork.com/view/japan-approves-t-dxd-combo-and-dato-dxd-for-first-line-metastatic-breast-cancer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18-09-2026 10:45 UTC</t>
+          <t>18-09-2026 19:11 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FDA / regulatory actions: CHMP recommendation for a biologic for autoimmune disease</t>
+          <t>market launch/approval of biologics from a monitored company</t>
         </is>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AstraZeneca halts one lung cancer trial after mixed Phase 3 results</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-halts-one-lung-cancer-trial-mixed-phase-3-results/48530243</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>19-09-2026 02:26 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>clinical trial news for a biologic, involving a monitored company via partnership</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Enhertu receives EU recommendation for HER2-positive breast cancer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>grafa.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://grafa.com/en/news/united-states/enhertu-eu-recommendation-her2-positive-breast-cancer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>18-09-2026 16:50 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FDA / regulatory action for a biologic from a monitored company</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ocrevus for Paediatric MS Gets CHMP EU Backing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Voice of Healthcare</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://vohnetwork.com/news/pharma/chmp-backs-roche-s-ocrevus-for-paediatric-relapsing-multiple-sclerosis</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>19-09-2026 06:40 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FDA / regulatory action for a biologic in an autoimmune disease</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>bioprocessonline.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>19-09-2026 12:43 UTC</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>manufacturing/quality news for a biologics manufacturer (monitored company)</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Antibody Contract Manufacturing Market to Reach USD 44.96 Billion by 2034, Growing at a CAGR of 9.96%</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4636095/antibody-contract-manufacturing-market-to-reach-usd-44-96</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>18-09-2026 17:18 UTC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>market news for antibody contract manufacturing relevant to a monitored company</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1095,7 +1295,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19-09-2026 13:21:58</t>
+          <t>19-09-2026 20:17:16</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,12 +494,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19-09-2026 12:15 UTC</t>
+          <t>19-09-2026 12:13 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>biosimilar partnership and deal with monitored company Sandoz</t>
+          <t>Biosimilars &amp; Biologics; Partnerships, Deals, Licensing &amp; Acquisition for a monitored company (Sandoz)</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHMP's September meeting highlights</t>
+          <t>Pfizer to share higher overseas drug revenue with US health agency</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AllSci</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
+          <t>https://www.business-standard.com/world-news/pfizer-to-share-higher-overseas-drug-revenue-with-us-health-agency-126092000066_1.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18-09-2026 16:46 UTC</t>
+          <t>20-09-2026 02:34 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FDA / regulatory action for a biologic</t>
+          <t>Market Launches, Approvals &amp; Commercial Events for a monitored company (Pfizer) related to drug revenue/pricing deals</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rheumatoid Arthritis Pipeline Insight 2026: 75+ Companies</t>
+          <t>Shilpa Medicare Hyderabad Unit Gets 1 Procedural Observation in USFDA Inspection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4636200/rheumatoid-arthritis-pipeline-insight-2026-75-companies</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/shilpa-medicare-hyderabad-unit-gets-1-procedural-observation-in-usfda-inspection-179592</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18-09-2026 20:30 UTC</t>
+          <t>19-09-2026 14:06 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>clinical trials &amp; pipeline news in relevant therapeutic area (rheumatology/autoimmune)</t>
+          <t>FDA / Regulatory Actions for a monitored company's manufacturing site (Shilpa Biologicals)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>All 50 States Join Medicaid Drug Pricing Program: Trump</t>
+          <t>KRX Healthcare shifts to large caps as Korea favors new-tech biomed - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NTD News</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.ntd.com/all-50-states-join-medicaid-drug-pricing-program-trump_1173670.html</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/20/UYEIW47GOJA7XDOKS7M4MLXK6U/?outputType=amp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-09-2026 21:17 UTC</t>
+          <t>19-09-2026 23:00 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FDA / regulatory action and market access news affecting drug pricing</t>
+          <t>Monitored company (Celltrion) and market trends in biomed</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AstraZeneca, Amgen TEZSPIRE meets Phase III EoE trial endpoints</t>
+          <t>APAC Healthcare Weekly (Sept 20) –Sino Bio, Impact Therapeutics, Takeda, Daiichi Sankyo, SK Biopharm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Smartkarma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-amgen-tezspire-meets-phase-iii-eoe-trial-endpoints/49376112</t>
+          <t>https://www.smartkarma.com/insights/apac-healthcare-weekly-sept-20-sino-bio-impact-therapeutics-takeda-daiichi-sankyo-sk-biopharm</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19-09-2026 01:34 UTC</t>
+          <t>20-09-2026 02:03 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>clinical trial results for a biologic from a monitored company in immunology</t>
+          <t>Vedolizumab / Entyvio primary signal (Takeda mention) in a healthcare summary</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sun Pharma to acquire US-based Organon in nearly $11.75 billion deal</t>
+          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DD News</t>
+          <t>Bioprocess Online</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/sun-pharma-to-acquire-us-based-organon-in-nearly-11-75-billion-deal/</t>
+          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18-09-2026 18:35 UTC</t>
+          <t>20-09-2026 00:43 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>acquisition of a monitored company active in biosimilars</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity for a monitored company (Samsung Biologics)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secret contracts reveal undisclosed terms in Trump’s drug-pricing deals</t>
+          <t>Samsung Biologics labor talks seek fall deal as Korea mediator steps in - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.washingtonpost.com/politics/2026/09/19/secret-contracts-reveal-undisclosed-terms-trumps-drug-pricing-deals/</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/20/ETB7FNLIN5CQNDK5CEXKTIF4MU/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19-09-2026 14:32 UTC</t>
+          <t>19-09-2026 23:21 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FDA / regulatory action and market access news affecting drug pricing</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity (labor talks potentially impacting operations) for a monitored company (Samsung Biologics)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -748,526 +748,6 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Pfizer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ARDD 2026 brings global pharma, FDA leaders and longevity science pioneers to Harvard October 1–3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>EurekAlert!</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.eurekalert.org/news-releases/1144599</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>18-09-2026 17:31 UTC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>industry meeting involving FDA leaders and pharma</t>
-        </is>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Biogen</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Japan approves LEQEMBI Pen for at-home treatment of early Alzheimer’s disease</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>BioSpectrum Asia</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.biospectrumasia.com/news/26/28399/japan-approves-leqembi-pen-for-at-home-treatment-of-early-alzheimers-disease.html</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>18-09-2026 15:50 UTC</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>approval of a biologic from a monitored company</t>
-        </is>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dr Reddy's to sell Takeda's German-made dengue vaccine, Takeda-Biological E manufacturing pact targets national immunisation programmes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Fortune India</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://www.fortuneindia.com/business-news/dr-reddys-to-sell-takedas-german-made-dengue-vaccine-takeda-biological-e-manufacturing-pact-targets-national-immunisation-programmes/160079</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>18-09-2026 15:39 UTC</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>partnership/licensing deal involving monitored company Dr. Reddy's and Takeda (Entyvio manufacturer), including manufacturing aspect</t>
-        </is>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma Gets US FDA Approval for Asthma Inhaler</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>The Indian Practitioner</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://theindianpractitioner.com/aurobindo-pharma-gets-us-fda-approval-for-asthma-inhaler/</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>19-09-2026 12:28 UTC</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>FDA approval for an immunology drug from a monitored company</t>
-        </is>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Shilpa Biologicals</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Shilpa Medicare Unit VII inspection ends with one procedural observation</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>business-standard.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/shilpa-medicare-unit-vii-inspection-ends-with-one-procedural-observation-126091900148_1.html</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>19-09-2026 04:01 UTC</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>FDA inspection observation at a monitored company's biologics manufacturing unit</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Shilpa Biologicals</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Sharp Expands Autoinjector and Pen Assembly Capacity in U.S. and EU</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Contract Pharma</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.contractpharma.com/live_from_shows/sharp-expands-autoinjector-and-pen-assembly-capacity-in-u-s-and-eu/</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>19-09-2026 08:08 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>manufacturing capacity expansion for devices used with biologics/biosimilars</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Medical Dialogues</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>18-09-2026 16:40 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>market launch/approval of a biologic from a monitored company (Enhertu)</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Japan Approves T-DXd Combo and Dato-DXd for First-Line Metastatic Breast Cancer</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CancerNetwork</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.cancernetwork.com/view/japan-approves-t-dxd-combo-and-dato-dxd-for-first-line-metastatic-breast-cancer</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>18-09-2026 19:11 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>market launch/approval of biologics from a monitored company</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AstraZeneca halts one lung cancer trial after mixed Phase 3 results</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-halts-one-lung-cancer-trial-mixed-phase-3-results/48530243</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>19-09-2026 02:26 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>clinical trial news for a biologic, involving a monitored company via partnership</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Enhertu receives EU recommendation for HER2-positive breast cancer</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>grafa.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://grafa.com/en/news/united-states/enhertu-eu-recommendation-her2-positive-breast-cancer</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>18-09-2026 16:50 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>FDA / regulatory action for a biologic from a monitored company</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ocrevus for Paediatric MS Gets CHMP EU Backing</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Voice of Healthcare</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://vohnetwork.com/news/pharma/chmp-backs-roche-s-ocrevus-for-paediatric-relapsing-multiple-sclerosis</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>19-09-2026 06:40 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>FDA / regulatory action for a biologic in an autoimmune disease</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>bioprocessonline.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>19-09-2026 12:43 UTC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>manufacturing/quality news for a biologics manufacturer (monitored company)</t>
-        </is>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Antibody Contract Manufacturing Market to Reach USD 44.96 Billion by 2034, Growing at a CAGR of 9.96%</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.openpr.com/news/4636095/antibody-contract-manufacturing-market-to-reach-usd-44-96</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>18-09-2026 17:18 UTC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>market news for antibody contract manufacturing relevant to a monitored company</t>
-        </is>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1295,7 +775,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19-09-2026 20:17:16</t>
+          <t>20-09-2026 13:46:33</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
+          <t>Liver Injury FDA Warning for Tavneos Patients</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pharmacy Business</t>
+          <t>Pharmacy Practice News</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
+          <t>https://www.pharmacypracticenews.com/Online-First/GI-Disorders/Article/09-26/Liver-Injury-FDA-Warning-for-Tavneos-Patients/81461</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19-09-2026 12:13 UTC</t>
+          <t>20-09-2026 06:47 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics; Partnerships, Deals, Licensing &amp; Acquisition for a monitored company (Sandoz)</t>
+          <t>Monitored company (Amgen) product with FDA regulatory action</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pfizer to share higher overseas drug revenue with US health agency</t>
+          <t>Fake drugs: Karnataka cancels 16 licenses, suspends 8 including that of Pfizer depot</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/world-news/pfizer-to-share-higher-overseas-drug-revenue-with-us-health-agency-126092000066_1.html</t>
+          <t>https://m.economictimes.com/news/india/fake-drugs-karnataka-cancels-16-licenses-suspends-8-including-that-of-pfizer-depot/articleshow/134369786.cms</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20-09-2026 02:34 UTC</t>
+          <t>20-09-2026 13:56 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events for a monitored company (Pfizer) related to drug revenue/pricing deals</t>
+          <t>Monitored company (Pfizer) supply chain/quality issue</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Hyderabad Unit Gets 1 Procedural Observation in USFDA Inspection</t>
+          <t>Pfizer to Share Revenue With HHS in Deal on Overseas Drug Prices</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Bloomberg.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/shilpa-medicare-hyderabad-unit-gets-1-procedural-observation-in-usfda-inspection-179592</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-19/pfizer-to-share-revenue-with-hhs-in-deal-on-overseas-drug-prices</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19-09-2026 14:06 UTC</t>
+          <t>19-09-2026 21:12 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions for a monitored company's manufacturing site (Shilpa Biologicals)</t>
+          <t>Monitored company (Pfizer) commercial event &amp; drug pricing</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KRX Healthcare shifts to large caps as Korea favors new-tech biomed - CHOSUNBIZ</t>
+          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>bioprocessonline.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/20/UYEIW47GOJA7XDOKS7M4MLXK6U/?outputType=amp</t>
+          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19-09-2026 23:00 UTC</t>
+          <t>20-09-2026 00:43 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company (Celltrion) and market trends in biomed</t>
+          <t>Monitored company (Samsung Biologics) manufacturing quality improvement</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,118 +634,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>APAC Healthcare Weekly (Sept 20) –Sino Bio, Impact Therapeutics, Takeda, Daiichi Sankyo, SK Biopharm</t>
+          <t>Samsung Biologics labor talks seek fall deal as Korea mediator steps in - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Smartkarma</t>
+          <t>biz.chosun.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.smartkarma.com/insights/apac-healthcare-weekly-sept-20-sino-bio-impact-therapeutics-takeda-daiichi-sankyo-sk-biopharm</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/20/ETB7FNLIN5CQNDK5CEXKTIF4MU/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20-09-2026 02:03 UTC</t>
+          <t>19-09-2026 23:21 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedolizumab / Entyvio primary signal (Takeda mention) in a healthcare summary</t>
+          <t>Monitored company (Samsung Biologics) labor relations affecting operations</t>
         </is>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bioprocess Online</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>20-09-2026 00:43 UTC</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity for a monitored company (Samsung Biologics)</t>
-        </is>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Samsung Biologics labor talks seek fall deal as Korea mediator steps in - CHOSUNBIZ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/20/ETB7FNLIN5CQNDK5CEXKTIF4MU/</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>19-09-2026 23:21 UTC</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (labor talks potentially impacting operations) for a monitored company (Samsung Biologics)</t>
-        </is>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>Collaboration</t>
         </is>
@@ -775,7 +695,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20-09-2026 13:46:33</t>
+          <t>20-09-2026 20:23:52</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Liver Injury FDA Warning for Tavneos Patients</t>
+          <t>Sandoz and mAbxience agree on emicizumab biosimilar partnership</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pharmacy Practice News</t>
+          <t>Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pharmacypracticenews.com/Online-First/GI-Disorders/Article/09-26/Liver-Injury-FDA-Warning-for-Tavneos-Patients/81461</t>
+          <t>https://www.pharmaceutical-technology.com/news/sandoz-mabxience-emicizumab-biosimilar/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20-09-2026 06:47 UTC</t>
+          <t>21-09-2026 07:43 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company (Amgen) product with FDA regulatory action</t>
+          <t>Biosimilars &amp; biologics partnership involving monitored company Sandoz</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fake drugs: Karnataka cancels 16 licenses, suspends 8 including that of Pfizer depot</t>
+          <t>Class A Dig — Organon/Sun Pharma premature-close (May ACQ deleted; early-2027 expected)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>app.dealroom.co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/fake-drugs-karnataka-cancels-16-licenses-suspends-8-including-that-of-pfizer-depot/articleshow/134369786.cms</t>
+          <t>https://app.dealroom.co/news/note/class-a-dig-organon-sun-pharma-premature-close-may-acq-deleted-early-2027-expected</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20-09-2026 13:56 UTC</t>
+          <t>20-09-2026 15:45 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company (Pfizer) supply chain/quality issue</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition involving monitored company Organon</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pfizer to Share Revenue With HHS in Deal on Overseas Drug Prices</t>
+          <t>Karnataka FSDA cancels 16 pharmacy licences, suspends 8, including Pfizer depot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-19/pfizer-to-share-revenue-with-hhs-in-deal-on-overseas-drug-prices</t>
+          <t>https://www.thehindu.com/news/cities/bangalore/fda-cancels-16-pharmacy-licences-suspends-8-including-pfizer-depot/article71488486.ece</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19-09-2026 21:12 UTC</t>
+          <t>20-09-2026 15:11 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company (Pfizer) commercial event &amp; drug pricing</t>
+          <t>FDA regulatory action (licence suspension) involving monitored company Pfizer</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
+          <t>Biocon Pertuzumab Receives First Positive EMA CHMP Recommendation Under Tailored Clinical Method</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bioprocessonline.com</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
+          <t>https://www.sahi.com/news/biocon-pertuzumab-receives-first-positive-ema-chmp-recommendation-under-tailored-clinical-method</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20-09-2026 00:43 UTC</t>
+          <t>21-09-2026 04:16 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company (Samsung Biologics) manufacturing quality improvement</t>
+          <t>Biosimilars &amp; biologics regulatory approval (EMA CHMP recommendation for biosimilar Pertuzumab) for monitored company Biocon</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samsung Biologics labor talks seek fall deal as Korea mediator steps in - CHOSUNBIZ</t>
+          <t>Celltrion Wins EMA Approval to Modify Phase 3 Trial for Darzalex Biosimilar CT-P44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>biz.chosun.com</t>
+          <t>tipranks.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/20/ETB7FNLIN5CQNDK5CEXKTIF4MU/</t>
+          <t>https://www.tipranks.com/news/company-announcements/celltrion-wins-ema-approval-to-modify-phase-3-trial-for-darzalex-biosimilar-ct-p44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19-09-2026 23:21 UTC</t>
+          <t>21-09-2026 03:25 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company (Samsung Biologics) labor relations affecting operations</t>
+          <t>Biosimilars &amp; biologics regulatory approval (EMA for biosimilar clinical trial) for monitored company Celltrion</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,7 +667,87 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo, AstraZeneca’s Enhertu Wins EU Panel Backing for Early Breast Cancer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>biopharmaapac.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://biopharmaapac.com/news/86/8452/daiichi-sankyo-astrazenecas-enhertu-wins-eu-panel-backing-for-early-breast-cancer.html</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>21-09-2026 01:18 UTC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Biologics regulatory approval (EU panel backing for Enhertu, an antibody-drug conjugate) involving monitored company Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Medincell: Teva unveils new data on its olanzapine, FDA decision expected end of 2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Idéal Investisseur</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.ideal-investisseur.fr/en/stock-news/medincell-teva-unveils-new-data-on-its-olanzapine-fda-decision-expected-end-of-2026/25427.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21-09-2026 06:34 UTC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FDA regulatory action (decision expected) for monitored company Teva</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -695,7 +775,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20-09-2026 20:23:52</t>
+          <t>21-09-2026 14:03:58</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,22 +484,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pharmaceutical Technology</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-technology.com/news/sandoz-mabxience-emicizumab-biosimilar/</t>
+          <t>https://finance.yahoo.com/healthcare/articles/sandoz-mabxience-agree-emicizumab-biosimilar-083853595.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21-09-2026 07:43 UTC</t>
+          <t>21-09-2026 08:38 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics partnership involving monitored company Sandoz</t>
+          <t>biosimilar partnership for monitored company</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Class A Dig — Organon/Sun Pharma premature-close (May ACQ deleted; early-2027 expected)</t>
+          <t>Eight Names, One Drug: Why Adalimumab Biosimilars Are Creating Real Confusion at the Counter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>app.dealroom.co</t>
+          <t>Pharmacy Times</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://app.dealroom.co/news/note/class-a-dig-organon-sun-pharma-premature-close-may-acq-deleted-early-2027-expected</t>
+          <t>https://www.pharmacytimes.com/view/eight-names-one-drug-why-adalimumab-biosimilars-are-creating-real-confusion-at-the-counter</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20-09-2026 15:45 UTC</t>
+          <t>21-09-2026 16:58 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition involving monitored company Organon</t>
+          <t>adalimumab biosimilar market dynamics for monitored company</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Karnataka FSDA cancels 16 pharmacy licences, suspends 8, including Pfizer depot</t>
+          <t>Pfizer depot suspended after Bengaluru fake drug bust; 16 licences cancelled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/bangalore/fda-cancels-16-pharmacy-licences-suspends-8-including-pfizer-depot/article71488486.ece</t>
+          <t>https://indianexpress.com/article/cities/bangalore/bengaluru-pfizer-depot-suspended-fake-drug-bust-16-licences-cancelled-10887193/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20-09-2026 15:11 UTC</t>
+          <t>21-09-2026 07:57 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FDA regulatory action (licence suspension) involving monitored company Pfizer</t>
+          <t>manufacturing/supply chain issue for monitored company</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Biocon Pertuzumab Receives First Positive EMA CHMP Recommendation Under Tailored Clinical Method</t>
+          <t>Pfizer, Lilly 'most favored nation' deals to give US share of revenue from raised foreign prices</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/biocon-pertuzumab-receives-first-positive-ema-chmp-recommendation-under-tailored-clinical-method</t>
+          <t>https://endpoints.news/pfizer-lilly-most-favored-nation-deals-to-give-us-share-of-raised-foreign-prices/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21-09-2026 04:16 UTC</t>
+          <t>21-09-2026 16:14 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics regulatory approval (EMA CHMP recommendation for biosimilar Pertuzumab) for monitored company Biocon</t>
+          <t>healthcare policy affecting drug pricing for monitored company</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Celltrion Wins EMA Approval to Modify Phase 3 Trial for Darzalex Biosimilar CT-P44</t>
+          <t>Biocon receives EMA CHMP approval for Pertuzumab biosimilar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tipranks.com</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/celltrion-wins-ema-approval-to-modify-phase-3-trial-for-darzalex-biosimilar-ct-p44</t>
+          <t>https://www.expresspharma.in/amp/biocon-receives-ema-chmp-approval-for-pertuzumab-biosimilar/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21-09-2026 03:25 UTC</t>
+          <t>21-09-2026 09:45 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics regulatory approval (EMA for biosimilar clinical trial) for monitored company Celltrion</t>
+          <t>biosimilar EMA regulatory milestone for monitored company</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo, AstraZeneca’s Enhertu Wins EU Panel Backing for Early Breast Cancer</t>
+          <t>Celltrion’s ‘Remsima’ overtakes original after 11 years to claim top market share in Japan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>biopharmaapac.com</t>
+          <t>thebionews.net</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/86/8452/daiichi-sankyo-astrazenecas-enhertu-wins-eu-panel-backing-for-early-breast-cancer.html</t>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28346</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21-09-2026 01:18 UTC</t>
+          <t>21-09-2026 09:45 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biologics regulatory approval (EU panel backing for Enhertu, an antibody-drug conjugate) involving monitored company Daiichi Sankyo</t>
+          <t>infliximab biosimilar market share for monitored company</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,38 +714,198 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medincell: Teva unveils new data on its olanzapine, FDA decision expected end of 2026</t>
+          <t>Celltrion Wins EMA Approval to Modify Phase 3 Trial for Darzalex Biosimilar CT-P44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Idéal Investisseur</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.ideal-investisseur.fr/en/stock-news/medincell-teva-unveils-new-data-on-its-olanzapine-fda-decision-expected-end-of-2026/25427.html</t>
+          <t>https://www.tipranks.com/news/company-announcements/celltrion-wins-ema-approval-to-modify-phase-3-trial-for-darzalex-biosimilar-ct-p44</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21-09-2026 06:34 UTC</t>
+          <t>21-09-2026 03:25 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FDA regulatory action (decision expected) for monitored company Teva</t>
+          <t>biosimilar clinical/regulatory update for monitored company</t>
         </is>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo, AstraZeneca’s Enhertu Wins EU Panel Backing for Early Breast Cancer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BioPharma APAC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://biopharmaapac.com/news/86/8452/daiichi-sankyo-astrazenecas-enhertu-wins-eu-panel-backing-for-early-breast-cancer.html</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21-09-2026 01:18 UTC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>biologic regulatory milestone for monitored company</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Enhertu Extends PFS by Six Months in HER2 Lung Cancer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MyChesCo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.mychesco.com/a/news/regional/enhertu-extends-pfs-by-six-months-in-her2-lung-cancer/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21-09-2026 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>biologic clinical data for monitored company</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Samsung Biologics union warns of group action as talks stall in South Korea - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-science/2026/09/21/VJML65HP5NHNROA2UIWJFC7OH4/?outputType=amp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>21-09-2026 09:27 UTC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>manufacturing/labor dispute for monitored company</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical Fermentation Market Expands as Single-Use Bioreactors and Process Automation Scale Biologics Output</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Business Upturn</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://businessupturn.com/brand-post/biopharmaceutical-fermentation-market-expands-as-single-use-bioreactors-and-process-automation-scale-biologics-output/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>21-09-2026 13:29 UTC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>biologic manufacturing market trends</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -775,7 +935,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21-09-2026 14:03:58</t>
+          <t>21-09-2026 22:49:52</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>biosimilar partnership for monitored company</t>
+          <t>Partnerships, deals, licensing &amp; acquisition (biosimilar partnership for monitored company)</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eight Names, One Drug: Why Adalimumab Biosimilars Are Creating Real Confusion at the Counter</t>
+          <t>Malay Naik Appointed Executive Director, US Brand Lead – Oncology at Amgen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pharmacy Times</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pharmacytimes.com/view/eight-names-one-drug-why-adalimumab-biosimilars-are-creating-real-confusion-at-the-counter</t>
+          <t>https://hrtoday.in/malay-naik-appointed-executive-director-us-brand-lead-oncology-at-amgen/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21-09-2026 16:58 UTC</t>
+          <t>22-09-2026 07:00 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>adalimumab biosimilar market dynamics for monitored company</t>
+          <t>Monitored company (Amgen) corporate appointment directly related to commercialization in a biologics-heavy area (oncology)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pfizer depot suspended after Bengaluru fake drug bust; 16 licences cancelled</t>
+          <t>Eight Names, One Drug: Why Adalimumab Biosimilars Are Creating Real Confusion at the Counter</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Pharmacy Times</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/bangalore/bengaluru-pfizer-depot-suspended-fake-drug-bust-16-licences-cancelled-10887193/</t>
+          <t>https://www.pharmacytimes.com/view/eight-names-one-drug-why-adalimumab-biosimilars-are-creating-real-confusion-at-the-counter</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21-09-2026 07:57 UTC</t>
+          <t>21-09-2026 19:03 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>manufacturing/supply chain issue for monitored company</t>
+          <t>Market Launches, Approvals &amp; Commercial Events (adalimumab biosimilar market activity)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,7 +587,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -599,27 +599,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pfizer, Lilly 'most favored nation' deals to give US share of revenue from raised foreign prices</t>
+          <t>Medicuss Pfizer Deal Was Not a Fire Sale: A Strategic Bet on De-Risked ADC Drug</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>Streetwise Reports</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://endpoints.news/pfizer-lilly-most-favored-nation-deals-to-give-us-share-of-raised-foreign-prices/</t>
+          <t>https://www.streetwisereports.com/article/2026/09/21/medicuss-pfizer-deal-was-not-a-fire-sale-a-strategic-bet-on-de-risked-adc-drug.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21-09-2026 16:14 UTC</t>
+          <t>21-09-2026 20:35 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>healthcare policy affecting drug pricing for monitored company</t>
+          <t>Partnerships, deals, licensing &amp; acquisition (deal for ADC, a type of biologic)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Biocon receives EMA CHMP approval for Pertuzumab biosimilar</t>
+          <t>Press Release Distribution India</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>Business Wire India</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/amp/biocon-receives-ema-chmp-approval-for-pertuzumab-biosimilar/</t>
+          <t>https://www.businesswireindia.com/takeda-and-dr.-reddy's-laboratories-enter-into-exclusive-collaboration-to-promote-and-distribute-qdenga%C2%AE-in-india's-pediatric-and-adult-private-market-101818.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21-09-2026 09:45 UTC</t>
+          <t>21-09-2026 16:08 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>biosimilar EMA regulatory milestone for monitored company</t>
+          <t>Partnerships, deals, licensing &amp; acquisition (collaboration involving primary signal company Takeda)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Celltrion’s ‘Remsima’ overtakes original after 11 years to claim top market share in Japan</t>
+          <t>Dr. Reddy's Sees Dengue Vaccine Opportunity As QDENGA Launch Nears</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thebionews.net</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28346</t>
+          <t>https://www.businesstoday.in/bt-tv/market-today/video/dr-reddys-sees-dengue-vaccine-opportunity-as-qdenga-launch-nears-556778-2026-09-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21-09-2026 09:45 UTC</t>
+          <t>21-09-2026 08:54 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>infliximab biosimilar market share for monitored company</t>
+          <t>Earnings &amp; Financial Reports (guidance update mentioning pipeline milestones for monitored company related to Takeda)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celltrion Wins EMA Approval to Modify Phase 3 Trial for Darzalex Biosimilar CT-P44</t>
+          <t>Biocon Gets Positive CHMP Opinion for Pertuzumab Biosimilar Pebrilzo in HER2-Positive Breast Cancer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/celltrion-wins-ema-approval-to-modify-phase-3-trial-for-darzalex-biosimilar-ct-p44</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/biocon-gets-positive-chmp-opinion-for-pertuzumab-biosimilar-pebrilzo-in-her2-positive-breast-cancer-179713</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21-09-2026 03:25 UTC</t>
+          <t>21-09-2026 13:59 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>biosimilar clinical/regulatory update for monitored company</t>
+          <t>Biosimilars &amp; Biologics (biosimilar regulatory milestone)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo, AstraZeneca’s Enhertu Wins EU Panel Backing for Early Breast Cancer</t>
+          <t>Pearce IP BioBlast® for the week ending 18 September 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>Pearce IP</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/86/8452/daiichi-sankyo-astrazenecas-enhertu-wins-eu-panel-backing-for-early-breast-cancer.html</t>
+          <t>https://www.pearceip.law/2026/09/22/pearce-ip-bioblast-for-the-week-ending-18-september-2026/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21-09-2026 01:18 UTC</t>
+          <t>22-09-2026 05:48 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>biologic regulatory milestone for monitored company</t>
+          <t>Biosimilars &amp; Biologics (biotech IP/patent review)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Enhertu Extends PFS by Six Months in HER2 Lung Cancer</t>
+          <t>South Korea's Celltrion Ramps Up Songdo Plant 3, Targeting 15% Output Growth This Year</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MyChesCo</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.mychesco.com/a/news/regional/enhertu-extends-pfs-by-six-months-in-her2-lung-cancer/</t>
+          <t>https://finance.biggo.com/news/19517387-5726-40d3-8cd0-2e90f3a4b0cf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21-09-2026 17:00 UTC</t>
+          <t>22-09-2026 00:55 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>biologic clinical data for monitored company</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity (biologic manufacturing expansion and output growth)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Samsung Biologics union warns of group action as talks stall in South Korea - CHOSUNBIZ</t>
+          <t>Celltrion’s ‘Remsima’ overtakes original after 11 years to claim top market share in Japan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>더바이오</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/21/VJML65HP5NHNROA2UIWJFC7OH4/?outputType=amp</t>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28346</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21-09-2026 09:27 UTC</t>
+          <t>21-09-2026 09:45 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>manufacturing/labor dispute for monitored company</t>
+          <t>Market Launches, Approvals &amp; Commercial Events (biosimilar market share for IBD-relevant drug)</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,38 +874,198 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Prestige Biopharma</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Prestige Biopharma Deepens Oncology Focus With Biosimilars, Novel Antibodies and Platform Technologies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/company-announcements/prestige-biopharma-deepens-oncology-focus-with-biosimilars-novel-antibodies-and-platform-technologies</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>21-09-2026 22:45 UTC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics (strategy focusing on biosimilars and novel antibodies)</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo, AstraZeneca’s Enhertu Wins EU Panel Backing for Early Breast Cancer</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BioPharma APAC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://biopharmaapac.com/news/86/8452/daiichi-sankyo-astrazenecas-enhertu-wins-eu-panel-backing-for-early-breast-cancer.html</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>22-09-2026 03:32 UTC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FDA / Regulatory Actions (regulatory backing for a biologic (ADC))</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi inaugurates its new production line, a 28 million investment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://en.ilsole24ore.com/art/fresenius-kabi-launches-new-investment-line-worth-28-million-AJSreJKB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21-09-2026 17:23 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (manufacturing investment/expansion for sterile injectables)</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Roche’s Ocrevus moves closer to EU nod for paediatric MS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Indian Pharma Post</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.indianpharmapost.com/news/roches-ocrevus-moves-closer-to-eu-nod-for-paediatric-ms-21933</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>21-09-2026 12:15 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FDA / Regulatory Actions (biologic regulatory milestone in autoimmune disease)</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Biopharmaceutical Fermentation Market Expands as Single-Use Bioreactors and Process Automation Scale Biologics Output</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Business Upturn</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://businessupturn.com/brand-post/biopharmaceutical-fermentation-market-expands-as-single-use-bioreactors-and-process-automation-scale-biologics-output/</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>21-09-2026 13:29 UTC</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>biologic manufacturing market trends</t>
-        </is>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Samsung Biologics union warns of group action as talks stall in South Korea - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-science/2026/09/21/VJML65HP5NHNROA2UIWJFC7OH4/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>21-09-2026 09:27 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (manufacturing event affecting supply of biologics)</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -935,7 +1095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21-09-2026 22:49:52</t>
+          <t>22-09-2026 13:48:44</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,22 +484,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Pharmaceutical Business review -</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/sandoz-mabxience-agree-emicizumab-biosimilar-083853595.html</t>
+          <t>https://www.pharmaceutical-business-review.com/news/sandoz-mabxience-emicizumab-biosimilar/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21-09-2026 08:38 UTC</t>
+          <t>21-09-2026 16:02 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Partnerships, deals, licensing &amp; acquisition (biosimilar partnership for monitored company)</t>
+          <t>biosimilar partnership involving a monitored company</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Malay Naik Appointed Executive Director, US Brand Lead – Oncology at Amgen</t>
+          <t>Envisagenics and Boehringer Ingelheim Enter Multi-Target</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/malay-naik-appointed-executive-director-us-brand-lead-oncology-at-amgen/</t>
+          <t>https://www.globenewswire.com/news-release/2026/09/22/3366249/0/en/envisagenics-and-boehringer-ingelheim-enter-multi-target-collaboration-to-develop-first-in-class-precision-therapies-based-on-rna-splicing-derived-targets-for-hard-to-treat-cancers.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22-09-2026 07:00 UTC</t>
+          <t>22-09-2026 12:00 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company (Amgen) corporate appointment directly related to commercialization in a biologics-heavy area (oncology)</t>
+          <t>biologics licensing deal for a monitored company</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eight Names, One Drug: Why Adalimumab Biosimilars Are Creating Real Confusion at the Counter</t>
+          <t>AMGEN ANNOUNCES POSITIVE TOPLINE PHASE 3 RESULTS FOR DAZODALIBEP IN MODERATE-TO-SEVERE SYSTEMIC SJÖGREN'S DISEASE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pharmacy Times</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pharmacytimes.com/view/eight-names-one-drug-why-adalimumab-biosimilars-are-creating-real-confusion-at-the-counter</t>
+          <t>https://www.prnewswire.com/news-releases/amgen-announces-positive-topline-phase-3-results-for-dazodalibep-in-moderate-to-severe-systemic-sjogrens-disease-302885422.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21-09-2026 19:03 UTC</t>
+          <t>22-09-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events (adalimumab biosimilar market activity)</t>
+          <t>autoimmune biologic clinical trial news for a monitored company</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Medicuss Pfizer Deal Was Not a Fire Sale: A Strategic Bet on De-Risked ADC Drug</t>
+          <t>Eight Names, One Drug: Why Adalimumab Biosimilars Are Creating Real Confusion at the Counter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Streetwise Reports</t>
+          <t>Pharmacy Times</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.streetwisereports.com/article/2026/09/21/medicuss-pfizer-deal-was-not-a-fire-sale-a-strategic-bet-on-de-risked-adc-drug.html</t>
+          <t>https://www.pharmacytimes.com/view/eight-names-one-drug-why-adalimumab-biosimilars-are-creating-real-confusion-at-the-counter</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21-09-2026 20:35 UTC</t>
+          <t>21-09-2026 19:03 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partnerships, deals, licensing &amp; acquisition (deal for ADC, a type of biologic)</t>
+          <t>market discussion on adalimumab biosimilars</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Press Release Distribution India</t>
+          <t>Karnataka Fake Drug Bust: Pfizer Warehouse Suspended, 16 Licences Cancelled Near Bengaluru</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Business Wire India</t>
+          <t>LawBeat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.businesswireindia.com/takeda-and-dr.-reddy's-laboratories-enter-into-exclusive-collaboration-to-promote-and-distribute-qdenga%C2%AE-in-india's-pediatric-and-adult-private-market-101818.html</t>
+          <t>https://lawbeat.in/news-updates/karnataka-fake-drug-bust-pfizer-warehouse-suspended-16-licences-cancelled-near-bengaluru-1634046</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21-09-2026 16:08 UTC</t>
+          <t>22-09-2026 08:42 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partnerships, deals, licensing &amp; acquisition (collaboration involving primary signal company Takeda)</t>
+          <t>manufacturing/supply chain issue for a monitored company</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Sees Dengue Vaccine Opportunity As QDENGA Launch Nears</t>
+          <t>Biocon's Pertuzumab Becomes First Biosimilar to Secure EMA CHMP Approval Recommendation Under New Tailored Clinical Approach</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/bt-tv/market-today/video/dr-reddys-sees-dengue-vaccine-opportunity-as-qdenga-launch-nears-556778-2026-09-21</t>
+          <t>https://www.prnewswire.com/news-releases/biocons-pertuzumab-becomes-first-biosimilar-to-secure-ema-chmp-approval-recommendation-under-new-tailored-clinical-approach-302886103.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21-09-2026 08:54 UTC</t>
+          <t>22-09-2026 11:56 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Earnings &amp; Financial Reports (guidance update mentioning pipeline milestones for monitored company related to Takeda)</t>
+          <t>biosimilar regulatory milestone (EMA CHMP positive opinion) for a monitored company</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Biocon Gets Positive CHMP Opinion for Pertuzumab Biosimilar Pebrilzo in HER2-Positive Breast Cancer</t>
+          <t>Celltrion renews EU-GMP certification for 250,000-liter Songdo facilities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/biocon-gets-positive-chmp-opinion-for-pertuzumab-biosimilar-pebrilzo-in-her2-positive-breast-cancer-179713</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33267</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21-09-2026 13:59 UTC</t>
+          <t>22-09-2026 01:55 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics (biosimilar regulatory milestone)</t>
+          <t>biologic manufacturing EU-GMP renewal and capacity expansion for a monitored company</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pearce IP BioBlast® for the week ending 18 September 2026</t>
+          <t>Prestige Biopharma Deepens Oncology Focus With Biosimilars, Novel Antibodies and Platform Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pearce IP</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pearceip.law/2026/09/22/pearce-ip-bioblast-for-the-week-ending-18-september-2026/</t>
+          <t>https://www.tipranks.com/news/company-announcements/prestige-biopharma-deepens-oncology-focus-with-biosimilars-novel-antibodies-and-platform-technologies</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22-09-2026 05:48 UTC</t>
+          <t>21-09-2026 22:45 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics (biotech IP/patent review)</t>
+          <t>monitored company's strategy in biosimilars and novel antibodies</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>South Korea's Celltrion Ramps Up Songdo Plant 3, Targeting 15% Output Growth This Year</t>
+          <t>Daiichi Sankyo Names Ken Keller Chief Commercialization Officer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>The Healthcare Technology Report.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/19517387-5726-40d3-8cd0-2e90f3a4b0cf</t>
+          <t>https://thehealthcaretechnologyreport.com/daiichi-sankyo-names-ken-keller-chief-commercialization-officer/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22-09-2026 00:55 UTC</t>
+          <t>22-09-2026 12:03 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (biologic manufacturing expansion and output growth)</t>
+          <t>corporate appointment related to commercialization for a monitored company</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Celltrion’s ‘Remsima’ overtakes original after 11 years to claim top market share in Japan</t>
+          <t>Daiichi Sankyo, AstraZeneca’s Enhertu Wins EU Panel Backing for Early Breast Cancer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>더바이오</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28346</t>
+          <t>https://biopharmaapac.com/news/86/8452/daiichi-sankyo-astrazenecas-enhertu-wins-eu-panel-backing-for-early-breast-cancer.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21-09-2026 09:45 UTC</t>
+          <t>22-09-2026 03:32 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events (biosimilar market share for IBD-relevant drug)</t>
+          <t>biologic regulatory/market access news for a monitored company</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prestige Biopharma Deepens Oncology Focus With Biosimilars, Novel Antibodies and Platform Technologies</t>
+          <t>Psoriatic Arthritis Market Landscape: 6 Key Late-Stage Drugs Set to Drive Future Growth | DelveInsight</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/prestige-biopharma-deepens-oncology-focus-with-biosimilars-novel-antibodies-and-platform-technologies</t>
+          <t>https://www.globenewswire.com/news-release/2026/09/21/3365777/0/en/psoriatic-arthritis-market-landscape-6-key-late-stage-drugs-set-to-drive-future-growth-delveinsight.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21-09-2026 22:45 UTC</t>
+          <t>21-09-2026 17:00 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics (strategy focusing on biosimilars and novel antibodies)</t>
+          <t>autoimmune disease market report relevant to biologics/pipeline for a monitored company</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo, AstraZeneca’s Enhertu Wins EU Panel Backing for Early Breast Cancer</t>
+          <t>Fresenius Kabi inaugurates its new production line, a 28 million investment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/86/8452/daiichi-sankyo-astrazenecas-enhertu-wins-eu-panel-backing-for-early-breast-cancer.html</t>
+          <t>https://en.ilsole24ore.com/art/fresenius-kabi-launches-new-investment-line-worth-28-million-AJSreJKB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22-09-2026 03:32 UTC</t>
+          <t>21-09-2026 17:23 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions (regulatory backing for a biologic (ADC))</t>
+          <t>manufacturing expansion for a monitored company active in biosimilars</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fresenius Kabi inaugurates its new production line, a 28 million investment</t>
+          <t>Teva CEO Details Biopharma Pivot, $700M Savings Plan and Growth Pipeline</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://en.ilsole24ore.com/art/fresenius-kabi-launches-new-investment-line-worth-28-million-AJSreJKB</t>
+          <t>https://finance.yahoo.com/healthcare/articles/teva-ceo-details-biopharma-pivot-090251701.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21-09-2026 17:23 UTC</t>
+          <t>22-09-2026 09:02 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (manufacturing investment/expansion for sterile injectables)</t>
+          <t>monitored company's biopharma strategy and pipeline news</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,85 +987,45 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Roche’s Ocrevus moves closer to EU nod for paediatric MS</t>
+          <t>Samsung BioLogics Union: "Third Post-Mediation Next Month... Strike to Begin if No Progress"</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/roches-ocrevus-moves-closer-to-eu-nod-for-paediatric-ms-21933</t>
+          <t>https://www.asiae.co.kr/en/article/economic-general/2026092217194790038</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21-09-2026 12:15 UTC</t>
+          <t>22-09-2026 08:19 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions (biologic regulatory milestone in autoimmune disease)</t>
+          <t>manufacturing/supply chain event (potential strike) for a monitored biologics CDMO</t>
         </is>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Samsung Biologics union warns of group action as talks stall in South Korea - CHOSUNBIZ</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/21/VJML65HP5NHNROA2UIWJFC7OH4/</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>21-09-2026 09:27 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (manufacturing event affecting supply of biologics)</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1095,7 +1055,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-09-2026 13:48:44</t>
+          <t>22-09-2026 21:16:58</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Chime Biologics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz and mAbxience agree on emicizumab biosimilar partnership</t>
+          <t>Biosimilar Contract Manufacturing Market to reach USD 51.42 Billion by 2035 at 14.9% CAGR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pharmaceutical Business review -</t>
+          <t>EIN News</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-business-review.com/news/sandoz-mabxience-emicizumab-biosimilar/</t>
+          <t>https://www.einnews.com/pr_news/944482502/biosimilar-contract-manufacturing-market-to-reach-usd-51-42-billion-by-2035-at-14-9-cagr</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21-09-2026 16:02 UTC</t>
+          <t>23-09-2026 07:34 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>biosimilar partnership involving a monitored company</t>
+          <t>Biosimilar &amp; Biologic manufacturing market news, Monitored Company.</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Envisagenics and Boehringer Ingelheim Enter Multi-Target</t>
+          <t>AMGEN ANNOUNCES POSITIVE TOPLINE PHASE 3 RESULTS FOR DAZODALIBEP IN MODERATE-TO-SEVERE SYSTEMIC SJÖGREN'S DISEASE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/09/22/3366249/0/en/envisagenics-and-boehringer-ingelheim-enter-multi-target-collaboration-to-develop-first-in-class-precision-therapies-based-on-rna-splicing-derived-targets-for-hard-to-treat-cancers.html</t>
+          <t>https://www.prnewswire.com/news-releases/amgen-announces-positive-topline-phase-3-results-for-dazodalibep-in-moderate-to-severe-systemic-sjogrens-disease-302885422.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22-09-2026 12:00 UTC</t>
+          <t>22-09-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>biologics licensing deal for a monitored company</t>
+          <t>Monitored company, clinical trial results for a biologic in autoimmune disease.</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMGEN ANNOUNCES POSITIVE TOPLINE PHASE 3 RESULTS FOR DAZODALIBEP IN MODERATE-TO-SEVERE SYSTEMIC SJÖGREN'S DISEASE</t>
+          <t>Karnataka Fake Drug Bust: Pfizer Warehouse Suspended, 16 Licences Cancelled Near Bengaluru</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>LawBeat</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/amgen-announces-positive-topline-phase-3-results-for-dazodalibep-in-moderate-to-severe-systemic-sjogrens-disease-302885422.html</t>
+          <t>https://lawbeat.in/amp/news-updates/karnataka-fake-drug-bust-pfizer-warehouse-suspended-16-licences-cancelled-near-bengaluru-1634046</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22-09-2026 13:00 UTC</t>
+          <t>22-09-2026 08:42 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>autoimmune biologic clinical trial news for a monitored company</t>
+          <t>Monitored company, regulatory enforcement action / supply chain integrity concern.</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eight Names, One Drug: Why Adalimumab Biosimilars Are Creating Real Confusion at the Counter</t>
+          <t>Multiple Sclerosis Pipeline 2026: FDA Updates, Therapy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pharmacy Times</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pharmacytimes.com/view/eight-names-one-drug-why-adalimumab-biosimilars-are-creating-real-confusion-at-the-counter</t>
+          <t>https://www.openpr.com/news/4640253/multiple-sclerosis-pipeline-2026-fda-updates-therapy</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21-09-2026 19:03 UTC</t>
+          <t>23-09-2026 00:46 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>market discussion on adalimumab biosimilars</t>
+          <t>Relevant therapeutic area (autoimmune disease) pipeline news.</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Karnataka Fake Drug Bust: Pfizer Warehouse Suspended, 16 Licences Cancelled Near Bengaluru</t>
+          <t>Biocon's Pertuzumab Becomes First Biosimilar to Secure EMA CHMP Approval Recommendation Under New Tailored Clinical Approach</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LawBeat</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://lawbeat.in/news-updates/karnataka-fake-drug-bust-pfizer-warehouse-suspended-16-licences-cancelled-near-bengaluru-1634046</t>
+          <t>https://www.prnewswire.com/news-releases/biocons-pertuzumab-becomes-first-biosimilar-to-secure-ema-chmp-approval-recommendation-under-new-tailored-clinical-approach-302886103.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22-09-2026 08:42 UTC</t>
+          <t>22-09-2026 11:56 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>manufacturing/supply chain issue for a monitored company</t>
+          <t>Monitored company, biosimilar CHMP approval recommendation, new regulatory pathway.</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -679,27 +679,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Biocon's Pertuzumab Becomes First Biosimilar to Secure EMA CHMP Approval Recommendation Under New Tailored Clinical Approach</t>
+          <t>Syngene Expands Integrated Drug Development and Manufacturing Services with BMS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Genetic Engineering and Biotechnology News</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/biocons-pertuzumab-becomes-first-biosimilar-to-secure-ema-chmp-approval-recommendation-under-new-tailored-clinical-approach-302886103.html</t>
+          <t>https://www.genengnews.com/topics/bioprocessing/syngene-expands-integrated-drug-development-and-manufacturing-services-with-bms/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22-09-2026 11:56 UTC</t>
+          <t>22-09-2026 17:48 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>biosimilar regulatory milestone (EMA CHMP positive opinion) for a monitored company</t>
+          <t>Monitored company (Biocon subsidiary), manufacturing/CDMO deal.</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celltrion renews EU-GMP certification for 250,000-liter Songdo facilities</t>
+          <t>Karnataka Suspends Assistant Drug Controller Over Alleged Lapses in Counterfeit Drug Case</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33267</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/karnataka-suspends-assistant-drug-controller-over-alleged-lapses-in-counterfeit-drug-case-179781</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22-09-2026 01:55 UTC</t>
+          <t>22-09-2026 17:01 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>biologic manufacturing EU-GMP renewal and capacity expansion for a monitored company</t>
+          <t>Monitored company, regulatory enforcement action.</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prestige Biopharma Deepens Oncology Focus With Biosimilars, Novel Antibodies and Platform Technologies</t>
+          <t>Lotte Biologics: "No Issues With 'GMP-Ready' in November"... Songdo CDMO Competition Begins</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/prestige-biopharma-deepens-oncology-focus-with-biosimilars-novel-antibodies-and-platform-technologies</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026092207275643128</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21-09-2026 22:45 UTC</t>
+          <t>23-09-2026 00:22 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>monitored company's strategy in biosimilars and novel antibodies</t>
+          <t>Biologic CDMO market competition, manufacturing capacity news.</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Names Ken Keller Chief Commercialization Officer</t>
+          <t>Prestige’s Caribbean Biosimilar Approval Paves Way For International Expansion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The Healthcare Technology Report.</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://thehealthcaretechnologyreport.com/daiichi-sankyo-names-ken-keller-chief-commercialization-officer/</t>
+          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/prestiges-caribbean-biosimilar-approval-paves-way-for-international-expansion-DL4EA5ESEFE2PED4ICO4DLK74I/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22-09-2026 12:03 UTC</t>
+          <t>22-09-2026 14:45 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>corporate appointment related to commercialization for a monitored company</t>
+          <t>Monitored company, biosimilar international approval.</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo, AstraZeneca’s Enhertu Wins EU Panel Backing for Early Breast Cancer</t>
+          <t>Teva CEO Details Biopharma Pivot, $700M Savings Plan and Growth Pipeline</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/86/8452/daiichi-sankyo-astrazenecas-enhertu-wins-eu-panel-backing-for-early-breast-cancer.html</t>
+          <t>https://finance.yahoo.com/healthcare/articles/teva-ceo-details-biopharma-pivot-090251701.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22-09-2026 03:32 UTC</t>
+          <t>22-09-2026 09:02 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>biologic regulatory/market access news for a monitored company</t>
+          <t>Monitored company, strategic pivot towards biopharma/biologics.</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Psoriatic Arthritis Market Landscape: 6 Key Late-Stage Drugs Set to Drive Future Growth | DelveInsight</t>
+          <t>Virtual Event | The Next Era of Biosimilars: Rewriting the Playbook</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>STAT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/09/21/3365777/0/en/psoriatic-arthritis-market-landscape-6-key-late-stage-drugs-set-to-drive-future-growth-delveinsight.html</t>
+          <t>https://www.statnews.com/event/next-era-of-biosimilars-rewriting-the-playbook/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21-09-2026 17:00 UTC</t>
+          <t>22-09-2026 21:59 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>autoimmune disease market report relevant to biologics/pipeline for a monitored company</t>
+          <t>Monitored company, biosimilar industry event.</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,32 +914,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fresenius Kabi inaugurates its new production line, a 28 million investment</t>
+          <t>John Rim Builds Samsung Biologics Into a Global CDMO Powerhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>인사이트코리아</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://en.ilsole24ore.com/art/fresenius-kabi-launches-new-investment-line-worth-28-million-AJSreJKB</t>
+          <t>https://www.insightkorea.co.kr/news/articleViewAmp.html?idxno=255225</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21-09-2026 17:23 UTC</t>
+          <t>23-09-2026 04:36 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>manufacturing expansion for a monitored company active in biosimilars</t>
+          <t>Monitored company (Samsung Biologics), growth of biologics CDMO business.</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,85 +947,45 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Teva CEO Details Biopharma Pivot, $700M Savings Plan and Growth Pipeline</t>
+          <t>Samsung Biologics labor talks stall as union readies strike in South Korea - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/teva-ceo-details-biopharma-pivot-090251701.html</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/22/ZYWD2Z6JVREO7PSK6J5L65NQLA/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22-09-2026 09:02 UTC</t>
+          <t>22-09-2026 08:49 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>monitored company's biopharma strategy and pipeline news</t>
+          <t>Monitored company (Samsung Biologics), labor dispute potentially affecting biologics manufacturing.</t>
         </is>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Samsung BioLogics Union: "Third Post-Mediation Next Month... Strike to Begin if No Progress"</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>아시아경제</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.asiae.co.kr/en/article/economic-general/2026092217194790038</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>22-09-2026 08:19 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>manufacturing/supply chain event (potential strike) for a monitored biologics CDMO</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1055,7 +1015,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-09-2026 21:16:58</t>
+          <t>23-09-2026 13:49:55</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilar &amp; Biologic manufacturing market news, Monitored Company.</t>
+          <t>Biosimilars &amp; Biologics market context and Monitored Company</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMGEN ANNOUNCES POSITIVE TOPLINE PHASE 3 RESULTS FOR DAZODALIBEP IN MODERATE-TO-SEVERE SYSTEMIC SJÖGREN'S DISEASE</t>
+          <t>Envisagenics and Boehringer ink up to $1 billion RNA splicing oncology deal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/amgen-announces-positive-topline-phase-3-results-for-dazodalibep-in-moderate-to-severe-systemic-sjogrens-disease-302885422.html</t>
+          <t>https://www.thepharmaletter.com/biotech-news/envisagenics-and-boehringer-ink-up-to-1-billion-rna-splicing-oncology-deal</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22-09-2026 13:00 UTC</t>
+          <t>22-09-2026 16:06 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company, clinical trial results for a biologic in autoimmune disease.</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition for a monitored company active in biologics</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Karnataka Fake Drug Bust: Pfizer Warehouse Suspended, 16 Licences Cancelled Near Bengaluru</t>
+          <t>Amgen's autoimmune drug succeeds in late-stage trial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LawBeat</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://lawbeat.in/amp/news-updates/karnataka-fake-drug-bust-pfizer-warehouse-suspended-16-licences-cancelled-near-bengaluru-1634046</t>
+          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/amgens-autoimmune-drug-succeeds-late-stage-trial-2026-09-22/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:42 UTC</t>
+          <t>22-09-2026 17:14 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company, regulatory enforcement action / supply chain integrity concern.</t>
+          <t>Clinical Trials &amp; Pipeline News for an autoimmune biologic drug from a monitored company</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Multiple Sclerosis Pipeline 2026: FDA Updates, Therapy</t>
+          <t>Dr Reddy's Q1FY27 revenue falls to ₹8,071 Cr on semaglutide hit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4640253/multiple-sclerosis-pipeline-2026-fda-updates-therapy</t>
+          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-q1fy27-revenue-falls-6-to-8-071-cr-margins-hit-by-api-costs/46269828</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23-09-2026 00:46 UTC</t>
+          <t>23-09-2026 00:09 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Relevant therapeutic area (autoimmune disease) pipeline news.</t>
+          <t>Earnings &amp; Financial Reports mentioning biologic drug (semaglutide) from a monitored company</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Biocon's Pertuzumab Becomes First Biosimilar to Secure EMA CHMP Approval Recommendation Under New Tailored Clinical Approach</t>
+          <t>Semaglutide in India: Sun Pharma, Dr Reddy’s, Glenmark Launch Drug As Novo Nordisk Patent Expires | Explained</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Goodreturns</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/biocons-pertuzumab-becomes-first-biosimilar-to-secure-ema-chmp-approval-recommendation-under-new-tailored-clinical-approach-302886103.html</t>
+          <t>https://www.goodreturns.in/news/semaglutide-in-india-sun-pharma-dr-reddy-s-gelnmark-launch-drug-as-novo-nordisk-patent-expires-1497377.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22-09-2026 11:56 UTC</t>
+          <t>23-09-2026 07:19 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company, biosimilar CHMP approval recommendation, new regulatory pathway.</t>
+          <t>Biosimilars &amp; Biologics market launch for a biologic drug from a monitored company</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Syngene Expands Integrated Drug Development and Manufacturing Services with BMS</t>
+          <t>Intas Pharmaceuticals appoints Taranpreet Singh Lamba as Executive Vice President – Global IPR &amp; Portfolio, India &amp; Emerging Markets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Genetic Engineering and Biotechnology News</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.genengnews.com/topics/bioprocessing/syngene-expands-integrated-drug-development-and-manufacturing-services-with-bms/</t>
+          <t>https://www.indianpharmapost.com/people/intas-pharmaceuticals-appoints-taranpreet-singh-lamba-as-executive-vice-president-global-ipr-portfolio-india-emerging-markets-21954</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22-09-2026 17:48 UTC</t>
+          <t>23-09-2026 11:10 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company (Biocon subsidiary), manufacturing/CDMO deal.</t>
+          <t>Monitored Company corporate appointment relevant to IPR &amp; Portfolio strategy for biologics/biosimilars</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Karnataka Suspends Assistant Drug Controller Over Alleged Lapses in Counterfeit Drug Case</t>
+          <t>Biocon's Pertuzumab Biosimilar Earns CHMP Nod Under EMA's New Tailored Pathway</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>biopharminternational.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/karnataka-suspends-assistant-drug-controller-over-alleged-lapses-in-counterfeit-drug-case-179781</t>
+          <t>https://www.biopharminternational.com/view/biocon-s-pertuzumab-biosimilar-earns-chmp-nod-under-ema-s-new-tailored-pathway</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22-09-2026 17:01 UTC</t>
+          <t>22-09-2026 15:45 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company, regulatory enforcement action.</t>
+          <t>Biosimilars &amp; Biologics regulatory milestone (CHMP Nod) for a monitored company</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lotte Biologics: "No Issues With 'GMP-Ready' in November"... Songdo CDMO Competition Begins</t>
+          <t>Syngene Expands Integrated Drug Development and Manufacturing Services with BMS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Genetic Engineering and Biotechnology News</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026092207275643128</t>
+          <t>https://www.genengnews.com/topics/bioprocessing/syngene-expands-integrated-drug-development-and-manufacturing-services-with-bms/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23-09-2026 00:22 UTC</t>
+          <t>22-09-2026 17:48 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Biologic CDMO market competition, manufacturing capacity news.</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity deal for a monitored company's subsidiary</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prestige’s Caribbean Biosimilar Approval Paves Way For International Expansion</t>
+          <t>Aurobindo Pharma's Apitoria Unit Receives VAI Classification from USFDA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/prestiges-caribbean-biosimilar-approval-paves-way-for-international-expansion-DL4EA5ESEFE2PED4ICO4DLK74I/</t>
+          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-s-apitoria-unit-receives-vai-classification-from-usfda-following-december-inspection/35526827</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22-09-2026 14:45 UTC</t>
+          <t>23-09-2026 00:08 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored company, biosimilar international approval.</t>
+          <t>FDA / REGULATORY ACTIONS and Manufacturing, Supply Chain &amp; Capacity for a monitored company</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Teva CEO Details Biopharma Pivot, $700M Savings Plan and Growth Pipeline</t>
+          <t>Celltrion Wins US FDA Nod for RA Trial of Zymfentra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/teva-ceo-details-biopharma-pivot-090251701.html</t>
+          <t>https://www.marketscreener.com/news/celltrion-wins-us-fda-nod-for-ra-trial-of-zymfentra-ce785ad9dc8dfe27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22-09-2026 09:02 UTC</t>
+          <t>23-09-2026 11:56 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitored company, strategic pivot towards biopharma/biologics.</t>
+          <t>Clinical Trials &amp; Pipeline News for a biosimilar drug from a monitored company in an autoimmune indication</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Virtual Event | The Next Era of Biosimilars: Rewriting the Playbook</t>
+          <t>Lotte Biologics: "No Issues With 'GMP-Ready' in November"... Songdo CDMO Competition Begins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STAT</t>
+          <t>asiae.co.kr</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.statnews.com/event/next-era-of-biosimilars-rewriting-the-playbook/</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026092207275643128</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22-09-2026 21:59 UTC</t>
+          <t>23-09-2026 00:22 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitored company, biosimilar industry event.</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity (CDMO competition) relevant to monitored companies</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,32 +914,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>John Rim Builds Samsung Biologics Into a Global CDMO Powerhouse</t>
+          <t>Mucopolysaccharidosis Type I Market Size, Share, Growth, Epidemiology and Forecast to 2036</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>인사이트코리아</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleViewAmp.html?idxno=255225</t>
+          <t>https://www.barchart.com/press-releases/4744495/mucopolysaccharidosis-type-i-market-size-share-growth-epidemiology-and-forecast-to-2036</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23-09-2026 04:36 UTC</t>
+          <t>22-09-2026 23:30 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monitored company (Samsung Biologics), growth of biologics CDMO business.</t>
+          <t>Clinical Trials &amp; Pipeline News (market report) for rare disease relevant to monitored companies</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -954,38 +954,238 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Eczema Pipeline: Emerging Therapies and Key Developments Shaping the Treatment Landscape | DelveInsight</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4641457/eczema-pipeline-emerging-therapies-and-key-developments</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23-09-2026 14:32 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Clinical Trials &amp; Pipeline News for a relevant specialty market (eczema/dermatology) from a monitored company</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Polpharma</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Polpharma Santo launches exports of Kazakhstan-made medicines to EU</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Qazinform</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://qazinform.com/news/polpharma-santo-launches-exports-of-kazakhstan-made-medicines-to-eu-008830</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>23-09-2026 05:46 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Market Launches, Approvals &amp; Commercial Events (exports) for a monitored company active in biosimilars</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Multiple Sclerosis Pipeline 2026: FDA Updates, Therapy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4640253/multiple-sclerosis-pipeline-2026-fda-updates-therapy</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>23-09-2026 00:46 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Clinical Trials &amp; Pipeline News for an autoimmune disease from a monitored company</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Advanz Pharma</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EU General Court Judgment in Case T-455/24 Advanz Pharma v Commission</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INSIGHT EU MONITORING</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://ieu-monitoring.com/event/eu-general-court-judgment-in-case-t-455-24-advanz-pharma-v-commission</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>22-09-2026 23:39 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FDA / REGULATORY ACTIONS for a monitored company</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>John Rim Builds Samsung Biologics Into a Global CDMO Powerhouse</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>인사이트코리아</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.insightkorea.co.kr/news/articleViewAmp.html?idxno=255225</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>23-09-2026 04:36 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (CDMO growth) for a monitored company</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Samsung Biologics labor talks stall as union readies strike in South Korea - CHOSUNBIZ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/22/ZYWD2Z6JVREO7PSK6J5L65NQLA/</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>22-09-2026 08:49 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Monitored company (Samsung Biologics), labor dispute potentially affecting biologics manufacturing.</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical Manufacturing Market Is Going to Boom with</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4640517/biopharmaceutical-manufacturing-market-is-going-to-boom-with</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>23-09-2026 07:10 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity market context for a monitored company</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1015,7 +1215,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-09-2026 13:49:55</t>
+          <t>23-09-2026 21:11:53</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chime Biologics</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biosimilar Contract Manufacturing Market to reach USD 51.42 Billion by 2035 at 14.9% CAGR</t>
+          <t>$275M Sandoz and Fougera antitrust class action settlement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EIN News</t>
+          <t>Top Class Actions</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.einnews.com/pr_news/944482502/biosimilar-contract-manufacturing-market-to-reach-usd-51-42-billion-by-2035-at-14-9-cagr</t>
+          <t>https://topclassactions.com/lawsuit-settlements/open-lawsuit-settlements/275m-sandoz-and-fougera-antitrust-class-action-settlement/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23-09-2026 07:34 UTC</t>
+          <t>24-09-2026 04:48 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics market context and Monitored Company</t>
+          <t>Monitored company Sandoz, significant antitrust settlement (market event)</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Envisagenics and Boehringer ink up to $1 billion RNA splicing oncology deal</t>
+          <t>Amgen's Dazodalibep Meets Primary Endpoint in Phase 3 Sjögren's Trial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biotech-news/envisagenics-and-boehringer-ink-up-to-1-billion-rna-splicing-oncology-deal</t>
+          <t>https://www.biopharminternational.com/view/amgen-dazodalibep-primary-endpoint-phase-3-sjogrens-trial</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22-09-2026 16:06 UTC</t>
+          <t>23-09-2026 15:46 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition for a monitored company active in biologics</t>
+          <t>Monitored company Amgen, clinical trial results for biologic in autoimmune disease</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amgen's autoimmune drug succeeds in late-stage trial</t>
+          <t>Coherus Oncology retains Oppenheimer to market legacy biosimilar assets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/amgens-autoimmune-drug-succeeds-late-stage-trial-2026-09-22/</t>
+          <t>https://www.tipranks.com/news/the-fly/coherus-oncology-retains-oppenheimer-to-market-legacy-biosimilar-assets-thefly-news</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22-09-2026 17:14 UTC</t>
+          <t>23-09-2026 14:39 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News for an autoimmune biologic drug from a monitored company</t>
+          <t>Monitored company Coherus Biosciences, biosimilar commercial event</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q1FY27 revenue falls to ₹8,071 Cr on semaglutide hit</t>
+          <t>Pfizer India removes products from Karnataka markets after spurious drugs crackdown</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-q1fy27-revenue-falls-6-to-8-071-cr-margins-hit-by-api-costs/46269828</t>
+          <t>https://www.thehindubusinessline.com/companies/pfizer-india-removes-products-from-karnataka-markets-after-spurious-drugs-crackdown/article71498929.ece</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23-09-2026 00:09 UTC</t>
+          <t>23-09-2026 08:27 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earnings &amp; Financial Reports mentioning biologic drug (semaglutide) from a monitored company</t>
+          <t>Monitored company Pfizer, regulatory action related to quality/supply chain</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -639,27 +639,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semaglutide in India: Sun Pharma, Dr Reddy’s, Glenmark Launch Drug As Novo Nordisk Patent Expires | Explained</t>
+          <t>Global Vitiligo Treatment Market to Reach USD 2.97 Billion by 2034 at 5.8% CAGR as Rising Disease Prevalence, Growing Aesthetic Awareness, and Advances in Targeted Therapies Accelerate Market Growth, Reports Maximize Market Research</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Goodreturns</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.goodreturns.in/news/semaglutide-in-india-sun-pharma-dr-reddy-s-gelnmark-launch-drug-as-novo-nordisk-patent-expires-1497377.html</t>
+          <t>https://www.prnewswire.com/news-releases/global-vitiligo-treatment-market-to-reach-usd-2-97-billion-by-2034-at-5-8-cagr-as-rising-disease-prevalence-growing-aesthetic-awareness-and-advances-in-targeted-therapies-accelerate-market-growth-reports-maximize-market-resear-302887627.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23-09-2026 07:19 UTC</t>
+          <t>23-09-2026 21:45 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics market launch for a biologic drug from a monitored company</t>
+          <t>Biosimilars &amp; Biologics, market report for autoimmune disease (vitiligo) with targeted therapies</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,7 +667,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23-09-2026 11:10 UTC</t>
+          <t>23-09-2026 12:20 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored Company corporate appointment relevant to IPR &amp; Portfolio strategy for biologics/biosimilars</t>
+          <t>Monitored company Intas, corporate appointment for Global IPR &amp; Portfolio impacting biosimilar strategy</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -719,27 +719,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Biocon's Pertuzumab Biosimilar Earns CHMP Nod Under EMA's New Tailored Pathway</t>
+          <t>Insulin Glargine Market Size to Reach US$ 14.52 Billion by 2035 as</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>biopharminternational.com</t>
+          <t>openpr.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.biopharminternational.com/view/biocon-s-pertuzumab-biosimilar-earns-chmp-nod-under-ema-s-new-tailored-pathway</t>
+          <t>https://www.openpr.com/news/4641218/insulin-glargine-market-size-to-reach-us-14-52-billion-by-2035-as</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22-09-2026 15:45 UTC</t>
+          <t>23-09-2026 12:42 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics regulatory milestone (CHMP Nod) for a monitored company</t>
+          <t>Monitored company Biocon, biosimilar market research (insulin glargine)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Syngene Expands Integrated Drug Development and Manufacturing Services with BMS</t>
+          <t>Zydus Life Bets on Innovation &amp; Specialty Drugs to Drive Growth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Genetic Engineering and Biotechnology News</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.genengnews.com/topics/bioprocessing/syngene-expands-integrated-drug-development-and-manufacturing-services-with-bms/</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/zydus-life-bets-on-innovation-specialty-drugs-to-drive-growth/134449035</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22-09-2026 17:48 UTC</t>
+          <t>24-09-2026 01:44 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity deal for a monitored company's subsidiary</t>
+          <t>Monitored company Zydus Biotech, strategy for innovation and specialty drugs (biosimilars relevant)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma's Apitoria Unit Receives VAI Classification from USFDA</t>
+          <t>Celltrion Wins US FDA Nod for RA Trial of Zymfentra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-s-apitoria-unit-receives-vai-classification-from-usfda-following-december-inspection/35526827</t>
+          <t>https://www.marketscreener.com/news/celltrion-wins-us-fda-nod-for-ra-trial-of-zymfentra-ce785ad9dc8dfe27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23-09-2026 00:08 UTC</t>
+          <t>23-09-2026 11:56 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FDA / REGULATORY ACTIONS and Manufacturing, Supply Chain &amp; Capacity for a monitored company</t>
+          <t>Monitored company Celltrion, FDA nod for clinical trial of IBD biologic in autoimmune disease (RA)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Celltrion Wins US FDA Nod for RA Trial of Zymfentra</t>
+          <t>Turbine, Daiichi Sankyo Expand Virtual Biology Collaboration to Accelerate ADC Discovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>biopharmaapac.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/celltrion-wins-us-fda-nod-for-ra-trial-of-zymfentra-ce785ad9dc8dfe27</t>
+          <t>https://biopharmaapac.com/news/41/8478/turbine-daiichi-sankyo-expand-virtual-biology-collaboration-to-accelerate-adc-discovery.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23-09-2026 11:56 UTC</t>
+          <t>24-09-2026 06:10 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News for a biosimilar drug from a monitored company in an autoimmune indication</t>
+          <t>Monitored company Daiichi Sankyo, partnership for biologic (ADC) discovery</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotte Biologics: "No Issues With 'GMP-Ready' in November"... Songdo CDMO Competition Begins</t>
+          <t>Trastuzumab Rezetecan Improves Progression-Free Survival in Chemotherapy-Refractory HER2-Positive Advanced Colorectal Cancer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>asiae.co.kr</t>
+          <t>The ASCO Post</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026092207275643128</t>
+          <t>https://ascopost.com/news/september-2026/trastuzumab-rezetecan-improves-progression-free-survival-in-chemotherapy-refractory-her2-positive-advanced-colorectal-cancer/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23-09-2026 00:22 UTC</t>
+          <t>23-09-2026 19:12 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (CDMO competition) relevant to monitored companies</t>
+          <t>Clinical trials &amp; pipeline news, monoclonal antibody (biologic) in oncology</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mucopolysaccharidosis Type I Market Size, Share, Growth, Epidemiology and Forecast to 2036</t>
+          <t>Eczema Pipeline: Emerging Therapies and Key Developments Shaping the Treatment Landscape | DelveInsight</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4744495/mucopolysaccharidosis-type-i-market-size-share-growth-epidemiology-and-forecast-to-2036</t>
+          <t>https://www.barchart.com/press-releases/4757719/eczema-pipeline-emerging-therapies-and-key-developments-shaping-the-treatment-landscape-delveinsight</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22-09-2026 23:30 UTC</t>
+          <t>23-09-2026 14:28 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News (market report) for rare disease relevant to monitored companies</t>
+          <t>Clinical trials &amp; pipeline news, pipeline report for immunology/autoimmune disease (eczema)</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eczema Pipeline: Emerging Therapies and Key Developments Shaping the Treatment Landscape | DelveInsight</t>
+          <t>Could Faster Biosimilar Development Change the Economics of Biologic Drug Competition?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Kings Research</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4641457/eczema-pipeline-emerging-therapies-and-key-developments</t>
+          <t>https://www.kingsresearch.com/blog/future-of-biosimilar-development</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23-09-2026 14:32 UTC</t>
+          <t>23-09-2026 13:07 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News for a relevant specialty market (eczema/dermatology) from a monitored company</t>
+          <t>Biosimilars &amp; Biologics, industry commentary on biosimilar development</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -994,32 +994,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Polpharma Santo launches exports of Kazakhstan-made medicines to EU</t>
+          <t>Pyrogen-Free Dextrose Monohydrate Market To 2035: Biologics Demand Drives Expansion - News and Statistics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qazinform</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://qazinform.com/news/polpharma-santo-launches-exports-of-kazakhstan-made-medicines-to-eu-008830</t>
+          <t>https://www.indexbox.io/blog/pyrogen-free-dextrose-monohydrate-market-forecast-to-2035-growth-accelerates-on-biologics-and-injectable-drug-demand/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23-09-2026 05:46 UTC</t>
+          <t>23-09-2026 16:36 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Market Launches, Approvals &amp; Commercial Events (exports) for a monitored company active in biosimilars</t>
+          <t>Manufacturing, supply chain &amp; capacity, market research driven by biologics demand</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1027,39 +1027,39 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Multiple Sclerosis Pipeline 2026: FDA Updates, Therapy</t>
+          <t>Hospitals Told to Pull Two Lots of ICU Sedative Dexmedetomidine After Cellulose or Stopper Particles Were Found</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Medical Daily</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4640253/multiple-sclerosis-pipeline-2026-fda-updates-therapy</t>
+          <t>https://www.medicaldaily.com/dexmedetomidine-recall-par-health-particulate-matter-hospitals-478990</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23-09-2026 00:46 UTC</t>
+          <t>23-09-2026 14:15 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News for an autoimmune disease from a monitored company</t>
+          <t>Manufacturing, supply chain &amp; capacity, drug recall/quality issue for sterile injectable</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1067,39 +1067,39 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Advanz Pharma</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EU General Court Judgment in Case T-455/24 Advanz Pharma v Commission</t>
+          <t>Low-Adsorption Vials Market Forecast to 2035: Growth Driven by Biologics and LC-MS/MS Bioanalysis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INSIGHT EU MONITORING</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://ieu-monitoring.com/event/eu-general-court-judgment-in-case-t-455-24-advanz-pharma-v-commission</t>
+          <t>https://www.indexbox.io/blog/low-adsorption-vials-market-forecast-to-2035-growth-driven-by-biologics-and-lc-ms-ms-bioanalysis/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22-09-2026 23:39 UTC</t>
+          <t>23-09-2026 20:31 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FDA / REGULATORY ACTIONS for a monitored company</t>
+          <t>Manufacturing, supply chain &amp; capacity, market research driven by biologics demand</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1107,39 +1107,39 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>John Rim Builds Samsung Biologics Into a Global CDMO Powerhouse</t>
+          <t>Teva commits to lowering select Medicaid drug costs in US deal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인사이트코리아</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleViewAmp.html?idxno=255225</t>
+          <t>https://scanx.trade/stock-market-news/companies/teva-commits-lowering-select-medicaid-drug-costs-us-deal/49753721</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23-09-2026 04:36 UTC</t>
+          <t>23-09-2026 19:17 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (CDMO growth) for a monitored company</t>
+          <t>Monitored company Teva, market access/pricing action for drugs</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -1159,27 +1159,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Biopharmaceutical Manufacturing Market Is Going to Boom with</t>
+          <t>Experts discuss cutting biologic drug costs at BPI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>bioprocessintl.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4640517/biopharmaceutical-manufacturing-market-is-going-to-boom-with</t>
+          <t>https://www.bioprocessintl.com/economics/bpi-2026-panel-addresses-cost-challenges-at-bioprocess-international-event-in-boston</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23-09-2026 07:10 UTC</t>
+          <t>23-09-2026 16:46 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity market context for a monitored company</t>
+          <t>Biosimilars &amp; Biologics, discussion at industry meeting about biologic drug costs</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1215,7 +1215,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-09-2026 21:11:53</t>
+          <t>24-09-2026 13:41:43</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$275M Sandoz and Fougera antitrust class action settlement</t>
+          <t>Boehringer Ingelheim offloads Shanghai CDMO to local antibody developer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Top Class Actions</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://topclassactions.com/lawsuit-settlements/open-lawsuit-settlements/275m-sandoz-and-fougera-antitrust-class-action-settlement/</t>
+          <t>https://www.fiercepharma.com/pharma/boehringer-ingelheim-offloads-shanghai-cdmo-local-antibody-developer</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24-09-2026 04:48 UTC</t>
+          <t>24-09-2026 15:38 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company Sandoz, significant antitrust settlement (market event)</t>
+          <t>Manufacturing capacity deal involving antibody developer</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amgen's Dazodalibep Meets Primary Endpoint in Phase 3 Sjögren's Trial</t>
+          <t>Amgen says dazodalibep met Phase 3 Sjögren's endpoint</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>Mugglehead Investment Magazine</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.biopharminternational.com/view/amgen-dazodalibep-primary-endpoint-phase-3-sjogrens-trial</t>
+          <t>https://mugglehead.com/amgen-dazodalibep-oasiz-301-phase-3-sjogrens/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23-09-2026 15:46 UTC</t>
+          <t>23-09-2026 16:43 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company Amgen, clinical trial results for biologic in autoimmune disease</t>
+          <t>Clinical trial results for biologic in autoimmune disease (Sjögren's)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Coherus Oncology retains Oppenheimer to market legacy biosimilar assets</t>
+          <t>Glenmark’s Goa plant gets U.S. FDA EIR with VAI status after June inspection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>ETLegalWorld.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/the-fly/coherus-oncology-retains-oppenheimer-to-market-legacy-biosimilar-assets-thefly-news</t>
+          <t>https://legal.economictimes.indiatimes.com/news/corporate-business/glenmarks-goa-plant-gets-u-s-fda-eir-with-vai-status-after-june-inspection/134455139</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23-09-2026 14:39 UTC</t>
+          <t>24-09-2026 07:29 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company Coherus Biosciences, biosimilar commercial event</t>
+          <t>FDA inspection of a pharma manufacturing plant</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,7 +587,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
@@ -599,27 +599,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pfizer India removes products from Karnataka markets after spurious drugs crackdown</t>
+          <t>Pfizer India speaks up after Karnataka FDA crackdown, says patient safety is top priority</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/pfizer-india-removes-products-from-karnataka-markets-after-spurious-drugs-crackdown/article71498929.ece</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/pfizer-india-speaks-up-after-karnataka-fda-crackdown-says-patient-safety-is-top-priority/134449178</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23-09-2026 08:27 UTC</t>
+          <t>24-09-2026 01:37 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company Pfizer, regulatory action related to quality/supply chain</t>
+          <t>FDA action/crackdown on Pfizer India</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Global Vitiligo Treatment Market to Reach USD 2.97 Billion by 2034 at 5.8% CAGR as Rising Disease Prevalence, Growing Aesthetic Awareness, and Advances in Targeted Therapies Accelerate Market Growth, Reports Maximize Market Research</t>
+          <t>Zydus Life Bets on Innovation &amp; Specialty Drugs to Drive Growth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/global-vitiligo-treatment-market-to-reach-usd-2-97-billion-by-2034-at-5-8-cagr-as-rising-disease-prevalence-growing-aesthetic-awareness-and-advances-in-targeted-therapies-accelerate-market-growth-reports-maximize-market-resear-302887627.html</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/zydus-life-bets-on-innovation-specialty-drugs-to-drive-growth/134449035</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23-09-2026 21:45 UTC</t>
+          <t>24-09-2026 01:44 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics, market report for autoimmune disease (vitiligo) with targeted therapies</t>
+          <t>Monitored company's strategy mentioning specialty drugs (relevant for biologics/biosimilars)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intas Pharmaceuticals appoints Taranpreet Singh Lamba as Executive Vice President – Global IPR &amp; Portfolio, India &amp; Emerging Markets</t>
+          <t>Altruist Biologics preps for production following EMA GMP certification</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>BioProcess International</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/people/intas-pharmaceuticals-appoints-taranpreet-singh-lamba-as-executive-vice-president-global-ipr-portfolio-india-emerging-markets-21954</t>
+          <t>https://www.bioprocessintl.com/bioregions/altruist-biologics-preps-for-production-following-ema-gmp-certification</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23-09-2026 12:20 UTC</t>
+          <t>24-09-2026 04:55 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company Intas, corporate appointment for Global IPR &amp; Portfolio impacting biosimilar strategy</t>
+          <t>Biologic manufacturing EMA GMP certification</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Insulin Glargine Market Size to Reach US$ 14.52 Billion by 2035 as</t>
+          <t>Celltrion Renews EU-GMP Certification at Songdo Campus, Expands Production Capacity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>openpr.com</t>
+          <t>moomoo.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4641218/insulin-glargine-market-size-to-reach-us-14-52-billion-by-2035-as</t>
+          <t>https://www.moomoo.com/news/post/76573548/celltrion-renews-eu-gmp-certification-at-songdo-campus-expands-production</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23-09-2026 12:42 UTC</t>
+          <t>23-09-2026 21:41 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company Biocon, biosimilar market research (insulin glargine)</t>
+          <t>Biologic/biosimilar manufacturing EU-GMP certification and capacity expansion</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zydus Life Bets on Innovation &amp; Specialty Drugs to Drive Growth</t>
+          <t>Daiichi Sankyo expands Turbine collaboration to accelerate ADC discovery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/zydus-life-bets-on-innovation-specialty-drugs-to-drive-growth/134449035</t>
+          <t>https://manufacturingchemist.com/daiichi-sankyo-turbine-collaboration-accelerate-adc-discovery</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24-09-2026 01:44 UTC</t>
+          <t>24-09-2026 14:28 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored company Zydus Biotech, strategy for innovation and specialty drugs (biosimilars relevant)</t>
+          <t>Partnership for biologic (ADC) discovery</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Celltrion Wins US FDA Nod for RA Trial of Zymfentra</t>
+          <t>Pyrogen-Free Dextrose Monohydrate Market To 2035: Biologics Demand Drives Expansion - News and Statistics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/celltrion-wins-us-fda-nod-for-ra-trial-of-zymfentra-ce785ad9dc8dfe27</t>
+          <t>https://www.indexbox.io/blog/pyrogen-free-dextrose-monohydrate-market-forecast-to-2035-growth-accelerates-on-biologics-and-injectable-drug-demand/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23-09-2026 11:56 UTC</t>
+          <t>23-09-2026 16:36 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored company Celltrion, FDA nod for clinical trial of IBD biologic in autoimmune disease (RA)</t>
+          <t>Market trend driven by biologics demand (relevant to manufacturing/supply)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Turbine, Daiichi Sankyo Expand Virtual Biology Collaboration to Accelerate ADC Discovery</t>
+          <t>Low-Adsorption Vials Market Forecast to 2035: Growth Driven by Biologics and LC-MS/MS Bioanalysis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>biopharmaapac.com</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/41/8478/turbine-daiichi-sankyo-expand-virtual-biology-collaboration-to-accelerate-adc-discovery.html</t>
+          <t>https://www.indexbox.io/blog/low-adsorption-vials-market-forecast-to-2035-growth-driven-by-biologics-and-lc-ms-ms-bioanalysis/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24-09-2026 06:10 UTC</t>
+          <t>23-09-2026 20:31 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitored company Daiichi Sankyo, partnership for biologic (ADC) discovery</t>
+          <t>Market trend for drug delivery components (vials) driven by biologics</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Advanz Pharma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trastuzumab Rezetecan Improves Progression-Free Survival in Chemotherapy-Refractory HER2-Positive Advanced Colorectal Cancer</t>
+          <t>EU court backs withdrawal of liver drug’s conditional approval</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The ASCO Post</t>
+          <t>ICLG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://ascopost.com/news/september-2026/trastuzumab-rezetecan-improves-progression-free-survival-in-chemotherapy-refractory-her2-positive-advanced-colorectal-cancer/</t>
+          <t>https://iclg.com/news/eu-court-backs-withdrawal-of-liver-drugs-conditional-approval/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23-09-2026 19:12 UTC</t>
+          <t>24-09-2026 11:21 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news, monoclonal antibody (biologic) in oncology</t>
+          <t>Regulatory action (EU court backs withdrawal of conditional approval) for a drug</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,32 +914,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eczema Pipeline: Emerging Therapies and Key Developments Shaping the Treatment Landscape | DelveInsight</t>
+          <t>Teva, Wyeth Show How Claimed Advances Shape Enablement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4757719/eczema-pipeline-emerging-therapies-and-key-developments-shaping-the-treatment-landscape-delveinsight</t>
+          <t>https://www.law360.com/articles/2526719/teva-wyeth-show-how-claimed-advances-shape-enablement-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23-09-2026 14:28 UTC</t>
+          <t>23-09-2026 21:32 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news, pipeline report for immunology/autoimmune disease (eczema)</t>
+          <t>Patent law analysis (relevant to biologics/biosimilars)</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Could Faster Biosimilar Development Change the Economics of Biologic Drug Competition?</t>
+          <t>Teva commits to lowering select Medicaid drug costs in US deal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kings Research</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kingsresearch.com/blog/future-of-biosimilar-development</t>
+          <t>https://scanx.trade/stock-market-news/companies/teva-commits-lowering-select-medicaid-drug-costs-us-deal/49753721</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23-09-2026 13:07 UTC</t>
+          <t>23-09-2026 19:17 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics, industry commentary on biosimilar development</t>
+          <t>Market access/pricing deal for Teva in the US</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,39 +987,39 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pyrogen-Free Dextrose Monohydrate Market To 2035: Biologics Demand Drives Expansion - News and Statistics</t>
+          <t>BIX 2026 Names Canada as Country of Honor Showcasing Bioindustry Trends from BCI To Biotech Foods</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>businessnewsthisweek.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/pyrogen-free-dextrose-monohydrate-market-forecast-to-2035-growth-accelerates-on-biologics-and-injectable-drug-demand/</t>
+          <t>https://businessnewsthisweek.com/business/bix-2026-names-canada-as-country-of-honor-showcasing-bioindustry-trends-from-bci-to-biotech-foods/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23-09-2026 16:36 UTC</t>
+          <t>24-09-2026 06:59 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manufacturing, supply chain &amp; capacity, market research driven by biologics demand</t>
+          <t>Industry meeting/conference discussing bioindustry trends</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1034,32 +1034,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hospitals Told to Pull Two Lots of ICU Sedative Dexmedetomidine After Cellulose or Stopper Particles Were Found</t>
+          <t>Experts discuss cutting biologic drug costs at BPI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medical Daily</t>
+          <t>BioProcess International</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.medicaldaily.com/dexmedetomidine-recall-par-health-particulate-matter-hospitals-478990</t>
+          <t>https://www.bioprocessintl.com/economics/bpi-2026-panel-addresses-cost-challenges-at-bioprocess-international-event-in-boston</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23-09-2026 14:15 UTC</t>
+          <t>23-09-2026 16:46 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manufacturing, supply chain &amp; capacity, drug recall/quality issue for sterile injectable</t>
+          <t>Industry meeting discussing biologic drug costs</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1074,32 +1074,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Low-Adsorption Vials Market Forecast to 2035: Growth Driven by Biologics and LC-MS/MS Bioanalysis</t>
+          <t>The 10 Deals That Defined APAC Biopharma in 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/low-adsorption-vials-market-forecast-to-2035-growth-driven-by-biologics-and-lc-ms-ms-bioanalysis/</t>
+          <t>https://biopharmaapac.com/analysis/23/8472/the-10-deals-that-defined-apac-biopharma-in-2026.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23-09-2026 20:31 UTC</t>
+          <t>24-09-2026 03:29 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manufacturing, supply chain &amp; capacity, market research driven by biologics demand</t>
+          <t>Industry report on biopharma deals</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1107,87 +1107,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Teva commits to lowering select Medicaid drug costs in US deal</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://scanx.trade/stock-market-news/companies/teva-commits-lowering-select-medicaid-drug-costs-us-deal/49753721</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>23-09-2026 19:17 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Monitored company Teva, market access/pricing action for drugs</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
           <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Experts discuss cutting biologic drug costs at BPI</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>bioprocessintl.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessintl.com/economics/bpi-2026-panel-addresses-cost-challenges-at-bioprocess-international-event-in-boston</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>23-09-2026 16:46 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Biosimilars &amp; Biologics, discussion at industry meeting about biologic drug costs</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1135,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-09-2026 13:41:43</t>
+          <t>24-09-2026 21:35:12</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +484,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>fiercepharma.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manufacturing capacity deal involving antibody developer</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity; Partnerships, Deals, Licensing &amp; Acquisition (CDMO offload to antibody developer)</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amgen says dazodalibep met Phase 3 Sjögren's endpoint</t>
+          <t>Amgen Gains as Sjögren's Drug Clears Phase 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mugglehead Investment Magazine</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://mugglehead.com/amgen-dazodalibep-oasiz-301-phase-3-sjogrens/</t>
+          <t>https://www.gurufocus.com/news/9095786/amgen-gains-as-sjgrens-drug-clears-phase-3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23-09-2026 16:43 UTC</t>
+          <t>24-09-2026 19:18 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clinical trial results for biologic in autoimmune disease (Sjögren's)</t>
+          <t>Clinical Trials &amp; Pipeline News (Sjögren's drug, autoimmune disease)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glenmark’s Goa plant gets U.S. FDA EIR with VAI status after June inspection</t>
+          <t>The Biologics "Patent Cliff" Is Creating a New Leadership Talent War</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ETLegalWorld.com</t>
+          <t>ET HealthWorld</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/corporate-business/glenmarks-goa-plant-gets-u-s-fda-eir-with-vai-status-after-june-inspection/134455139</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/the-biologics-patent-cliff-is-creating-a-new-leadership-talent-war/134457629</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24-09-2026 07:29 UTC</t>
+          <t>25-09-2026 02:21 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FDA inspection of a pharma manufacturing plant</t>
+          <t>Biosimilars &amp; Biologics (Biologics 'Patent Cliff' impact on industry strategy)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pfizer India speaks up after Karnataka FDA crackdown, says patient safety is top priority</t>
+          <t>Generic Ozempic shortage at Quebec pharmacies amid recalls and skyrocketing demand</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>Montreal Gazette</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/pfizer-india-speaks-up-after-karnataka-fda-crackdown-says-patient-safety-is-top-priority/134449178</t>
+          <t>https://montrealgazette.com/news/health/generic-ozempic-out-of-stock-at-pharmacies-across-quebec-amid-recalls-and-skyrocketing-demand/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24-09-2026 01:37 UTC</t>
+          <t>24-09-2026 13:38 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FDA action/crackdown on Pfizer India</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity (shortage of a biologic/biosimilar)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zydus Life Bets on Innovation &amp; Specialty Drugs to Drive Growth</t>
+          <t>Plant Cell Culture Equipment Market To 2035: Biopharma Scale-Up and Synthetic Biology Drive Growth - News and Statistics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/zydus-life-bets-on-innovation-specialty-drugs-to-drive-growth/134449035</t>
+          <t>https://www.indexbox.io/blog/plant-cell-culture-equipment-market-forecast-to-2035-demand-accelerates-on-biopharma-scale-up-and-synthetic-biology-integration/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24-09-2026 01:44 UTC</t>
+          <t>24-09-2026 23:56 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company's strategy mentioning specialty drugs (relevant for biologics/biosimilars)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity (plant cell culture equipment for biopharma scale-up)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,32 +674,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Altruist Biologics preps for production following EMA GMP certification</t>
+          <t>Pfizer Says It Removed Affected Batches From Market Amid Karnataka Fake Drug Probe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BioProcess International</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.bioprocessintl.com/bioregions/altruist-biologics-preps-for-production-following-ema-gmp-certification</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/pfizer-says-it-removed-affected-batches-from-market-amid-karnataka-fake-drug-probe-179922</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24-09-2026 04:55 UTC</t>
+          <t>24-09-2026 16:21 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biologic manufacturing EMA GMP certification</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity (affected batches, fake drug probe)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celltrion Renews EU-GMP Certification at Songdo Campus, Expands Production Capacity</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>moomoo.com</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.moomoo.com/news/post/76573548/celltrion-renews-eu-gmp-certification-at-songdo-campus-expands-production</t>
+          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23-09-2026 21:41 UTC</t>
+          <t>25-09-2026 00:39 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Biologic/biosimilar manufacturing EU-GMP certification and capacity expansion</t>
+          <t>Clinical Trials &amp; Pipeline News (Pfizer's biologic vaccine); Market Launches, Approvals &amp; Commercial Events (Wegovy biologic commercialization)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo expands Turbine collaboration to accelerate ADC discovery</t>
+          <t>Pfizer plans cost cuts and new drugs to offset revenue loss from expiring patents by 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://manufacturingchemist.com/daiichi-sankyo-turbine-collaboration-accelerate-adc-discovery</t>
+          <t>https://pluang.com/en/news-feed/pfizer-berpotensi-naik-dengan-pipeline-obat-baru-dan-rencana-penghematan-biaya</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24-09-2026 14:28 UTC</t>
+          <t>24-09-2026 20:07 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Partnership for biologic (ADC) discovery</t>
+          <t>Earnings &amp; Financial Reports (pipeline strategy to offset patent expiry, including biologics/biosimilars); Biosimilars &amp; Biologics (patent strategy)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pyrogen-Free Dextrose Monohydrate Market To 2035: Biologics Demand Drives Expansion - News and Statistics</t>
+          <t>[Big read] Big Pharma bets billions on China biotech — will Washington pull the plug?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>ThinkChina</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/pyrogen-free-dextrose-monohydrate-market-forecast-to-2035-growth-accelerates-on-biologics-and-injectable-drug-demand/</t>
+          <t>https://www.thinkchina.sg/economy/big-read-big-pharma-bets-billions-china-biotech-will-washington-pull-plug</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23-09-2026 16:36 UTC</t>
+          <t>25-09-2026 06:19 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Market trend driven by biologics demand (relevant to manufacturing/supply)</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition (Big Pharma investment in biotech)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Low-Adsorption Vials Market Forecast to 2035: Growth Driven by Biologics and LC-MS/MS Bioanalysis</t>
+          <t>Global Autoimmune Disease Therapeutics Market is Predicted to Cross USD 60 Billion by 2034 | DelveInsight</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/low-adsorption-vials-market-forecast-to-2035-growth-driven-by-biologics-and-lc-ms-ms-bioanalysis/</t>
+          <t>https://businessupturn.com/brand-post/global-autoimmune-disease-therapeutics-market-is-predicted-to-cross-usd-60-billion-by-2034-delveinsight/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23-09-2026 20:31 UTC</t>
+          <t>24-09-2026 18:25 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Market trend for drug delivery components (vials) driven by biologics</t>
+          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (autoimmune disease therapeutics market)</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advanz Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EU court backs withdrawal of liver drug’s conditional approval</t>
+          <t>Dr. Reddy's faces securities fraud probe after Q1 earnings hit by semaglutide batch issues.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ICLG</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://iclg.com/news/eu-court-backs-withdrawal-of-liver-drugs-conditional-approval/</t>
+          <t>https://pluang.com/en/news-feed/peringatan-investor-pomerantz-investigasi-dr-reddys-laboratories</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24-09-2026 11:21 UTC</t>
+          <t>24-09-2026 22:57 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Regulatory action (EU court backs withdrawal of conditional approval) for a drug</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity; Earnings &amp; Financial Reports (semaglutide batch issues affecting earnings)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,32 +914,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teva, Wyeth Show How Claimed Advances Shape Enablement</t>
+          <t>Pharma Supply Chains in Flux: Navigating Tariffs, Trade and Geopolitics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.law360.com/articles/2526719/teva-wyeth-show-how-claimed-advances-shape-enablement-</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/supply-chain-and-logistics/pharma-supply-chains-in-flux-navigating-tariffs-trade-and-geopolitics/134467410</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23-09-2026 21:32 UTC</t>
+          <t>24-09-2026 17:30 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Patent law analysis (relevant to biologics/biosimilars)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity (pharma supply chains, includes biologics/biosimilars)</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Teva commits to lowering select Medicaid drug costs in US deal</t>
+          <t>Biocon Malaysia Unit Gets UK MHRA Nod For Insulin Line</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Equitypandit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/teva-commits-lowering-select-medicaid-drug-costs-us-deal/49753721</t>
+          <t>https://www.equitypandit.com/biocon-malaysia-unit-gets-uk-mhra-nod-for-insulin-line/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23-09-2026 19:17 UTC</t>
+          <t>25-09-2026 07:32 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Market access/pricing deal for Teva in the US</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity; FDA / Regulatory Actions (MHRA approval for insulin fill-finish line)</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,39 +987,39 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIX 2026 Names Canada as Country of Honor Showcasing Bioindustry Trends from BCI To Biotech Foods</t>
+          <t>Malaysia's IHH's unit appeals dismissal of Daiichi Sankyo damages claim</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>businessnewsthisweek.com</t>
+          <t>ET HealthWorld</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://businessnewsthisweek.com/business/bix-2026-names-canada-as-country-of-honor-showcasing-bioindustry-trends-from-bci-to-biotech-foods/</t>
+          <t>https://health.economictimes.indiatimes.com/amp/news/hospitals/malaysias-ihhs-unit-appeals-dismissal-of-daiichi-sankyo-damages-claim/134473019</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24-09-2026 06:59 UTC</t>
+          <t>25-09-2026 02:09 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Industry meeting/conference discussing bioindustry trends</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition (litigation arising from major acquisition by monitored company)</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1027,39 +1027,39 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Experts discuss cutting biologic drug costs at BPI</t>
+          <t>Daiichi Sankyo expands Turbine collaboration to accelerate ADC discovery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BioProcess International</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.bioprocessintl.com/economics/bpi-2026-panel-addresses-cost-challenges-at-bioprocess-international-event-in-boston</t>
+          <t>https://manufacturingchemist.com/daiichi-sankyo-turbine-collaboration-accelerate-adc-discovery</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23-09-2026 16:46 UTC</t>
+          <t>24-09-2026 19:13 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Industry meeting discussing biologic drug costs</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition; Clinical Trials &amp; Pipeline News (ADC discovery collaboration for biologics)</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1067,47 +1067,207 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pharmaceutical Policy in Motion Continued: The Trump Administration’s Second Wave of Drug Pricing Deals</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JD Supra</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.jdsupra.com/legalnews/pharmaceutical-policy-in-motion-9056020/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>24-09-2026 14:36 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (pharmaceutical policy on drug pricing affecting market access)</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Moderate to Severe Atopic Dermatitis Market Set for Robust</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4643108/moderate-to-severe-atopic-dermatitis-market-set-for-robust</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>24-09-2026 19:23 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (atopic dermatitis market, immunology/dermatology relevant)</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Global Multiple Sclerosis Treatment Market to Grow at 5.8% CAGR, Reaching USD 44.45 Billion by 2034 as Advanced Therapies and Disease-Modifying Treatments Gain Momentum, Says Maximize Market Research</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/global-multiple-sclerosis-treatment-market-to-grow-at-5-8-cagr-reaching-usd-44-45-billion-by-2034-as-advanced-therapies-and-disease-modifying-treatments-gain-momentum-says-maximize-market-research-302889376.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>24-09-2026 21:30 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (multiple sclerosis treatment market, autoimmune disease, advanced therapies/biologics)</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Global Autoimmune Treatment Market to Reach USD 321.95 Billion by 2034, Driven by Rising Prevalence of Autoimmune Diseases, Growing Adoption of Biologics, and Advances in Precision Medicine Says Maximize Market Research</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PR Newswire UK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.co.uk/news-releases/global-autoimmune-treatment-market-to-reach-usd-321-95-billion-by-2034--driven-by-rising-prevalence-of-autoimmune-diseases-growing-adoption-of-biologics-and-advances-in-precision-medicine-says-maximize-market-research-302889262.html</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>24-09-2026 22:15 UTC</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (autoimmune treatment market, adoption of biologics)</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The 10 Deals That Defined APAC Biopharma in 2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BioPharma APAC</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://biopharmaapac.com/analysis/23/8472/the-10-deals-that-defined-apac-biopharma-in-2026.html</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>24-09-2026 03:29 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Industry report on biopharma deals</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chromatography Systems Market To 2035: Biologics Demand Drives Forward Growth - News and Statistics</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/chromatography-systems-market-forecast-to-2035-growth-accelerates-on-biologics-pipeline-expansion/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>25-09-2026 05:41 UTC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (chromatography systems market driven by biologics demand)</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1295,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-09-2026 21:35:12</t>
+          <t>25-09-2026 14:03:27</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim offloads Shanghai CDMO to local antibody developer</t>
+          <t>Amgen Gains as Sjögren's Drug Clears Phase 3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fiercepharma.com</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/boehringer-ingelheim-offloads-shanghai-cdmo-local-antibody-developer</t>
+          <t>https://www.gurufocus.com/news/9095786/amgen-gains-as-sjgrens-drug-clears-phase-3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24-09-2026 15:38 UTC</t>
+          <t>24-09-2026 19:18 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity; Partnerships, Deals, Licensing &amp; Acquisition (CDMO offload to antibody developer)</t>
+          <t>Clinical Trials &amp; Pipeline News: autoimmune disease biologic from monitored company</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amgen Gains as Sjögren's Drug Clears Phase 3</t>
+          <t>The Biologics "Patent Cliff" Is Creating a New Leadership Talent War</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>ET HealthWorld</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/9095786/amgen-gains-as-sjgrens-drug-clears-phase-3</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/the-biologics-patent-cliff-is-creating-a-new-leadership-talent-war/134457629</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24-09-2026 19:18 UTC</t>
+          <t>25-09-2026 02:21 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News (Sjögren's drug, autoimmune disease)</t>
+          <t>Biosimilars &amp; Biologics: patent cliff discussion affecting biologics market</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Biologics "Patent Cliff" Is Creating a New Leadership Talent War</t>
+          <t>Pfizer Says It Removed Affected Batches From Market Amid Karnataka Fake Drug Probe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ET HealthWorld</t>
+          <t>medicaldialogues.in</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/the-biologics-patent-cliff-is-creating-a-new-leadership-talent-war/134457629</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/pfizer-says-it-removed-affected-batches-from-market-amid-karnataka-fake-drug-probe-179922</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25-09-2026 02:21 UTC</t>
+          <t>24-09-2026 16:21 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics (Biologics 'Patent Cliff' impact on industry strategy)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: quality issue for monitored company</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Generic Ozempic shortage at Quebec pharmacies amid recalls and skyrocketing demand</t>
+          <t>Pfizer plans cost cuts and new drugs to offset revenue loss from expiring patents by 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montreal Gazette</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://montrealgazette.com/news/health/generic-ozempic-out-of-stock-at-pharmacies-across-quebec-amid-recalls-and-skyrocketing-demand/</t>
+          <t>https://pluang.com/en/news-feed/pfizer-berpotensi-naik-dengan-pipeline-obat-baru-dan-rencana-penghematan-biaya</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24-09-2026 13:38 UTC</t>
+          <t>24-09-2026 20:07 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (shortage of a biologic/biosimilar)</t>
+          <t>Biosimilars &amp; Biologics: market strategy (patent expiry, new drugs)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plant Cell Culture Equipment Market To 2035: Biopharma Scale-Up and Synthetic Biology Drive Growth - News and Statistics</t>
+          <t>[Big read] Big Pharma bets billions on China biotech — will Washington pull the plug?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>ThinkChina</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/plant-cell-culture-equipment-market-forecast-to-2035-demand-accelerates-on-biopharma-scale-up-and-synthetic-biology-integration/</t>
+          <t>https://www.thinkchina.sg/economy/big-read-big-pharma-bets-billions-china-biotech-will-washington-pull-plug?ref=top-hero</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24-09-2026 23:56 UTC</t>
+          <t>25-09-2026 06:19 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (plant cell culture equipment for biopharma scale-up)</t>
+          <t>Biosimilars &amp; Biologics: market event (macro investment trend in biotech)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pfizer Says It Removed Affected Batches From Market Amid Karnataka Fake Drug Probe</t>
+          <t>Global Autoimmune Disease Therapeutics Market is Predicted to Cross USD 60 Billion by 2034 | DelveInsight</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/pfizer-says-it-removed-affected-batches-from-market-amid-karnataka-fake-drug-probe-179922</t>
+          <t>https://businessupturn.com/brand-post/global-autoimmune-disease-therapeutics-market-is-predicted-to-cross-usd-60-billion-by-2034-delveinsight/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24-09-2026 16:21 UTC</t>
+          <t>24-09-2026 18:25 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (affected batches, fake drug probe)</t>
+          <t>Biosimilars &amp; Biologics: market report (autoimmune disease therapeutics)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Dr. Reddy's faces securities fraud probe after Q1 earnings hit by semaglutide batch issues.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
+          <t>https://pluang.com/en/news-feed/peringatan-investor-pomerantz-investigasi-dr-reddys-laboratories</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25-09-2026 00:39 UTC</t>
+          <t>24-09-2026 22:57 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News (Pfizer's biologic vaccine); Market Launches, Approvals &amp; Commercial Events (Wegovy biologic commercialization)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: quality issue (batch issues) affecting a monitored company</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pfizer plans cost cuts and new drugs to offset revenue loss from expiring patents by 2026</t>
+          <t>Biocon Malaysia Unit Gets UK MHRA Nod For Insulin Line</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Equitypandit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/pfizer-berpotensi-naik-dengan-pipeline-obat-baru-dan-rencana-penghematan-biaya</t>
+          <t>https://www.equitypandit.com/biocon-malaysia-unit-gets-uk-mhra-nod-for-insulin-line/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24-09-2026 20:07 UTC</t>
+          <t>25-09-2026 07:32 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Earnings &amp; Financial Reports (pipeline strategy to offset patent expiry, including biologics/biosimilars); Biosimilars &amp; Biologics (patent strategy)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: regulatory approval for fill-finish line for a monitored company</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Big read] Big Pharma bets billions on China biotech — will Washington pull the plug?</t>
+          <t>PLI Scheme for Bulk Drugs for Resilient Pharmaceutical Supply Chain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ThinkChina</t>
+          <t>PIB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.thinkchina.sg/economy/big-read-big-pharma-bets-billions-china-biotech-will-washington-pull-plug</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2314891</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25-09-2026 06:19 UTC</t>
+          <t>25-09-2026 11:06 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition (Big Pharma investment in biotech)</t>
+          <t>FDA / Regulatory Actions: policy change affecting pharmaceutical supply chain</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Global Autoimmune Disease Therapeutics Market is Predicted to Cross USD 60 Billion by 2034 | DelveInsight</t>
+          <t>Fortis Healthcare: NTK Appeals Tokyo Court Ruling in Daiichi Sankyo Case to High Court</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/brand-post/global-autoimmune-disease-therapeutics-market-is-predicted-to-cross-usd-60-billion-by-2034-delveinsight/</t>
+          <t>https://www.sahi.com/news/fortis-healthcare-ntk-appeals-tokyo-court-ruling-in-daiichi-sankyo-case-to-high-court</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24-09-2026 18:25 UTC</t>
+          <t>25-09-2026 11:12 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (autoimmune disease therapeutics market)</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition: major legal dispute for monitored company</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dr. Reddy's faces securities fraud probe after Q1 earnings hit by semaglutide batch issues.</t>
+          <t>Daiichi Sankyo expands Turbine collaboration to accelerate ADC discovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/peringatan-investor-pomerantz-investigasi-dr-reddys-laboratories</t>
+          <t>https://manufacturingchemist.com/daiichi-sankyo-turbine-collaboration-accelerate-adc-discovery</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24-09-2026 22:57 UTC</t>
+          <t>24-09-2026 19:13 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity; Earnings &amp; Financial Reports (semaglutide batch issues affecting earnings)</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition: biologics collaboration for ADC discovery</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pharma Supply Chains in Flux: Navigating Tariffs, Trade and Geopolitics</t>
+          <t>Moderate to Severe Atopic Dermatitis Market Set for Robust</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/supply-chain-and-logistics/pharma-supply-chains-in-flux-navigating-tariffs-trade-and-geopolitics/134467410</t>
+          <t>https://www.openpr.com/news/4643108/moderate-to-severe-atopic-dermatitis-market-set-for-robust</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24-09-2026 17:30 UTC</t>
+          <t>24-09-2026 19:23 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (pharma supply chains, includes biologics/biosimilars)</t>
+          <t>Biosimilars &amp; Biologics: market report (autoimmune disease therapeutics)</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Biocon Malaysia Unit Gets UK MHRA Nod For Insulin Line</t>
+          <t>Two Wilson County Grads Turn a Night Class Into Jobs at Johnson &amp; Johnson's New Biologics Plant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Equitypandit</t>
+          <t>BioBuzz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/biocon-malaysia-unit-gets-uk-mhra-nod-for-insulin-line/</t>
+          <t>https://biobuzz.io/news/two-wilson-county-grads-turn-a-night-class-into-jobs-at-johnson-johnsons-new-biologics-plant/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25-09-2026 07:32 UTC</t>
+          <t>25-09-2026 13:12 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity; FDA / Regulatory Actions (MHRA approval for insulin fill-finish line)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: new biologics plant</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -994,32 +994,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Malaysia's IHH's unit appeals dismissal of Daiichi Sankyo damages claim</t>
+          <t>Global Multiple Sclerosis Treatment Market to Grow at 5.8% CAGR, Reaching USD 44.45 Billion by 2034 as Advanced Therapies and Disease-Modifying Treatments Gain Momentum, Says Maximize Market Research</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ET HealthWorld</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/amp/news/hospitals/malaysias-ihhs-unit-appeals-dismissal-of-daiichi-sankyo-damages-claim/134473019</t>
+          <t>https://www.prnewswire.com/news-releases/global-multiple-sclerosis-treatment-market-to-grow-at-5-8-cagr-reaching-usd-44-45-billion-by-2034-as-advanced-therapies-and-disease-modifying-treatments-gain-momentum-says-maximize-market-research-302889376.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25-09-2026 02:09 UTC</t>
+          <t>24-09-2026 21:30 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition (litigation arising from major acquisition by monitored company)</t>
+          <t>Biosimilars &amp; Biologics: market report (autoimmune disease therapeutics)</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1034,32 +1034,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo expands Turbine collaboration to accelerate ADC discovery</t>
+          <t>Samsung Bioepis Limits Nexatecan3 License to Three Drug Candidates</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://manufacturingchemist.com/daiichi-sankyo-turbine-collaboration-accelerate-adc-discovery</t>
+          <t>https://en.sedaily.com/finance/2026/09/25/samsung-bioepis-limits-nexatecan3-license-to-three-drug</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24-09-2026 19:13 UTC</t>
+          <t>25-09-2026 05:17 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition; Clinical Trials &amp; Pipeline News (ADC discovery collaboration for biologics)</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition: biologics licensing deal for a monitored company</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1074,32 +1074,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pharmaceutical Policy in Motion Continued: The Trump Administration’s Second Wave of Drug Pricing Deals</t>
+          <t>Global Autoimmune Treatment Market to Reach USD 321.95 Billion by 2034, Driven by Rising Prevalence of Autoimmune Diseases, Growing Adoption of Biologics, and Advances in Precision Medicine Says Maximize Market Research</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JD Supra</t>
+          <t>PR Newswire UK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.jdsupra.com/legalnews/pharmaceutical-policy-in-motion-9056020/</t>
+          <t>https://www.prnewswire.co.uk/news-releases/global-autoimmune-treatment-market-to-reach-usd-321-95-billion-by-2034--driven-by-rising-prevalence-of-autoimmune-diseases-growing-adoption-of-biologics-and-advances-in-precision-medicine-says-maximize-market-research-302889262.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24-09-2026 14:36 UTC</t>
+          <t>24-09-2026 22:15 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (pharmaceutical policy on drug pricing affecting market access)</t>
+          <t>Biosimilars &amp; Biologics: market report (autoimmune disease therapeutics, biologics adoption)</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1107,39 +1107,39 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Moderate to Severe Atopic Dermatitis Market Set for Robust</t>
+          <t>Chromatography Systems Market To 2035: Biologics Demand Drives Forward Growth - News and Statistics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>indexbox.io</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4643108/moderate-to-severe-atopic-dermatitis-market-set-for-robust</t>
+          <t>https://www.indexbox.io/blog/chromatography-systems-market-forecast-to-2035-growth-accelerates-on-biologics-pipeline-expansion/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24-09-2026 19:23 UTC</t>
+          <t>25-09-2026 05:41 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (atopic dermatitis market, immunology/dermatology relevant)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: biologics demand driving manufacturing equipment market</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1147,39 +1147,39 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Global Multiple Sclerosis Treatment Market to Grow at 5.8% CAGR, Reaching USD 44.45 Billion by 2034 as Advanced Therapies and Disease-Modifying Treatments Gain Momentum, Says Maximize Market Research</t>
+          <t>Six Industry Leaders Take the Stage in Rockville to Share Lessons on Quality, Manufacturing, and Scale</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>BioBuzz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/global-multiple-sclerosis-treatment-market-to-grow-at-5-8-cagr-reaching-usd-44-45-billion-by-2034-as-advanced-therapies-and-disease-modifying-treatments-gain-momentum-says-maximize-market-research-302889376.html</t>
+          <t>https://biobuzz.io/news/six-industry-leaders-take-the-stage-in-rockville-to-share-lessons-on-quality-manufacturing-and-scale/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24-09-2026 21:30 UTC</t>
+          <t>25-09-2026 14:19 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (multiple sclerosis treatment market, autoimmune disease, advanced therapies/biologics)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: industry event discussing quality, manufacturing, scale for biologics</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1187,85 +1187,45 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Global Autoimmune Treatment Market to Reach USD 321.95 Billion by 2034, Driven by Rising Prevalence of Autoimmune Diseases, Growing Adoption of Biologics, and Advances in Precision Medicine Says Maximize Market Research</t>
+          <t>Rapid Microbial-Detection Systems Market Forecast to 2035: Growth Accelerates on Biopharma QC Timelines</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PR Newswire UK</t>
+          <t>indexbox.io</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.co.uk/news-releases/global-autoimmune-treatment-market-to-reach-usd-321-95-billion-by-2034--driven-by-rising-prevalence-of-autoimmune-diseases-growing-adoption-of-biologics-and-advances-in-precision-medicine-says-maximize-market-research-302889262.html</t>
+          <t>https://www.indexbox.io/blog/rapid-microbial-detection-systems-market-forecast-to-2035-growth-accelerates-on-biopharma-qc-timelines/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24-09-2026 22:15 UTC</t>
+          <t>24-09-2026 20:41 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics; Market Launches, Approvals &amp; Commercial Events (autoimmune treatment market, adoption of biologics)</t>
+          <t>Manufacturing, Supply Chain &amp; Capacity: biopharma QC and microbial detection systems</t>
         </is>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Chromatography Systems Market To 2035: Biologics Demand Drives Forward Growth - News and Statistics</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>IndexBox</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/chromatography-systems-market-forecast-to-2035-growth-accelerates-on-biologics-pipeline-expansion/</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>25-09-2026 05:41 UTC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (chromatography systems market driven by biologics demand)</t>
-        </is>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
@@ -1295,7 +1255,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-09-2026 14:03:27</t>
+          <t>25-09-2026 21:34:27</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amgen Gains as Sjögren's Drug Clears Phase 3</t>
+          <t>Viatris Appoints Joe Paul Philip to Lead Manufacturing Science and Technology in Three Markets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>konsulteer.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/9095786/amgen-gains-as-sjgrens-drug-clears-phase-3</t>
+          <t>https://www.konsulteer.com/article/viatris-appoints-joe-paul-philip-to-lead-manufacturing-science-and-technology-in-three-markets</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24-09-2026 19:18 UTC</t>
+          <t>25-09-2026 13:19 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News: autoimmune disease biologic from monitored company</t>
+          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - leadership appointment in manufacturing science</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Biologics "Patent Cliff" Is Creating a New Leadership Talent War</t>
+          <t>Yaron Werber: Celldex's Urticaria Drug Won't Carry a Black Box; Amgen Maps a $25 Billion Sjogren's Market</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ET HealthWorld</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/the-biologics-patent-cliff-is-creating-a-new-leadership-talent-war/134457629</t>
+          <t>https://finance.biggo.com/news/75b4a2731f15e785</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25-09-2026 02:21 UTC</t>
+          <t>25-09-2026 21:11 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: patent cliff discussion affecting biologics market</t>
+          <t>Monitored companies; Clinical Trials &amp; Pipeline News - Amgen activity in autoimmune disease market</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pfizer Says It Removed Affected Batches From Market Amid Karnataka Fake Drug Probe</t>
+          <t>AMGN Jumps After Win In Sjögren’s Disease Trial As Citi Flags ‘Open Questions’</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>medicaldialogues.in</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/pfizer-says-it-removed-affected-batches-from-market-amid-karnataka-fake-drug-probe-179922</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/amgn-jumps-after-win-in-sjoegren-s-disease-trial-as-citi-flags-open-questions/cZMPwKgRB7B</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24-09-2026 16:21 UTC</t>
+          <t>26-09-2026 02:48 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: quality issue for monitored company</t>
+          <t>Monitored companies; Clinical Trials &amp; Pipeline News - autoimmune disease trial win</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pfizer plans cost cuts and new drugs to offset revenue loss from expiring patents by 2026</t>
+          <t>Mylan asks US court to clear Wegovy generic from Novo patent claims</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/pfizer-berpotensi-naik-dengan-pipeline-obat-baru-dan-rencana-penghematan-biaya</t>
+          <t>https://www.reuters.com/legal/legalindustry/mylan-asks-us-court-clear-wegovy-generic-novo-patent-claims-2026-09-25/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24-09-2026 20:07 UTC</t>
+          <t>25-09-2026 19:23 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: market strategy (patent expiry, new drugs)</t>
+          <t>Monitored companies; Biosimilars &amp; Biologics - patent litigation for specialty injectable (Wegovy)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Big read] Big Pharma bets billions on China biotech — will Washington pull the plug?</t>
+          <t>Squires Says Biocon Challenge To Eylea Patent Filed Too Late</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ThinkChina</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.thinkchina.sg/economy/big-read-big-pharma-bets-billions-china-biotech-will-washington-pull-plug?ref=top-hero</t>
+          <t>https://www.law360.com/publicpolicy/articles/2530219/squires-says-biocon-challenge-to-eylea-patent-filed-too-late</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25-09-2026 06:19 UTC</t>
+          <t>25-09-2026 22:37 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: market event (macro investment trend in biotech)</t>
+          <t>Monitored companies; Biosimilars &amp; Biologics - patent litigation for biologic (Eylea)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,32 +674,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Global Autoimmune Disease Therapeutics Market is Predicted to Cross USD 60 Billion by 2034 | DelveInsight</t>
+          <t>Biocon Malaysia gets UK MHRA approval for new drug product fill-finish unit for insulins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/brand-post/global-autoimmune-disease-therapeutics-market-is-predicted-to-cross-usd-60-billion-by-2034-delveinsight/</t>
+          <t>https://www.thehindubusinessline.com/companies/biocon-malaysia-gets-uk-mhra-approval-for-new-drug-product-fill-finish-unit-for-insulins/article71507863.ece/amp/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24-09-2026 18:25 UTC</t>
+          <t>25-09-2026 09:49 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: market report (autoimmune disease therapeutics)</t>
+          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - MHRA approval for biologic/biosimilar fill-finish unit</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dr. Reddy's faces securities fraud probe after Q1 earnings hit by semaglutide batch issues.</t>
+          <t>Zydus Lifesciences USA Office Clears USFDA Inspection With Nil Observations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Free Press Journal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/peringatan-investor-pomerantz-investigasi-dr-reddys-laboratories</t>
+          <t>https://www.freepressjournal.in/business/zydus-lifesciences-usa-office-clears-usfda-inspection-with-nil-observations</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24-09-2026 22:57 UTC</t>
+          <t>26-09-2026 07:07 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: quality issue (batch issues) affecting a monitored company</t>
+          <t>Monitored companies; FDA / Regulatory Actions - FDA inspection with nil observations</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Biocon Malaysia Unit Gets UK MHRA Nod For Insulin Line</t>
+          <t>Merck &amp; Co., Daiichi withdraw US submission for ADC in lung cancer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Equitypandit</t>
+          <t>FirstWord</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/biocon-malaysia-unit-gets-uk-mhra-nod-for-insulin-line/</t>
+          <t>https://firstwordpharma.com/story/8102182</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25-09-2026 07:32 UTC</t>
+          <t>26-09-2026 00:11 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: regulatory approval for fill-finish line for a monitored company</t>
+          <t>Monitored companies; FDA / Regulatory Actions - BLA withdrawal for biologic (ADC) in oncology</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PLI Scheme for Bulk Drugs for Resilient Pharmaceutical Supply Chain</t>
+          <t>Vials Market To 2035: Biologics Demand Drives Growth in Sterile Packaging - News and Statistics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PIB</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2314891</t>
+          <t>https://www.indexbox.io/blog/vials-market-forecast-to-2035-biologics-demand-drives-growth-in-sterile-packaging/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25-09-2026 11:06 UTC</t>
+          <t>25-09-2026 23:11 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions: policy change affecting pharmaceutical supply chain</t>
+          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - biologics demand affecting sterile packaging market</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fortis Healthcare: NTK Appeals Tokyo Court Ruling in Daiichi Sankyo Case to High Court</t>
+          <t>CE-SDS / icIEF Systems Market To 2035: Biologics Demand Drives Expansion - News and Statistics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/fortis-healthcare-ntk-appeals-tokyo-court-ruling-in-daiichi-sankyo-case-to-high-court</t>
+          <t>https://www.indexbox.io/blog/ce-sds-icief-systems-market-forecast-to-2035-growth-accelerates-on-rising-biologics-characterization-demand/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25-09-2026 11:12 UTC</t>
+          <t>25-09-2026 23:01 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition: major legal dispute for monitored company</t>
+          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - biologics demand affecting characterization systems market</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo expands Turbine collaboration to accelerate ADC discovery</t>
+          <t>The 10 Deals That Defined APAC Biopharma in 2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://manufacturingchemist.com/daiichi-sankyo-turbine-collaboration-accelerate-adc-discovery</t>
+          <t>https://biopharmaapac.com/analysis/73/8472/the-10-deals-that-defined-apac-biopharma-in-2026.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24-09-2026 19:13 UTC</t>
+          <t>25-09-2026 15:25 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition: biologics collaboration for ADC discovery</t>
+          <t>Monitored companies; Partnerships, Deals, Licensing &amp; Acquisition - deals in biopharma</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,318 +914,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Moderate to Severe Atopic Dermatitis Market Set for Robust</t>
+          <t>Six Industry Leaders Take the Stage in Rockville to Share Lessons on Quality, Manufacturing, and Scale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>biobuzz.io</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4643108/moderate-to-severe-atopic-dermatitis-market-set-for-robust</t>
+          <t>https://biobuzz.io/news/six-industry-leaders-take-the-stage-in-rockville-to-share-lessons-on-quality-manufacturing-and-scale/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24-09-2026 19:23 UTC</t>
+          <t>25-09-2026 14:19 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics: market report (autoimmune disease therapeutics)</t>
+          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - discussion on biologics manufacturing and quality</t>
         </is>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Two Wilson County Grads Turn a Night Class Into Jobs at Johnson &amp; Johnson's New Biologics Plant</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>BioBuzz</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://biobuzz.io/news/two-wilson-county-grads-turn-a-night-class-into-jobs-at-johnson-johnsons-new-biologics-plant/</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>25-09-2026 13:12 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: new biologics plant</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Global Multiple Sclerosis Treatment Market to Grow at 5.8% CAGR, Reaching USD 44.45 Billion by 2034 as Advanced Therapies and Disease-Modifying Treatments Gain Momentum, Says Maximize Market Research</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>prnewswire.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.prnewswire.com/news-releases/global-multiple-sclerosis-treatment-market-to-grow-at-5-8-cagr-reaching-usd-44-45-billion-by-2034-as-advanced-therapies-and-disease-modifying-treatments-gain-momentum-says-maximize-market-research-302889376.html</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>24-09-2026 21:30 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Biosimilars &amp; Biologics: market report (autoimmune disease therapeutics)</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis Limits Nexatecan3 License to Three Drug Candidates</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Seoul Economic Daily</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://en.sedaily.com/finance/2026/09/25/samsung-bioepis-limits-nexatecan3-license-to-three-drug</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>25-09-2026 05:17 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition: biologics licensing deal for a monitored company</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Global Autoimmune Treatment Market to Reach USD 321.95 Billion by 2034, Driven by Rising Prevalence of Autoimmune Diseases, Growing Adoption of Biologics, and Advances in Precision Medicine Says Maximize Market Research</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PR Newswire UK</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.prnewswire.co.uk/news-releases/global-autoimmune-treatment-market-to-reach-usd-321-95-billion-by-2034--driven-by-rising-prevalence-of-autoimmune-diseases-growing-adoption-of-biologics-and-advances-in-precision-medicine-says-maximize-market-research-302889262.html</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>24-09-2026 22:15 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Biosimilars &amp; Biologics: market report (autoimmune disease therapeutics, biologics adoption)</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Chromatography Systems Market To 2035: Biologics Demand Drives Forward Growth - News and Statistics</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>indexbox.io</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/chromatography-systems-market-forecast-to-2035-growth-accelerates-on-biologics-pipeline-expansion/</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>25-09-2026 05:41 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: biologics demand driving manufacturing equipment market</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Six Industry Leaders Take the Stage in Rockville to Share Lessons on Quality, Manufacturing, and Scale</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>BioBuzz</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://biobuzz.io/news/six-industry-leaders-take-the-stage-in-rockville-to-share-lessons-on-quality-manufacturing-and-scale/</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>25-09-2026 14:19 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: industry event discussing quality, manufacturing, scale for biologics</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Rapid Microbial-Detection Systems Market Forecast to 2035: Growth Accelerates on Biopharma QC Timelines</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>indexbox.io</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/rapid-microbial-detection-systems-market-forecast-to-2035-growth-accelerates-on-biopharma-qc-timelines/</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>24-09-2026 20:41 UTC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity: biopharma QC and microbial detection systems</t>
-        </is>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
@@ -1255,7 +975,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-09-2026 21:34:27</t>
+          <t>26-09-2026 13:49:29</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Viatris Appoints Joe Paul Philip to Lead Manufacturing Science and Technology in Three Markets</t>
+          <t>Growth Hormones Market Forecast to 2035: Demand Accelerates on Pediatric and Adult Deficiency Treatments</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>konsulteer.com</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.konsulteer.com/article/viatris-appoints-joe-paul-philip-to-lead-manufacturing-science-and-technology-in-three-markets</t>
+          <t>https://www.indexbox.io/blog/growth-hormones-market-forecast-to-2035-demand-accelerates-on-pediatric-and-adult-deficiency-treatments/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25-09-2026 13:19 UTC</t>
+          <t>25-09-2026 23:36 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - leadership appointment in manufacturing science</t>
+          <t>Biologics &amp; Biosimilars market trend (growth hormones are biologics) for monitored company</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25-09-2026 21:11 UTC</t>
+          <t>25-09-2026 21:08 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored companies; Clinical Trials &amp; Pipeline News - Amgen activity in autoimmune disease market</t>
+          <t>Monitored company (Amgen) assessing market for autoimmune disease (Sjogren's) relevant to biologics</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -579,7 +579,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored companies; Clinical Trials &amp; Pipeline News - autoimmune disease trial win</t>
+          <t>Clinical Trials &amp; Pipeline News for autoimmune disease (Sjogren's) from monitored company (Amgen)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -619,7 +619,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored companies; Biosimilars &amp; Biologics - patent litigation for specialty injectable (Wegovy)</t>
+          <t>Biosimilars &amp; Biologics patent litigation for a specialty injectable (Wegovy generic) from a monitored company (Viatris-Mylan)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Squires Says Biocon Challenge To Eylea Patent Filed Too Late</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.law360.com/publicpolicy/articles/2530219/squires-says-biocon-challenge-to-eylea-patent-filed-too-late</t>
+          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25-09-2026 22:37 UTC</t>
+          <t>26-09-2026 11:08 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored companies; Biosimilars &amp; Biologics - patent litigation for biologic (Eylea)</t>
+          <t>Clinical Trials &amp; Pipeline News for a biologic vaccine (Lyme disease) from a monitored company (Pfizer)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,32 +674,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Biocon Malaysia gets UK MHRA approval for new drug product fill-finish unit for insulins</t>
+          <t>2 studies find strong RSV vaccine protection against severe outcomes in older adults</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>CIDRAP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/biocon-malaysia-gets-uk-mhra-approval-for-new-drug-product-fill-finish-unit-for-insulins/article71507863.ece/amp/</t>
+          <t>https://www.cidrap.umn.edu/respiratory-syncytial-virus-rsv/2-studies-find-strong-rsv-vaccine-protection-against-severe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25-09-2026 09:49 UTC</t>
+          <t>25-09-2026 19:45 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - MHRA approval for biologic/biosimilar fill-finish unit</t>
+          <t>Clinical Trials &amp; Pipeline News for a biologic vaccine (RSV) from a monitored company (Pfizer)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences USA Office Clears USFDA Inspection With Nil Observations</t>
+          <t>Here's what you need to know about COVID-19 and flu vaccines in Minnesota this fall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Free Press Journal</t>
+          <t>MPR News</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/zydus-lifesciences-usa-office-clears-usfda-inspection-with-nil-observations</t>
+          <t>https://www.mprnews.org/story/2026/09/25/heres-what-you-need-to-know-about-covid19-and-flu-vaccines-in-minnesota-this-fall</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26-09-2026 07:07 UTC</t>
+          <t>25-09-2026 21:54 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored companies; FDA / Regulatory Actions - FDA inspection with nil observations</t>
+          <t>Clinical Trials &amp; Pipeline News for biologic vaccines (COVID-19 and flu) relevant to monitored company (Pfizer)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Merck &amp; Co., Daiichi withdraw US submission for ADC in lung cancer</t>
+          <t>IgA nephropathy’s formula for continuous innovation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FirstWord</t>
+          <t>BioCentury</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/8102182</t>
+          <t>https://www.biocentury.com/article/660896/iga-nephropathy-s-formula-for-continuous-innovation</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26-09-2026 00:11 UTC</t>
+          <t>26-09-2026 01:14 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored companies; FDA / Regulatory Actions - BLA withdrawal for biologic (ADC) in oncology</t>
+          <t>Clinical Trials &amp; Pipeline News for autoimmune disease (IgA nephropathy) for monitored company (Biogen)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vials Market To 2035: Biologics Demand Drives Growth in Sterile Packaging - News and Statistics</t>
+          <t>Dr Reddy's Q1FY27 revenue falls to ₹8,071 Cr on semaglutide hit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/vials-market-forecast-to-2035-biologics-demand-drives-growth-in-sterile-packaging/</t>
+          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-q1fy27-revenue-falls-6-to-8-071-cr-margins-hit-by-api-costs/46269828</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25-09-2026 23:11 UTC</t>
+          <t>26-09-2026 02:23 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - biologics demand affecting sterile packaging market</t>
+          <t>Earnings &amp; Financial Reports mentioning impact of specialty injectable (semaglutide) for monitored company (Dr. Reddy's)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CE-SDS / icIEF Systems Market To 2035: Biologics Demand Drives Expansion - News and Statistics</t>
+          <t>Biocon Loses Patent Challenge Bid as Squires Flexes Discretion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/ce-sds-icief-systems-market-forecast-to-2035-growth-accelerates-on-rising-biologics-characterization-demand/</t>
+          <t>https://news.bloomberglaw.com/ip-law/biocon-loses-patent-challenge-bid-as-squires-flexes-discretion</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25-09-2026 23:01 UTC</t>
+          <t>25-09-2026 20:51 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - biologics demand affecting characterization systems market</t>
+          <t>Biosimilars &amp; Biologics patent litigation (Eylea) for monitored company (Biocon)</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The 10 Deals That Defined APAC Biopharma in 2026</t>
+          <t>Zydus Lifesciences USA Office Clears USFDA Inspection With Nil Observations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>Free Press Journal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/analysis/73/8472/the-10-deals-that-defined-apac-biopharma-in-2026.html</t>
+          <t>https://www.freepressjournal.in/business/zydus-lifesciences-usa-office-clears-usfda-inspection-with-nil-observations</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25-09-2026 15:25 UTC</t>
+          <t>26-09-2026 07:07 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitored companies; Partnerships, Deals, Licensing &amp; Acquisition - deals in biopharma</t>
+          <t>FDA / Regulatory Actions (FDA inspection clearance) for monitored company (Zydus Lifesciences/Biotech)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,47 +907,287 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>K-Bio: Will its ₩430.8 Billion Bet Continue the 'Leclaza Myth'? New Drug Collaborations Accelerate on Two Fronts</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>재경일보</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://news.jkn.co.kr/post/997417</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>26-09-2026 05:40 UTC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition (new drug collaborations) within biologics for monitored company (Celltrion)</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo and Merck withdraw US filing for Ifinatamab Deruxtecan in small cell lung cancer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Indian Pharma Post</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.indianpharmapost.com/news/daiichi-sankyo-and-merck-withdraw-us-filing-for-ifinatamab-deruxtecan-in-small-cell-lung-cancer-21982</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>26-09-2026 12:10 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FDA / Regulatory Actions (BLA withdrawal for biologic Ifinatamab Deruxtecan) for monitored company (Daiichi Sankyo)</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vials Market To 2035: Biologics Demand Drives Growth in Sterile Packaging - News and Statistics</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/vials-market-forecast-to-2035-biologics-demand-drives-growth-in-sterile-packaging/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>25-09-2026 23:11 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (vials market driven by biologics demand) for monitored company (Fresenius Kabi)</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AI-Driven Drug Development Faces a Real Test... The Key Lies in Experimental Data [Weekend Money]</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026092309280601067</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>26-09-2026 02:22 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Biologics &amp; Biosimilars R&amp;D (AI-driven drug development) for monitored company (Samsung Bioepis)</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Six Industry Leaders Take the Stage in Rockville to Share Lessons on Quality, Manufacturing, and Scale</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>biobuzz.io</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://biobuzz.io/news/six-industry-leaders-take-the-stage-in-rockville-to-share-lessons-on-quality-manufacturing-and-scale/</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>25-09-2026 14:19 UTC</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Monitored companies; Manufacturing, Supply Chain &amp; Capacity - discussion on biologics manufacturing and quality</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CE-SDS / icIEF Systems Market To 2035: Biologics Demand Drives Expansion - News and Statistics</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/ce-sds-icief-systems-market-forecast-to-2035-growth-accelerates-on-rising-biologics-characterization-demand/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>25-09-2026 23:01 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (biologics characterization systems) for monitored company (Samsung Biologics)</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The 10 Deals That Defined APAC Biopharma in 2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BioPharma APAC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://biopharmaapac.com/analysis/73/8472/the-10-deals-that-defined-apac-biopharma-in-2026.html</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>25-09-2026 15:25 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition (biopharma deals) for monitored company (Samsung Biologics)</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>K-Bio's Open Innovation Blooms, Targeting Global Stage with New Drugs : 건강 : JKN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>재경일보</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://news.jkn.co.kr/post/997211</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26-09-2026 03:35 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition (open innovation in new drug development) for monitored company (Samsung Biologics)</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -975,7 +1215,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26-09-2026 13:49:29</t>
+          <t>26-09-2026 20:42:28</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Growth Hormones Market Forecast to 2035: Demand Accelerates on Pediatric and Adult Deficiency Treatments</t>
+          <t>Nevian signs Sandoz deal to widen medicine portfolio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/growth-hormones-market-forecast-to-2035-demand-accelerates-on-pediatric-and-adult-deficiency-treatments/</t>
+          <t>https://www.thedailystar.net/business/organisation-news/news/nevian-signs-sandoz-deal-widen-medicine-portfolio-4283646</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25-09-2026 23:36 UTC</t>
+          <t>26-09-2026 23:32 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biologics &amp; Biosimilars market trend (growth hormones are biologics) for monitored company</t>
+          <t>Monitored company (Sandoz) partnership</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yaron Werber: Celldex's Urticaria Drug Won't Carry a Black Box; Amgen Maps a $25 Billion Sjogren's Market</t>
+          <t>Mylan Challenges Novo Nordisk's Wegovy Patent as Danish Drugmaker Bets Billions on Life After Semagl</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/75b4a2731f15e785</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/unternehmensnachrichten/mylan-challenges-novo-nordisk-s-wegovy-patent-as-danish-drugmaker-bets/70187067</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25-09-2026 21:08 UTC</t>
+          <t>26-09-2026 19:50 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company (Amgen) assessing market for autoimmune disease (Sjogren's) relevant to biologics</t>
+          <t>Monitored company (Viatris-Mylan) patent litigation/challenge</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMGN Jumps After Win In Sjögren’s Disease Trial As Citi Flags ‘Open Questions’</t>
+          <t>Biocon Limited (NSE: BIOCON) Receives UK MHRA Approval for Insulin Fill-Finish Facility</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/amgn-jumps-after-win-in-sjoegren-s-disease-trial-as-citi-flags-open-questions/cZMPwKgRB7B</t>
+          <t>https://www.kalkine.co.in/article/healthcare/biocon-limited-nse-biocon-expands-insulin-manufacturing-capabilities-with-uk-mhra-clearance-for-malaysia-facility</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26-09-2026 02:48 UTC</t>
+          <t>26-09-2026 15:45 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News for autoimmune disease (Sjogren's) from monitored company (Amgen)</t>
+          <t>Monitored company (Biocon) biologic manufacturing facility approval</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mylan asks US court to clear Wegovy generic from Novo patent claims</t>
+          <t>Celltrion renews EU-GMP for 250,000-liter Songdo facility, boosts production capacity 15%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>더바이오</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/legalindustry/mylan-asks-us-court-clear-wegovy-generic-novo-patent-claims-2026-09-25/</t>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28457</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25-09-2026 19:23 UTC</t>
+          <t>26-09-2026 16:10 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics patent litigation for a specialty injectable (Wegovy generic) from a monitored company (Viatris-Mylan)</t>
+          <t>Monitored company (Celltrion) biologic manufacturing capacity and regulatory (GMP) news</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Daiichi Sankyo and Merck withdraw US filing for Ifinatamab Deruxtecan in small cell lung cancer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
+          <t>https://www.indianpharmapost.com/news/daiichi-sankyo-and-merck-withdraw-us-filing-for-ifinatamab-deruxtecan-in-small-cell-lung-cancer-21982</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26-09-2026 11:08 UTC</t>
+          <t>26-09-2026 12:10 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News for a biologic vaccine (Lyme disease) from a monitored company (Pfizer)</t>
+          <t>Monitored company (Daiichi Sankyo) regulatory news for a monoclonal antibody</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,525 +667,45 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2 studies find strong RSV vaccine protection against severe outcomes in older adults</t>
+          <t>Enhertu: NICE Approval Expands NHS Breast Cancer Care</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CIDRAP</t>
+          <t>Healthcare Digital</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/respiratory-syncytial-virus-rsv/2-studies-find-strong-rsv-vaccine-protection-against-severe</t>
+          <t>https://healthcare-digital.com/news/enhertu-nice-framework-shift-advances-nhs-womens-care</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25-09-2026 19:45 UTC</t>
+          <t>27-09-2026 08:03 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Clinical Trials &amp; Pipeline News for a biologic vaccine (RSV) from a monitored company (Pfizer)</t>
+          <t>Monitored company (Daiichi Sankyo) market access approval for a monoclonal antibody</t>
         </is>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pfizer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Here's what you need to know about COVID-19 and flu vaccines in Minnesota this fall</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MPR News</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://www.mprnews.org/story/2026/09/25/heres-what-you-need-to-know-about-covid19-and-flu-vaccines-in-minnesota-this-fall</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>25-09-2026 21:54 UTC</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Clinical Trials &amp; Pipeline News for biologic vaccines (COVID-19 and flu) relevant to monitored company (Pfizer)</t>
-        </is>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Biogen</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IgA nephropathy’s formula for continuous innovation</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>BioCentury</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.biocentury.com/article/660896/iga-nephropathy-s-formula-for-continuous-innovation</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>26-09-2026 01:14 UTC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Clinical Trials &amp; Pipeline News for autoimmune disease (IgA nephropathy) for monitored company (Biogen)</t>
-        </is>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Dr Reddy's Q1FY27 revenue falls to ₹8,071 Cr on semaglutide hit</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-q1fy27-revenue-falls-6-to-8-071-cr-margins-hit-by-api-costs/46269828</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>26-09-2026 02:23 UTC</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Earnings &amp; Financial Reports mentioning impact of specialty injectable (semaglutide) for monitored company (Dr. Reddy's)</t>
-        </is>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Biocon Loses Patent Challenge Bid as Squires Flexes Discretion</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bloomberg Law News</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://news.bloomberglaw.com/ip-law/biocon-loses-patent-challenge-bid-as-squires-flexes-discretion</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>25-09-2026 20:51 UTC</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Biosimilars &amp; Biologics patent litigation (Eylea) for monitored company (Biocon)</t>
-        </is>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Zydus Biotech</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Zydus Lifesciences USA Office Clears USFDA Inspection With Nil Observations</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Free Press Journal</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/business/zydus-lifesciences-usa-office-clears-usfda-inspection-with-nil-observations</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>26-09-2026 07:07 UTC</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>FDA / Regulatory Actions (FDA inspection clearance) for monitored company (Zydus Lifesciences/Biotech)</t>
-        </is>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>K-Bio: Will its ₩430.8 Billion Bet Continue the 'Leclaza Myth'? New Drug Collaborations Accelerate on Two Fronts</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>재경일보</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://news.jkn.co.kr/post/997417</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>26-09-2026 05:40 UTC</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition (new drug collaborations) within biologics for monitored company (Celltrion)</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo and Merck withdraw US filing for Ifinatamab Deruxtecan in small cell lung cancer</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Indian Pharma Post</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.indianpharmapost.com/news/daiichi-sankyo-and-merck-withdraw-us-filing-for-ifinatamab-deruxtecan-in-small-cell-lung-cancer-21982</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>26-09-2026 12:10 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>FDA / Regulatory Actions (BLA withdrawal for biologic Ifinatamab Deruxtecan) for monitored company (Daiichi Sankyo)</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Vials Market To 2035: Biologics Demand Drives Growth in Sterile Packaging - News and Statistics</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>IndexBox</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/vials-market-forecast-to-2035-biologics-demand-drives-growth-in-sterile-packaging/</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>25-09-2026 23:11 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (vials market driven by biologics demand) for monitored company (Fresenius Kabi)</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AI-Driven Drug Development Faces a Real Test... The Key Lies in Experimental Data [Weekend Money]</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>아시아경제</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026092309280601067</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>26-09-2026 02:22 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Biologics &amp; Biosimilars R&amp;D (AI-driven drug development) for monitored company (Samsung Bioepis)</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CE-SDS / icIEF Systems Market To 2035: Biologics Demand Drives Expansion - News and Statistics</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>IndexBox</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/ce-sds-icief-systems-market-forecast-to-2035-growth-accelerates-on-rising-biologics-characterization-demand/</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>25-09-2026 23:01 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (biologics characterization systems) for monitored company (Samsung Biologics)</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>The 10 Deals That Defined APAC Biopharma in 2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BioPharma APAC</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://biopharmaapac.com/analysis/73/8472/the-10-deals-that-defined-apac-biopharma-in-2026.html</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>25-09-2026 15:25 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition (biopharma deals) for monitored company (Samsung Biologics)</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>K-Bio's Open Innovation Blooms, Targeting Global Stage with New Drugs : 건강 : JKN</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>재경일보</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://news.jkn.co.kr/post/997211</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>26-09-2026 03:35 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition (open innovation in new drug development) for monitored company (Samsung Biologics)</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1215,7 +735,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26-09-2026 20:42:28</t>
+          <t>27-09-2026 14:22:06</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company (Sandoz) partnership</t>
+          <t>Monitored company partnership/deal (Sandoz)</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mylan Challenges Novo Nordisk's Wegovy Patent as Danish Drugmaker Bets Billions on Life After Semagl</t>
+          <t>Shanghai RAAS to Take Over Boehringer Ingelheim China Unit for Up to USD3 Million</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>一财全球Yicai Global</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/unternehmensnachrichten/mylan-challenges-novo-nordisk-s-wegovy-patent-as-danish-drugmaker-bets/70187067</t>
+          <t>https://www.yicaiglobal.com/news/shanghai-raas-to-take-over-boehringer-ingelheim-china-unit-for-up-to-usd3-million</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26-09-2026 19:50 UTC</t>
+          <t>27-09-2026 14:42 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company (Viatris-Mylan) patent litigation/challenge</t>
+          <t>Monitored company acquisition/deal (Boehringer Ingelheim)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Biocon Limited (NSE: BIOCON) Receives UK MHRA Approval for Insulin Fill-Finish Facility</t>
+          <t>Mylan Challenges Novo Nordisk's Wegovy Patent as Danish Drugmaker Bets Billions on Life After Semagl</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kalkine.co.in/article/healthcare/biocon-limited-nse-biocon-expands-insulin-manufacturing-capabilities-with-uk-mhra-clearance-for-malaysia-facility</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/unternehmensnachrichten/mylan-challenges-novo-nordisk-s-wegovy-patent-as-danish-drugmaker-bets/70187067</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26-09-2026 15:45 UTC</t>
+          <t>26-09-2026 19:50 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company (Biocon) biologic manufacturing facility approval</t>
+          <t>Monitored company patent litigation (Viatris-Mylan)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Celltrion renews EU-GMP for 250,000-liter Songdo facility, boosts production capacity 15%</t>
+          <t>Briefs: Biocon Malaysia, IOL Chemicals and NATCO Pharma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>더바이오</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28457</t>
+          <t>https://www.indianpharmapost.com/news/briefs-biocon-malaysia-iol-chemicals-and-natco-pharma-21986</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26-09-2026 16:10 UTC</t>
+          <t>27-09-2026 11:51 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company (Celltrion) biologic manufacturing capacity and regulatory (GMP) news</t>
+          <t>Monitored company news (Biocon)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,19 +627,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo and Merck withdraw US filing for Ifinatamab Deruxtecan in small cell lung cancer</t>
+          <t>Briefs: Zydus Lifesciences and RPG Active Pharma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/daiichi-sankyo-and-merck-withdraw-us-filing-for-ifinatamab-deruxtecan-in-small-cell-lung-cancer-21982</t>
+          <t>https://www.indianpharmapost.com/news/briefs-zydus-lifesciences-and-rpg-active-pharma-21988</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26-09-2026 12:10 UTC</t>
+          <t>27-09-2026 12:10 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company (Daiichi Sankyo) regulatory news for a monoclonal antibody</t>
+          <t>Monitored company news (Zydus Biotech/Lifesciences)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,38 +674,158 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Enhertu: NICE Approval Expands NHS Breast Cancer Care</t>
+          <t>Celltrion renews EU-GMP for 250,000-liter Songdo facility, boosts production capacity 15%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Healthcare Digital</t>
+          <t>더바이오</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://healthcare-digital.com/news/enhertu-nice-framework-shift-advances-nhs-womens-care</t>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28457</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27-09-2026 08:03 UTC</t>
+          <t>26-09-2026 16:10 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company (Daiichi Sankyo) market access approval for a monoclonal antibody</t>
+          <t>Monitored company biologic manufacturing capacity expansion and GMP renewal</t>
         </is>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fortis says no role in Daiichi-Singh Brothers dispute as SC allows forensic audit</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ETHealthworld.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://health.economictimes.indiatimes.com/amp/news/hospitals/fortis-says-no-role-in-daiichi-singh-brothers-dispute-as-sc-allows-forensic-audit/134518549</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>27-09-2026 10:41 UTC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Monitored company legal dispute (Daiichi Sankyo)</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Enhertu: NICE Approval Expands NHS Breast Cancer Care</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Healthcare Digital</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://healthcare-digital.com/news/enhertu-nice-framework-shift-advances-nhs-womens-care</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>27-09-2026 08:03 UTC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Monitored company biologic approval/market access (Enhertu)</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Georgiadis: “We welcome Samsung Bioepis to Greece” – What it means for patients</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pagenews.gr</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.pagenews.gr/2026/09/27/english-edition/georgiadis-we-welcome-samsung-bioepis-to-greece-what-it-means-for-patients/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>27-09-2026 07:23 UTC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Monitored company market entry/commercial event (Samsung Bioepis)</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -735,7 +855,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27-09-2026 14:22:06</t>
+          <t>27-09-2026 21:19:44</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nevian signs Sandoz deal to widen medicine portfolio</t>
+          <t>UK Set to Miss Out on Off-Patent Drug Savings, Lobby Group Warns</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Bloomberg.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/business/organisation-news/news/nevian-signs-sandoz-deal-widen-medicine-portfolio-4283646</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-28/uk-set-to-miss-out-on-off-patent-drug-savings-lobby-group-warns?srnd=phx-industries-health</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26-09-2026 23:32 UTC</t>
+          <t>28-09-2026 04:00 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company partnership/deal (Sandoz)</t>
+          <t>Biosimilars &amp; biologics market access/pricing policy</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shanghai RAAS to Take Over Boehringer Ingelheim China Unit for Up to USD3 Million</t>
+          <t>Why Singapore is a top choice for biopharma firms seeking global expansion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>一财全球Yicai Global</t>
+          <t>Singapore Economic Development Board (EDB)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.yicaiglobal.com/news/shanghai-raas-to-take-over-boehringer-ingelheim-china-unit-for-up-to-usd3-million</t>
+          <t>https://www.edb.gov.sg/en/news-and-insights/why-singapore-is-a-top-choice-for-biopharma-firms-seeking-global-expansion</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27-09-2026 14:42 UTC</t>
+          <t>28-09-2026 07:48 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company acquisition/deal (Boehringer Ingelheim)</t>
+          <t>Biologics manufacturing/industry trends</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mylan Challenges Novo Nordisk's Wegovy Patent as Danish Drugmaker Bets Billions on Life After Semagl</t>
+          <t>6 immunology targets to sustain a mammoth I&amp;I market</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/unternehmensnachrichten/mylan-challenges-novo-nordisk-s-wegovy-patent-as-danish-drugmaker-bets/70187067</t>
+          <t>https://www.biospace.com/drug-development/6-immunology-targets-to-sustain-a-mammoth-i-i-market</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26-09-2026 19:50 UTC</t>
+          <t>28-09-2026 04:04 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company patent litigation (Viatris-Mylan)</t>
+          <t>Immunology market/pipeline news</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Briefs: Biocon Malaysia, IOL Chemicals and NATCO Pharma</t>
+          <t>Dr Reddy's shares gain over 1% after Nomura retains 'Buy'; Rs1,740 target, key biologics milestones ahead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/briefs-biocon-malaysia-iol-chemicals-and-natco-pharma-21986</t>
+          <t>https://www.moneycontrol.com/news/business/stocks/dr-reddy-s-shares-gain-over-1-after-nomura-retains-buy-rs1-740-target-key-biologics-milestones-ahead-14039696.html/amp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27-09-2026 11:51 UTC</t>
+          <t>28-09-2026 04:12 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company news (Biocon)</t>
+          <t>Earnings/financial report with biologics relevance</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Briefs: Zydus Lifesciences and RPG Active Pharma</t>
+          <t>Dr. Reddy’s Share: How Important and Beneficial Is Its Abatacept Biosimilar Approval for the Company?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Trade Brains</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/briefs-zydus-lifesciences-and-rpg-active-pharma-21988</t>
+          <t>https://tradebrains.in/indian-markets/dr-reddys-share-how-important-and-beneficial-is-its-abatacept-biosimilar-approval-for-the-company-12585018</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27-09-2026 12:10 UTC</t>
+          <t>28-09-2026 08:35 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company news (Zydus Biotech/Lifesciences)</t>
+          <t>Biosimilar FDA approval / market commentary</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Celltrion renews EU-GMP for 250,000-liter Songdo facility, boosts production capacity 15%</t>
+          <t>Karnataka flags drug landing cost-MRP gap at hospitals of up to 52.6 times; seeks Centre's intervention</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>더바이오</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28457</t>
+          <t>https://timesofindia.indiatimes.com/india/karnataka-flags-drug-landing-cost-mrp-gap-at-hospitals-of-up-to-52-6-times-seeks-centres-intervention/articleshow/134523341.cms</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26-09-2026 16:10 UTC</t>
+          <t>27-09-2026 16:25 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company biologic manufacturing capacity expansion and GMP renewal</t>
+          <t>Biosimilars &amp; biologics market access/pricing policy</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fortis says no role in Daiichi-Singh Brothers dispute as SC allows forensic audit</t>
+          <t>Briefs: Biocon Malaysia, IOL Chemicals and NATCO Pharma</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ETHealthworld.com</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/amp/news/hospitals/fortis-says-no-role-in-daiichi-singh-brothers-dispute-as-sc-allows-forensic-audit/134518549</t>
+          <t>https://www.indianpharmapost.com/news/briefs-biocon-malaysia-iol-chemicals-and-natco-pharma-21986</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27-09-2026 10:41 UTC</t>
+          <t>27-09-2026 11:51 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company legal dispute (Daiichi Sankyo)</t>
+          <t>Monitored company manufacturing news</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Enhertu: NICE Approval Expands NHS Breast Cancer Care</t>
+          <t>PLI schemes boost India’s pharma, bulk drugs and medical devices manufacturing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Healthcare Digital</t>
+          <t>organiser.org</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://healthcare-digital.com/news/enhertu-nice-framework-shift-advances-nhs-womens-care</t>
+          <t>https://organiser.org/2026/09/28/383156/bharat/pli-schemes-boost-indias-pharma-bulk-drugs-and-medical-devices-manufacturing/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27-09-2026 08:03 UTC</t>
+          <t>28-09-2026 07:04 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored company biologic approval/market access (Enhertu)</t>
+          <t>Biologics manufacturing policy/incentives</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Georgiadis: “We welcome Samsung Bioepis to Greece” – What it means for patients</t>
+          <t>Celltrion wins U.S. Phase 3 clinical trial approval for ‘Zymfentra’ in rheumatoid arthritis, expanding indications</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pagenews.gr</t>
+          <t>더바이오</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pagenews.gr/2026/09/27/english-edition/georgiadis-we-welcome-samsung-bioepis-to-greece-what-it-means-for-patients/</t>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28463</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27-09-2026 07:23 UTC</t>
+          <t>27-09-2026 21:44 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored company market entry/commercial event (Samsung Bioepis)</t>
+          <t>Biologic clinical trial approval for indication expansion (immunology)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,7 +827,127 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ifinatamab Deruxtecan Biologics License Application for Certain Patients with Previously Treated Extensive-Stage Small Cell Lung Cancer Voluntarily Withdrawn</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BioSpace</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/ifinatamab-deruxtecan-biologics-license-application-for-certain-patients-with-previously-treated-extensive-stage-small-cell-lung-cancer-voluntarily-withdrawn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>28-09-2026 04:22 UTC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FDA action (BLA withdrawal) for a biologic</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Infusion Reservoir Bags Plastic Market To 2035: Multi-Chamber and Integrated-Filter Demand Drives 5-7% CAGR - News and Statistics</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/infusion-reservoir-bags-plastic-market-forecast-to-2035-multi-chamber-and-integrated-filter-demand-drives-5-7-cagr/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>28-09-2026 04:41 UTC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Manufacturing/supply chain for sterile injectable components (biologics relevant)</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Samsung Biologics Cuts Antibody Drug Development Time to 9.5 Months, Doubles Culture Productivity</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://finance.biggo.com/news/122ca7b6-85db-4d1b-9876-b1bf7bb1b1dd</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>28-09-2026 06:06 UTC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Biologic manufacturing process/efficiency improvements (CDMO)</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -855,7 +975,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27-09-2026 21:19:44</t>
+          <t>28-09-2026 14:49:02</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UK Set to Miss Out on Off-Patent Drug Savings, Lobby Group Warns</t>
+          <t>STADA and SBP Group launch biosimilars partnership</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-28/uk-set-to-miss-out-on-off-patent-drug-savings-lobby-group-warns?srnd=phx-industries-health</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/stada-and-sbp-group-launch-biosimilars-partnership</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28-09-2026 04:00 UTC</t>
+          <t>28-09-2026 12:02 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics market access/pricing policy</t>
+          <t>Monitored company biosimilars partnership</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,39 +507,39 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why Singapore is a top choice for biopharma firms seeking global expansion</t>
+          <t>Sino Biopharma Unit Grants STADA Commercialization License for Pembrolizumab Biosimilar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore Economic Development Board (EDB)</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.edb.gov.sg/en/news-and-insights/why-singapore-is-a-top-choice-for-biopharma-firms-seeking-global-expansion</t>
+          <t>https://www.marketscreener.com/news/sino-biopharma-unit-grants-stada-commercialization-license-for-pembrolizumab-biosimilar-ce785adcdd8cff2d</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28-09-2026 07:48 UTC</t>
+          <t>28-09-2026 09:56 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Biologics manufacturing/industry trends</t>
+          <t>Monitored company biosimilar licensing deal (pembrolizumab biosimilar)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6 immunology targets to sustain a mammoth I&amp;I market</t>
+          <t>Sun Pharma steps into PCSK9 arena with LIB Therapeutics’ monthly-shot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/drug-development/6-immunology-targets-to-sustain-a-mammoth-i-i-market</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/sun-pharma-steps-into-the-pcsk9-arena-with-lib-therapeutics-monthly-shot/134535007</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28-09-2026 04:04 UTC</t>
+          <t>28-09-2026 07:06 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Immunology market/pipeline news</t>
+          <t>Biologics market activity (PCSK9 inhibitor competitor)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr Reddy's shares gain over 1% after Nomura retains 'Buy'; Rs1,740 target, key biologics milestones ahead</t>
+          <t>Organon Canada Announces the Approval and Availability of NDUVRA® (Tapinarof Cream), 1%, a New Steroid-Free Topical Treatment for Moderate to Severe Atopic Dermatitis in Adult and Pediatric Patients 2 Years of Age and Older</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>PR Newswire Canada</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/stocks/dr-reddy-s-shares-gain-over-1-after-nomura-retains-buy-rs1-740-target-key-biologics-milestones-ahead-14039696.html/amp</t>
+          <t>https://www.newswire.ca/news-releases/organon-canada-announces-the-approval-and-availability-of-nduvra-r-tapinarof-cream-1-a-new-steroid-free-topical-treatment-for-moderate-to-severe-atopic-dermatitis-in-adult-and-pediatric-patients-2-years-of-age-and-older-842702881.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28-09-2026 04:12 UTC</t>
+          <t>28-09-2026 12:01 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earnings/financial report with biologics relevance</t>
+          <t>Monitored company approval in immunology/dermatology related specialty market</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Share: How Important and Beneficial Is Its Abatacept Biosimilar Approval for the Company?</t>
+          <t>Sun Pharma Inks Global Licensing Deal With LIB Therapeutics For PCSK9 Inhibitor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trade Brains</t>
+          <t>Free Press Journal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://tradebrains.in/indian-markets/dr-reddys-share-how-important-and-beneficial-is-its-abatacept-biosimilar-approval-for-the-company-12585018</t>
+          <t>https://www.freepressjournal.in/business/sun-pharma-inks-global-licensing-deal-with-lib-therapeutics-for-pcsk9-inhibitor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28-09-2026 08:35 UTC</t>
+          <t>28-09-2026 04:47 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biosimilar FDA approval / market commentary</t>
+          <t>Biologics licensing deal (PCSK9 inhibitor)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Karnataka flags drug landing cost-MRP gap at hospitals of up to 52.6 times; seeks Centre's intervention</t>
+          <t>Pfizer's Tilrekimig Phase 3 Program Seen as Potential Upside Driver, UBS Says</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/karnataka-flags-drug-landing-cost-mrp-gap-at-hospitals-of-up-to-52-6-times-seeks-centres-intervention/articleshow/134523341.cms</t>
+          <t>https://www.marketscreener.com/news/pfizer-s-tilrekimig-phase-3-program-seen-as-potential-upside-driver-ubs-says-ce785adcd189f025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27-09-2026 16:25 UTC</t>
+          <t>28-09-2026 15:57 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics market access/pricing policy</t>
+          <t>Monitored company biologic clinical pipeline news (immunology)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Briefs: Biocon Malaysia, IOL Chemicals and NATCO Pharma</t>
+          <t>Vitiligo Market Forecast 2034: Rising Demand, Novel Therapies, and Commercial Potential – DelveInsight | Pfizer, Clinuvel, Inc., Clinuvel Pharma, Bioniz Therapeutics, TAGCyx Biotech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/briefs-biocon-malaysia-iol-chemicals-and-natco-pharma-21986</t>
+          <t>https://www.barchart.com/press-releases/4833816/vitiligo-market-forecast-2034-rising-demand-novel-therapies-and-commercial-potential-delveinsight-pfizer-clinuvel-inc-clinuvel-pharma-bioniz-therapeutics-tagcyx-biotech</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27-09-2026 11:51 UTC</t>
+          <t>28-09-2026 13:56 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company manufacturing news</t>
+          <t>Monitored company activity in immunology/dermatology specialty market</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLI schemes boost India’s pharma, bulk drugs and medical devices manufacturing</t>
+          <t>Dr Reddy's shares gain over 1% after Nomura retains 'Buy'; Rs1,740 target, key biologics milestones ahead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>organiser.org</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://organiser.org/2026/09/28/383156/bharat/pli-schemes-boost-indias-pharma-bulk-drugs-and-medical-devices-manufacturing/</t>
+          <t>https://www.moneycontrol.com/news/business/stocks/dr-reddy-s-shares-gain-over-1-after-nomura-retains-buy-rs1-740-target-key-biologics-milestones-ahead-14039696.html/amp</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28-09-2026 07:04 UTC</t>
+          <t>28-09-2026 04:12 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Biologics manufacturing policy/incentives</t>
+          <t>Earnings/financial report mentioning biologics business</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Celltrion wins U.S. Phase 3 clinical trial approval for ‘Zymfentra’ in rheumatoid arthritis, expanding indications</t>
+          <t>How Significant Is Abatacept Biosimilar Approval for Dr. Reddy’s?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>더바이오</t>
+          <t>Motilal Oswal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28463</t>
+          <t>https://www.motilaloswal.com/news/stocks/129811</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27-09-2026 21:44 UTC</t>
+          <t>28-09-2026 11:18 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Biologic clinical trial approval for indication expansion (immunology)</t>
+          <t>Monitored company biosimilar approval (Abatacept)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ifinatamab Deruxtecan Biologics License Application for Certain Patients with Previously Treated Extensive-Stage Small Cell Lung Cancer Voluntarily Withdrawn</t>
+          <t>Biocon Malaysia Receives UK Approval for Insulin Fill-Finish Unit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>themachinemaker.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/ifinatamab-deruxtecan-biologics-license-application-for-certain-patients-with-previously-treated-extensive-stage-small-cell-lung-cancer-voluntarily-withdrawn</t>
+          <t>https://themachinemaker.com/news/biocon-malaysia-receives-uk-approval-for-insulin-fill-finish-unit/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28-09-2026 04:22 UTC</t>
+          <t>28-09-2026 10:30 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FDA action (BLA withdrawal) for a biologic</t>
+          <t>Monitored company biologic manufacturing capacity approval (insulin fill-finish unit)</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Infusion Reservoir Bags Plastic Market To 2035: Multi-Chamber and Integrated-Filter Demand Drives 5-7% CAGR - News and Statistics</t>
+          <t>Celltrion wins U.S. Phase 3 clinical trial approval for ‘Zymfentra’ in rheumatoid arthritis, expanding indications</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>더바이오</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/infusion-reservoir-bags-plastic-market-forecast-to-2035-multi-chamber-and-integrated-filter-demand-drives-5-7-cagr/</t>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28463</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28-09-2026 04:41 UTC</t>
+          <t>27-09-2026 21:44 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manufacturing/supply chain for sterile injectable components (biologics relevant)</t>
+          <t>Monitored company biologic clinical trial approval (rheumatoid arthritis)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,47 +907,327 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Prestige Biopharma</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Prestige BioPharma wins Brazil approval for Herceptin biosimilar Tuznue</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Korea Biomedical Review</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33311</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>28-09-2026 06:14 UTC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Monitored company biosimilar approval (trastuzumab biosimilar)</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Merck, Daiichi pull lung cancer filing after FDA pushback deals another blow to $4B deal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fierce Biotech</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.fiercebiotech.com/biotech/merck-co-and-daiichi-pull-lung-cancer-filing-after-fda-pushback-deals-another-blow-4b-deal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>28-09-2026 08:30 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Monitored company biologic regulatory action (BLA withdrawal)</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo Says NTK Appeals Tokyo District Court's 203 Billion Yen Claim Dismissal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/news/daiichi-sankyo-says-ntk-appeals-tokyo-district-court-s-203-billion-yen-claim-dismissal-ce785adcdb8afe21</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>28-09-2026 04:26 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Monitored company patent litigation</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Link Cell Therapies Initiates Clinical Dosing with Logic-Gated CAR-T Therapy, Expands Executive Leadership, and Upsizes Series A Financing to $90 Million</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>The Manila Times</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.manilatimes.net/2026/09/28/tmt-newswire/pr-newswire/link-cell-therapies-initiates-clinical-dosing-with-logic-gated-car-t-therapy-expands-executive-leadership-and-upsizes-series-a-financing-to-90-million/2434075</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>28-09-2026 11:58 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Monitored company advanced therapy clinical trial (CAR-T)</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fresenius Pours EUR 54 Million Into European Infusion Capacity as NutriChef Lands in Six Markets</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/unternehmensnachrichten/fresenius-pours-eur-54-million-into-european-infusion-capacity-as/70193335</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>28-09-2026 14:11 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Monitored company manufacturing capacity expansion (sterile injectables)</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alvotech Soars As FDA Breakthrough Ignites Biosimilar Hopes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/catalyst/alvotech-soars-as-fda-breakthrough-ignites-biosimilar-hopes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>28-09-2026 16:07 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Monitored company FDA regulatory action for biosimilars</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Samsung Biologics Cuts Antibody Drug Development Time to 9.5 Months, Doubles Culture Productivity</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>finance.biggo.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://finance.biggo.com/news/122ca7b6-85db-4d1b-9876-b1bf7bb1b1dd</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>28-09-2026 06:06 UTC</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Biologic manufacturing process/efficiency improvements (CDMO)</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Samsung Biologics cuts complex antibody development timeline to 9.5 months</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Korea Biomedical Review</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33312</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>28-09-2026 06:58 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Monitored company biologic manufacturing innovation</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Samsung BioLogics Union Broadens Scope of 'Ongoing Management Involvement'</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.asiae.co.kr/en/article/2026092719524964396</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>28-09-2026 02:19 UTC</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Monitored company manufacturing/operations news (union involvement)</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -975,7 +1255,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28-09-2026 14:49:02</t>
+          <t>29-09-2026 00:21:40</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STADA and SBP Group launch biosimilars partnership</t>
+          <t>Sandoz opens advanced high-volume drug substance manufacturing centre in Lendava, significantly strengthening in-house capacity and flexibility across leading European biosimilar network</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/stada-and-sbp-group-launch-biosimilars-partnership</t>
+          <t>https://www.sandoz.com/sandoz-opens-advanced-high-volume-drug-substance-manufacturing-centre-lendava-significantly</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28-09-2026 12:02 UTC</t>
+          <t>29-09-2026 05:33 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company biosimilars partnership</t>
+          <t>Monitored company (Sandoz) biosimilar manufacturing expansion</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company biosimilar licensing deal (pembrolizumab biosimilar)</t>
+          <t>Monitored company (Stada) biosimilar licensing deal</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sun Pharma steps into PCSK9 arena with LIB Therapeutics’ monthly-shot</t>
+          <t>Fact or Fiction: Updates in Hereditary Angioedema</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>Medscape Reference</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/sun-pharma-steps-into-the-pcsk9-arena-with-lib-therapeutics-monthly-shot/134535007</t>
+          <t>https://reference.medscape.com/viewarticle/hae-fact-or-fiction-2026a1000wln</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28-09-2026 07:06 UTC</t>
+          <t>28-09-2026 19:26 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Biologics market activity (PCSK9 inhibitor competitor)</t>
+          <t>Autoimmune disease (HAE) therapy area news</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -619,7 +619,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company approval in immunology/dermatology related specialty market</t>
+          <t>Monitored company (Organon) approval in dermatology/autoimmune disease</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sun Pharma Inks Global Licensing Deal With LIB Therapeutics For PCSK9 Inhibitor</t>
+          <t>How Significant Is Abatacept Biosimilar Approval for Dr. Reddy’s?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Free Press Journal</t>
+          <t>Motilal Oswal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/sun-pharma-inks-global-licensing-deal-with-lib-therapeutics-for-pcsk9-inhibitor</t>
+          <t>https://www.motilaloswal.com/news/stocks/129811</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28-09-2026 04:47 UTC</t>
+          <t>28-09-2026 11:18 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biologics licensing deal (PCSK9 inhibitor)</t>
+          <t>Monitored company (Dr. Reddy's) biosimilar approval (Abatacept for autoimmune disease)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pfizer's Tilrekimig Phase 3 Program Seen as Potential Upside Driver, UBS Says</t>
+          <t>Biocon Malaysia Receives UK Approval for Insulin Fill-Finish Unit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Machine Maker</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/pfizer-s-tilrekimig-phase-3-program-seen-as-potential-upside-driver-ubs-says-ce785adcd189f025</t>
+          <t>https://themachinemaker.com/news/biocon-malaysia-receives-uk-approval-for-insulin-fill-finish-unit/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28-09-2026 15:57 UTC</t>
+          <t>28-09-2026 10:30 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company biologic clinical pipeline news (immunology)</t>
+          <t>Monitored company (Biocon) biologic manufacturing approval (insulin fill-finish)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vitiligo Market Forecast 2034: Rising Demand, Novel Therapies, and Commercial Potential – DelveInsight | Pfizer, Clinuvel, Inc., Clinuvel Pharma, Bioniz Therapeutics, TAGCyx Biotech</t>
+          <t>USFDA concludes inspection at Zydus Life's SEZ II Ahmedabad plant with 1 observation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4833816/vitiligo-market-forecast-2034-rising-demand-novel-therapies-and-commercial-potential-delveinsight-pfizer-clinuvel-inc-clinuvel-pharma-bioniz-therapeutics-tagcyx-biotech</t>
+          <t>https://www.indianpharmapost.com/news/usfda-concludes-inspection-at-zydus-lifes-sez-ii-ahmedabad-plant-with-1-observation-22009</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28-09-2026 13:56 UTC</t>
+          <t>29-09-2026 03:07 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company activity in immunology/dermatology specialty market</t>
+          <t>Monitored company (Zydus Biotech) FDA inspection with observation</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dr Reddy's shares gain over 1% after Nomura retains 'Buy'; Rs1,740 target, key biologics milestones ahead</t>
+          <t>Celltrion targets CDMO deals, supply-chain partners at CPHI 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/stocks/dr-reddy-s-shares-gain-over-1-after-nomura-retains-buy-rs1-740-target-key-biologics-milestones-ahead-14039696.html/amp</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33324</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28-09-2026 04:12 UTC</t>
+          <t>29-09-2026 05:53 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Earnings/financial report mentioning biologics business</t>
+          <t>Monitored company (Celltrion) seeking CDMO and drug pipeline partnerships</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>How Significant Is Abatacept Biosimilar Approval for Dr. Reddy’s?</t>
+          <t>Daiichi Sankyo, Merck Pull Ifinatamab Deruxtecan BLA in SCLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Motilal Oswal</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.motilaloswal.com/news/stocks/129811</t>
+          <t>https://www.biopharminternational.com/view/daiichi-sankyo-merck-pull-ifinatamab-deruxtecan-bla-sclc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28-09-2026 11:18 UTC</t>
+          <t>28-09-2026 16:35 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored company biosimilar approval (Abatacept)</t>
+          <t>Monitored company (Daiichi Sankyo) biologic (ADC) BLA withdrawal (regulatory action)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Biocon Malaysia Receives UK Approval for Insulin Fill-Finish Unit</t>
+          <t>Fresenius Pours EUR 54 Million Into European Infusion Capacity as NutriChef Lands in Six Markets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>themachinemaker.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://themachinemaker.com/news/biocon-malaysia-receives-uk-approval-for-insulin-fill-finish-unit/</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/unternehmensnachrichten/fresenius-pours-eur-54-million-into-european-infusion-capacity-as/70193335</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28-09-2026 10:30 UTC</t>
+          <t>28-09-2026 14:11 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitored company biologic manufacturing capacity approval (insulin fill-finish unit)</t>
+          <t>Monitored company (Fresenius Kabi) manufacturing capacity expansion for sterile products</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Celltrion wins U.S. Phase 3 clinical trial approval for ‘Zymfentra’ in rheumatoid arthritis, expanding indications</t>
+          <t>Alvotech Soars As FDA Breakthrough Ignites Biosimilar Hopes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>더바이오</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28463</t>
+          <t>https://www.tipranks.com/news/catalyst/alvotech-soars-as-fda-breakthrough-ignites-biosimilar-hopes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27-09-2026 21:44 UTC</t>
+          <t>28-09-2026 16:07 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitored company biologic clinical trial approval (rheumatoid arthritis)</t>
+          <t>Monitored company (Alvotech) FDA biosimilar breakthrough news</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prestige BioPharma wins Brazil approval for Herceptin biosimilar Tuznue</t>
+          <t>Teva Continues Biosimilar Momentum with U.S. FDA Approval of DEGEVMA™ (denosumab-adet), a Biosimilar to Xgeva® (denosumab)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Macau Business</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33311</t>
+          <t>https://macaubusiness.com/teva-continues-biosimilar-momentum-with-u-s-fda-approval-of-degevma-denosumab-adet-a-biosimilar-to-xgeva-denosumab/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28-09-2026 06:14 UTC</t>
+          <t>29-09-2026 02:42 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monitored company biosimilar approval (trastuzumab biosimilar)</t>
+          <t>Monitored company (Teva) biosimilar FDA approval</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Merck, Daiichi pull lung cancer filing after FDA pushback deals another blow to $4B deal</t>
+          <t>Samsung Biologics cuts antibody drug development time to 9.5 months</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fierce Biotech</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.fiercebiotech.com/biotech/merck-co-and-daiichi-pull-lung-cancer-filing-after-fda-pushback-deals-another-blow-4b-deal</t>
+          <t>https://www.mk.co.kr/news/english/12163637</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28-09-2026 08:30 UTC</t>
+          <t>29-09-2026 05:43 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monitored company biologic regulatory action (BLA withdrawal)</t>
+          <t>Monitored company (Samsung Biologics) CDMO service improvement for biologic development</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,247 +987,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo Says NTK Appeals Tokyo District Court's 203 Billion Yen Claim Dismissal</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/news/daiichi-sankyo-says-ntk-appeals-tokyo-district-court-s-203-billion-yen-claim-dismissal-ce785adcdb8afe21</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>28-09-2026 04:26 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Monitored company patent litigation</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Link Cell Therapies Initiates Clinical Dosing with Logic-Gated CAR-T Therapy, Expands Executive Leadership, and Upsizes Series A Financing to $90 Million</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>The Manila Times</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.manilatimes.net/2026/09/28/tmt-newswire/pr-newswire/link-cell-therapies-initiates-clinical-dosing-with-logic-gated-car-t-therapy-expands-executive-leadership-and-upsizes-series-a-financing-to-90-million/2434075</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>28-09-2026 11:58 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Monitored company advanced therapy clinical trial (CAR-T)</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Fresenius Pours EUR 54 Million Into European Infusion Capacity as NutriChef Lands in Six Markets</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/unternehmensnachrichten/fresenius-pours-eur-54-million-into-european-infusion-capacity-as/70193335</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>28-09-2026 14:11 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Monitored company manufacturing capacity expansion (sterile injectables)</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Alvotech Soars As FDA Breakthrough Ignites Biosimilar Hopes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.tipranks.com/news/catalyst/alvotech-soars-as-fda-breakthrough-ignites-biosimilar-hopes</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>28-09-2026 16:07 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Monitored company FDA regulatory action for biosimilars</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Samsung Biologics cuts complex antibody development timeline to 9.5 months</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Korea Biomedical Review</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33312</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>28-09-2026 06:58 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Monitored company biologic manufacturing innovation</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
           <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Samsung BioLogics Union Broadens Scope of 'Ongoing Management Involvement'</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>아시아경제</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.asiae.co.kr/en/article/2026092719524964396</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>28-09-2026 02:19 UTC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Monitored company manufacturing/operations news (union involvement)</t>
-        </is>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1015,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29-09-2026 00:21:40</t>
+          <t>29-09-2026 15:04:01</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company (Sandoz) biosimilar manufacturing expansion</t>
+          <t>Monitored company Sandoz, biosimilar manufacturing expansion</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sino Biopharma Unit Grants STADA Commercialization License for Pembrolizumab Biosimilar</t>
+          <t>China's Shanghai RAAS to Acquire Boehringer Ingelheim's CDMO Plant in China for Up to 20 Million Yuan, Betting on Hemophilia Drug SR604</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/sino-biopharma-unit-grants-stada-commercialization-license-for-pembrolizumab-biosimilar-ce785adcdd8cff2d</t>
+          <t>https://finance.biggo.com/news/4d371b49-1a71-4480-879d-71082460dc69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28-09-2026 09:56 UTC</t>
+          <t>29-09-2026 09:55 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company (Stada) biosimilar licensing deal</t>
+          <t>Monitored company Boehringer Ingelheim, acquisition of CDMO plant (potential biologic manufacturing)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fact or Fiction: Updates in Hereditary Angioedema</t>
+          <t>BMS’s Opdivo patent suit against Amgen adds to eventful 2026 for biosimilar spats</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medscape Reference</t>
+          <t>iam-media.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://reference.medscape.com/viewarticle/hae-fact-or-fiction-2026a1000wln</t>
+          <t>https://www.iam-media.com/article/bmss-opdivo-patent-suit-against-amgen-adds-eventful-2026-biosimilar-spats</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28-09-2026 19:26 UTC</t>
+          <t>29-09-2026 14:24 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Autoimmune disease (HAE) therapy area news</t>
+          <t>Monitored company Amgen, biosimilar patent litigation</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Organon Canada Announces the Approval and Availability of NDUVRA® (Tapinarof Cream), 1%, a New Steroid-Free Topical Treatment for Moderate to Severe Atopic Dermatitis in Adult and Pediatric Patients 2 Years of Age and Older</t>
+          <t>Pfizer, Moderna lose bids to escape Bayer US mRNA patent lawsuit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PR Newswire Canada</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.newswire.ca/news-releases/organon-canada-announces-the-approval-and-availability-of-nduvra-r-tapinarof-cream-1-a-new-steroid-free-topical-treatment-for-moderate-to-severe-atopic-dermatitis-in-adult-and-pediatric-patients-2-years-of-age-and-older-842702881.html</t>
+          <t>https://www.reuters.com/legal/legalindustry/pfizer-moderna-lose-bids-escape-bayer-us-mrna-patent-lawsuit-2026-09-28/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28-09-2026 12:01 UTC</t>
+          <t>28-09-2026 19:42 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company (Organon) approval in dermatology/autoimmune disease</t>
+          <t>Monitored company Pfizer, biologic patent litigation</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How Significant Is Abatacept Biosimilar Approval for Dr. Reddy’s?</t>
+          <t>Biocon Malaysia wins UK clearance as IOL Chemicals, NATCO Pharma advance Europe and capital plans</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Motilal Oswal</t>
+          <t>Indiatimes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.motilaloswal.com/news/stocks/129811</t>
+          <t>https://chemicals.economictimes.indiatimes.com/news/policy-and-regulation/biocon-malaysia-wins-uk-clearance-as-iol-chemicals-natco-pharma-advance-europe-and-capital-plans/134538932</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28-09-2026 11:18 UTC</t>
+          <t>28-09-2026 17:30 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company (Dr. Reddy's) biosimilar approval (Abatacept for autoimmune disease)</t>
+          <t>Monitored company Biocon, biosimilar/biologic regulatory clearance (UK)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Biocon Malaysia Receives UK Approval for Insulin Fill-Finish Unit</t>
+          <t>USFDA concludes inspection at Zydus Life's SEZ II Ahmedabad plant with 1 observation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Machine Maker</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://themachinemaker.com/news/biocon-malaysia-receives-uk-approval-for-insulin-fill-finish-unit/</t>
+          <t>https://www.indianpharmapost.com/news/usfda-concludes-inspection-at-zydus-lifes-sez-ii-ahmedabad-plant-with-1-observation-22009</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28-09-2026 10:30 UTC</t>
+          <t>29-09-2026 03:07 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company (Biocon) biologic manufacturing approval (insulin fill-finish)</t>
+          <t>Monitored company Zydus Biotech, FDA inspection with observation at plant</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USFDA concludes inspection at Zydus Life's SEZ II Ahmedabad plant with 1 observation</t>
+          <t>Celltrion targets CDMO deals, supply-chain partners at CPHI 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/usfda-concludes-inspection-at-zydus-lifes-sez-ii-ahmedabad-plant-with-1-observation-22009</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33324</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29-09-2026 03:07 UTC</t>
+          <t>29-09-2026 05:18 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company (Zydus Biotech) FDA inspection with observation</t>
+          <t>Monitored company Celltrion, CDMO deals and partnering at industry meeting</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Celltrion targets CDMO deals, supply-chain partners at CPHI 2026</t>
+          <t>Daiichi Sankyo, Merck withdraw bid for accelerated approval of I-DXd in small cell lung cancer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Managed Healthcare Executive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33324</t>
+          <t>https://www.managedhealthcareexecutive.com/view/daiichi-sankyo-merck-withdraw-bid-for-accelerated-approval-of-i-dxd-in-small-cell-lung-cancer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29-09-2026 05:53 UTC</t>
+          <t>28-09-2026 21:04 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored company (Celltrion) seeking CDMO and drug pipeline partnerships</t>
+          <t>Monitored company Daiichi Sankyo, regulatory withdrawal for biologic ADC</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo, Merck Pull Ifinatamab Deruxtecan BLA in SCLC</t>
+          <t>Kyowa Kirin and Knight Therapeutics Enter Into Exclusive Distribution Agreement for POTELIGEO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.biopharminternational.com/view/daiichi-sankyo-merck-pull-ifinatamab-deruxtecan-bla-sclc</t>
+          <t>https://www.businesswire.com/news/home/20260929434860/en/Kyowa-Kirin-and-Knight-Therapeutics-Enter-Into-Exclusive-Distribution-Agreement-for-POTELIGEO-mogamulizumab-for-Cutaneous-T-Cell-Lymphoma-CTCL-Patients-Across-Latin-America</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28-09-2026 16:35 UTC</t>
+          <t>29-09-2026 12:00 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored company (Daiichi Sankyo) biologic (ADC) BLA withdrawal (regulatory action)</t>
+          <t>Monitored company Kyowa Kirin, distribution agreement for biologic (monoclonal antibody)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -839,27 +839,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fresenius Pours EUR 54 Million Into European Infusion Capacity as NutriChef Lands in Six Markets</t>
+          <t>Waltz Health and Fresenius Kabi Expand Direct Access to Biosimilars Through Waltz Connect Platform</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/unternehmensnachrichten/fresenius-pours-eur-54-million-into-european-infusion-capacity-as/70193335</t>
+          <t>https://www.prnewswire.com/news-releases/waltz-health-and-fresenius-kabi-expand-direct-access-to-biosimilars-through-waltz-connect-platform-302892345.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28-09-2026 14:11 UTC</t>
+          <t>29-09-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitored company (Fresenius Kabi) manufacturing capacity expansion for sterile products</t>
+          <t>Monitored company Fresenius Kabi, biosimilar market access/commercial event</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alvotech Soars As FDA Breakthrough Ignites Biosimilar Hopes</t>
+          <t>Teva Receives U.S. FDA Approval for Denosumab Biosimilar for Oncology Indications</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/catalyst/alvotech-soars-as-fda-breakthrough-ignites-biosimilar-hopes</t>
+          <t>https://oncodaily.com/not-to-miss/denosumab-biosimilar-596674</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28-09-2026 16:07 UTC</t>
+          <t>29-09-2026 10:36 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitored company (Alvotech) FDA biosimilar breakthrough news</t>
+          <t>Monitored company Teva, biosimilar FDA approval</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,85 +907,45 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teva Continues Biosimilar Momentum with U.S. FDA Approval of DEGEVMA™ (denosumab-adet), a Biosimilar to Xgeva® (denosumab)</t>
+          <t>Samsung Biologics cuts antibody drug development time to 9.5 months</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Macau Business</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://macaubusiness.com/teva-continues-biosimilar-momentum-with-u-s-fda-approval-of-degevma-denosumab-adet-a-biosimilar-to-xgeva-denosumab/</t>
+          <t>https://www.mk.co.kr/news/english/12163637</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29-09-2026 02:42 UTC</t>
+          <t>29-09-2026 05:43 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monitored company (Teva) biosimilar FDA approval</t>
+          <t>Monitored company Samsung Biologics, biologic CDMO capability improvement</t>
         </is>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Samsung Biologics cuts antibody drug development time to 9.5 months</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>매일경제</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/english/12163637</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>29-09-2026 05:43 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Monitored company (Samsung Biologics) CDMO service improvement for biologic development</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
@@ -1015,7 +975,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29-09-2026 15:04:01</t>
+          <t>29-09-2026 22:40:18</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz opens advanced high-volume drug substance manufacturing centre in Lendava, significantly strengthening in-house capacity and flexibility across leading European biosimilar network</t>
+          <t>Sandoz opens biosimilar production plant in Slovenia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>SeeNews</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.sandoz.com/sandoz-opens-advanced-high-volume-drug-substance-manufacturing-centre-lendava-significantly</t>
+          <t>https://seenews.com/news/sandoz-opens-biosimilar-production-plant-in-slovenia-1302085</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29-09-2026 05:33 UTC</t>
+          <t>29-09-2026 14:12 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company Sandoz, biosimilar manufacturing expansion</t>
+          <t>Biologic or biosimilar manufacturing expansion by a monitored company (Sandoz)</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -539,7 +539,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company Boehringer Ingelheim, acquisition of CDMO plant (potential biologic manufacturing)</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition (CDMO plant acquisition for biologics)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BMS’s Opdivo patent suit against Amgen adds to eventful 2026 for biosimilar spats</t>
+          <t>Amgen Readies Daxdilimab For Phase III In Discoid Lupus After Mid-Stage Trial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iam-media.com</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.iam-media.com/article/bmss-opdivo-patent-suit-against-amgen-adds-eventful-2026-biosimilar-spats</t>
+          <t>https://insights.citeline.com/scrip/scrip/r-and-d/clinical-trials/amgen-readies-daxdilimab-for-phase-iii-in-discoid-lupus-after-mid-stage-trial-O7Z3KNGGKVCK5FUZYCMDYG3FNQ/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29-09-2026 14:24 UTC</t>
+          <t>30-09-2026 05:06 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company Amgen, biosimilar patent litigation</t>
+          <t>Clinical trials &amp; pipeline news (Phase III for biologic in autoimmune disease)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pfizer, Moderna lose bids to escape Bayer US mRNA patent lawsuit</t>
+          <t>amgen weight loss drug trial update</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>polskieradio.pl</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/legalindustry/pfizer-moderna-lose-bids-escape-bayer-us-mrna-patent-lawsuit-2026-09-28/</t>
+          <t>https://www.polskieradio.pl/health-library/en-SE/amgen-weight-loss-drug-trial-update</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28-09-2026 19:42 UTC</t>
+          <t>30-09-2026 01:38 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company Pfizer, biologic patent litigation</t>
+          <t>Monitored company pipeline news (Amgen weight loss drug trial, likely biologic)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Biocon Malaysia wins UK clearance as IOL Chemicals, NATCO Pharma advance Europe and capital plans</t>
+          <t>Sun Pharma plans ₹10,000 crore bond sale to refinance Organon acquisition loan: Report</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indiatimes</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://chemicals.economictimes.indiatimes.com/news/policy-and-regulation/biocon-malaysia-wins-uk-clearance-as-iol-chemicals-natco-pharma-advance-europe-and-capital-plans/134538932</t>
+          <t>https://www.livemint.com/companies/news/sun-pharma-plans-rs-10-000-crore-bond-sale-to-refinance-organon-acquisition-loan-report-11790695336859.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28-09-2026 17:30 UTC</t>
+          <t>29-09-2026 15:45 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company Biocon, biosimilar/biologic regulatory clearance (UK)</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition (refinancing related to monitored company's acquisition)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USFDA concludes inspection at Zydus Life's SEZ II Ahmedabad plant with 1 observation</t>
+          <t>new pfizer weight loss drug</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>polskieradio.pl</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/usfda-concludes-inspection-at-zydus-lifes-sez-ii-ahmedabad-plant-with-1-observation-22009</t>
+          <t>https://www.polskieradio.pl/healthy-living/new-pfizer-weight-loss-drug</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29-09-2026 03:07 UTC</t>
+          <t>30-09-2026 08:05 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company Zydus Biotech, FDA inspection with observation at plant</t>
+          <t>Monitored company pipeline news (Pfizer weight loss drug trial, potential biologic)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celltrion targets CDMO deals, supply-chain partners at CPHI 2026</t>
+          <t>Pfizer, BioNTech and Moderna Must Face Bayer Patent Lawsuits Over COVID-19 Vaccines</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Law Commentary</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33324</t>
+          <t>https://www.lawcommentary.com/articles/pfizer-moderna-biontech-bayer-covid-vaccine-patent-lawsuits</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29-09-2026 05:18 UTC</t>
+          <t>29-09-2026 16:26 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company Celltrion, CDMO deals and partnering at industry meeting</t>
+          <t>Biosimilars &amp; Biologics (patent litigation involving biologics from a monitored company)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo, Merck withdraw bid for accelerated approval of I-DXd in small cell lung cancer</t>
+          <t>Kyowa Kirin and Knight Therapeutics Enter Into Exclusive Distribution Agreement for POTELIGEO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Managed Healthcare Executive</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.managedhealthcareexecutive.com/view/daiichi-sankyo-merck-withdraw-bid-for-accelerated-approval-of-i-dxd-in-small-cell-lung-cancer</t>
+          <t>https://www.businesswire.com/news/home/20260929434860/en/Kyowa-Kirin-and-Knight-Therapeutics-Enter-Into-Exclusive-Distribution-Agreement-for-POTELIGEO-mogamulizumab-for-Cutaneous-T-Cell-Lymphoma-CTCL-Patients-Across-Latin-America</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28-09-2026 21:04 UTC</t>
+          <t>29-09-2026 12:00 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored company Daiichi Sankyo, regulatory withdrawal for biologic ADC</t>
+          <t>Partnerships, Deals, Licensing &amp; Acquisition (distribution deal for biologic in immunology)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kyowa Kirin and Knight Therapeutics Enter Into Exclusive Distribution Agreement for POTELIGEO</t>
+          <t>Why Waltz Health, Fresenius Kabi Are Taking Biosimilars Direct</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Pharmaceutical Commerce</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260929434860/en/Kyowa-Kirin-and-Knight-Therapeutics-Enter-Into-Exclusive-Distribution-Agreement-for-POTELIGEO-mogamulizumab-for-Cutaneous-T-Cell-Lymphoma-CTCL-Patients-Across-Latin-America</t>
+          <t>https://www.pharmaceuticalcommerce.com/view/why-waltz-health-fresenius-kabi-are-taking-biosimilars-direct</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29-09-2026 12:00 UTC</t>
+          <t>29-09-2026 13:09 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored company Kyowa Kirin, distribution agreement for biologic (monoclonal antibody)</t>
+          <t>Biosimilars &amp; Biologics (commercialization strategy for biosimilars)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -839,27 +839,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waltz Health and Fresenius Kabi Expand Direct Access to Biosimilars Through Waltz Connect Platform</t>
+          <t>​FDA cites ‘significant violations,’ including hair in drugs, at suburban Fresenius plant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Crain's Chicago Business</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/waltz-health-and-fresenius-kabi-expand-direct-access-to-biosimilars-through-waltz-connect-platform-302892345.html</t>
+          <t>https://www.chicagobusiness.com/health-care/ccb-fresenius-kabi-fda-warning-illinois-20260929/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29-09-2026 13:00 UTC</t>
+          <t>29-09-2026 16:09 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitored company Fresenius Kabi, biosimilar market access/commercial event</t>
+          <t>FDA / Regulatory Actions &amp; Manufacturing, Supply Chain &amp; Capacity (FDA inspection violations at Fresenius plant)</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -879,27 +879,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teva Receives U.S. FDA Approval for Denosumab Biosimilar for Oncology Indications</t>
+          <t>Teva Continues Biosimilar Momentum with U.S. FDA Approval of DEGEVMA (denosumab-adet), a Biosimilar to Xgeva (denosumab)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>Indovizka.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/not-to-miss/denosumab-biosimilar-596674</t>
+          <t>https://indovizka.com/news/detail/23028/teva-continues-biosimilar-momentum-with-us-fda-approval-of-degevma-denosumabadet-a-biosimilar-to-xgeva-denosumab</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29-09-2026 10:36 UTC</t>
+          <t>29-09-2026 13:04 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitored company Teva, biosimilar FDA approval</t>
+          <t>Biosimilars &amp; Biologics (FDA approval of biosimilar)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,40 +914,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Construction Begins on 'K-Bio Lab Hub' in Songdo, Incheon...Support for Bio Startup Growth</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.asiae.co.kr/en/article/region/2026093009552052417</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>30-09-2026 06:12 UTC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (groundbreaking for biotech hub, supporting biologics R&amp;D/manufacturing)</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Samsung Biologics cuts antibody drug development time to 9.5 months</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>매일경제</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/news/english/12163637</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>29-09-2026 05:43 UTC</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Monitored company Samsung Biologics, biologic CDMO capability improvement</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Integrated Development and Manufacturing for Complex Bioconjugation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fierce Pharma</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.fiercepharma.com/premium/webinar/1383673</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30-09-2026 02:49 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (integrated development and manufacturing for biologics)</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Samsung Biologics union, management resume talks as strike prep escalates in Korea - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-science/2026/09/30/4V6WP7PXMRBWVEC5UMXWWNAKV4/?outputType=amp</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>30-09-2026 06:52 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Manufacturing, Supply Chain &amp; Capacity (labor dispute affecting biologic manufacturing supply)</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -975,7 +1055,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29-09-2026 22:40:18</t>
+          <t>30-09-2026 14:56:09</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz opens biosimilar production plant in Slovenia</t>
+          <t>Technology transfer expert insights | BioXcellence</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SeeNews</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://seenews.com/news/sandoz-opens-biosimilar-production-plant-in-slovenia-1302085</t>
+          <t>https://www.boehringer-ingelheim.com/partnering/boehringer-ingelheim-bioxcellence/newsroom/technology-transfer-expert-insights-bioxcellence</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29-09-2026 14:12 UTC</t>
+          <t>30-09-2026 13:50 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Biologic or biosimilar manufacturing expansion by a monitored company (Sandoz)</t>
+          <t>Manufacturing, supply chain &amp; capacity (Technology transfer for biologics by a monitored company).</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>China's Shanghai RAAS to Acquire Boehringer Ingelheim's CDMO Plant in China for Up to 20 Million Yuan, Betting on Hemophilia Drug SR604</t>
+          <t>Amgen reveals 6-point drop in lupus severity behind phase 2 win for Horizon antibody</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Fierce Biotech</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/4d371b49-1a71-4480-879d-71082460dc69</t>
+          <t>https://www.fiercebiotech.com/biotech/amgen-reveals-6-point-drop-lupus-severity-behind-phase-2-win-horizon-antibody</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29-09-2026 09:55 UTC</t>
+          <t>30-09-2026 08:26 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition (CDMO plant acquisition for biologics)</t>
+          <t>Clinical trials &amp; pipeline news (Monitored company's biologic antibody for autoimmune disease).</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -569,17 +569,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/scrip/scrip/r-and-d/clinical-trials/amgen-readies-daxdilimab-for-phase-iii-in-discoid-lupus-after-mid-stage-trial-O7Z3KNGGKVCK5FUZYCMDYG3FNQ/</t>
+          <t>https://insights.citeline.com/scrip/r-and-d/clinical-trials/amgen-readies-daxdilimab-for-phase-iii-in-discoid-lupus-after-mid-stage-trial-O7Z3KNGGKVCK5FUZYCMDYG3FNQ/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30-09-2026 05:06 UTC</t>
+          <t>30-09-2026 10:40 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news (Phase III for biologic in autoimmune disease)</t>
+          <t>Clinical trials &amp; pipeline news (Monitored company's biologic pipeline in autoimmune disease).</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -599,27 +599,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>amgen weight loss drug trial update</t>
+          <t>Experimental therapy rapidly lowers disease activity in Sjögren’s trial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>polskieradio.pl</t>
+          <t>Sjogren's Disease News</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.polskieradio.pl/health-library/en-SE/amgen-weight-loss-drug-trial-update</t>
+          <t>https://sjogrenssyndromenews.com/news/experimental-therapy-lowers-disease-activity-sjogrens-trial/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30-09-2026 01:38 UTC</t>
+          <t>30-09-2026 14:32 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company pipeline news (Amgen weight loss drug trial, likely biologic)</t>
+          <t>Clinical trials &amp; pipeline news (Monitored company's therapy in autoimmune disease).</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sun Pharma plans ₹10,000 crore bond sale to refinance Organon acquisition loan: Report</t>
+          <t>Aurobindo's CuraTeQ Biologics Reports Positive Phase 3 Results for Omalizumab Biosimilar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/companies/news/sun-pharma-plans-rs-10-000-crore-bond-sale-to-refinance-organon-acquisition-loan-report-11790695336859.html</t>
+          <t>https://scanx.trade/stock-market-news/companies/curateq-biologics-achieves-positive-phase-3-results-for-omalizumab-biosimilar-bp11/37029552</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29-09-2026 15:45 UTC</t>
+          <t>29-09-2026 23:00 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition (refinancing related to monitored company's acquisition)</t>
+          <t>Biosimilars &amp; biologics (Phase 3 results for omalizumab biosimilar by a monitored company).</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>new pfizer weight loss drug</t>
+          <t>Shilpa Biologicals unveils new gene to GMP manufacturing platform SB HiMax for biotechs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>polskieradio.pl</t>
+          <t>BioSpectrum India</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.polskieradio.pl/healthy-living/new-pfizer-weight-loss-drug</t>
+          <t>https://www.biospectrumindia.com/news/16/28580/shilpa-biologicals-unveils-new-gene-to-gmp-manufacturing-platform-sb-himax-for-biotechs-.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30-09-2026 08:05 UTC</t>
+          <t>30-09-2026 12:18 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company pipeline news (Pfizer weight loss drug trial, potential biologic)</t>
+          <t>Manufacturing, supply chain &amp; capacity (New GMP manufacturing platform for biologics by a monitored company).</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pfizer, BioNTech and Moderna Must Face Bayer Patent Lawsuits Over COVID-19 Vaccines</t>
+          <t>I-DXd withdrawal thins October PDUFA calendar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Law Commentary</t>
+          <t>biocentury.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.lawcommentary.com/articles/pfizer-moderna-biontech-bayer-covid-vaccine-patent-lawsuits</t>
+          <t>https://www.biocentury.com/article/660934/i-dxd-withdrawal-thins-october-pdufa-calendar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29-09-2026 16:26 UTC</t>
+          <t>30-09-2026 01:27 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics (patent litigation involving biologics from a monitored company)</t>
+          <t>FDA / Regulatory Actions (PDUFA calendar change for a biologic/monoclonal antibody from a monitored company).</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -754,32 +754,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kyowa Kirin and Knight Therapeutics Enter Into Exclusive Distribution Agreement for POTELIGEO</t>
+          <t>Turbine Deepens ADC Discovery Collaboration With Daiichi Sankyo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260929434860/en/Kyowa-Kirin-and-Knight-Therapeutics-Enter-Into-Exclusive-Distribution-Agreement-for-POTELIGEO-mogamulizumab-for-Cutaneous-T-Cell-Lymphoma-CTCL-Patients-Across-Latin-America</t>
+          <t>https://www.tipranks.com/news/private-companies/turbine-deepens-adc-discovery-collaboration-with-daiichi-sankyo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29-09-2026 12:00 UTC</t>
+          <t>30-09-2026 09:00 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Partnerships, Deals, Licensing &amp; Acquisition (distribution deal for biologic in immunology)</t>
+          <t>Partnerships, deals, licensing &amp; acquisition (Monitored company deepens ADC/biologic discovery collaboration).</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why Waltz Health, Fresenius Kabi Are Taking Biosimilars Direct</t>
+          <t>Kyowa Kirin, Knight agree Latin American distribution deal for mogamulizumab</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pharmaceutical Commerce</t>
+          <t>Pharmaceutical Business review -</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pharmaceuticalcommerce.com/view/why-waltz-health-fresenius-kabi-are-taking-biosimilars-direct</t>
+          <t>https://www.pharmaceutical-business-review.com/news/kyowa-kirin-knight-latin-american-distribution-mogamulizumab/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29-09-2026 13:09 UTC</t>
+          <t>30-09-2026 09:49 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics (commercialization strategy for biosimilars)</t>
+          <t>Partnerships, deals, licensing &amp; acquisition (Monitored company's distribution deal for a biologic).</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -839,27 +839,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>​FDA cites ‘significant violations,’ including hair in drugs, at suburban Fresenius plant</t>
+          <t>FDA warns Fresenius Kabi over sterile manufacturing violations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Crain's Chicago Business</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.chicagobusiness.com/health-care/ccb-fresenius-kabi-fda-warning-illinois-20260929/</t>
+          <t>https://manufacturingchemist.com/fda-warns-fresenius-kabi-over-sterile-manufacturing-violations</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29-09-2026 16:09 UTC</t>
+          <t>30-09-2026 14:30 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions &amp; Manufacturing, Supply Chain &amp; Capacity (FDA inspection violations at Fresenius plant)</t>
+          <t>FDA / Regulatory Actions (FDA warning letter for sterile manufacturing violations by a monitored company).</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teva Continues Biosimilar Momentum with U.S. FDA Approval of DEGEVMA (denosumab-adet), a Biosimilar to Xgeva (denosumab)</t>
+          <t>Waltz Health, Fresenius Kabi partner for direct-to-payer biosimilar program</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indovizka.com</t>
+          <t>Fierce Healthcare</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://indovizka.com/news/detail/23028/teva-continues-biosimilar-momentum-with-us-fda-approval-of-degevma-denosumabadet-a-biosimilar-to-xgeva-denosumab</t>
+          <t>https://www.fiercehealthcare.com/payers/waltz-health-fresenius-kabi-partner-direct-payer-biosimilar-program</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29-09-2026 13:04 UTC</t>
+          <t>29-09-2026 19:18 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; Biologics (FDA approval of biosimilar)</t>
+          <t>Biosimilars &amp; biologics (Monitored company partners for direct-to-payer biosimilar program).</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,39 +907,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Construction Begins on 'K-Bio Lab Hub' in Songdo, Incheon...Support for Bio Startup Growth</t>
+          <t>Teva Continues Biosimilar Momentum with U.S. FDA Approval of DEGEVMA (denosumab-adet), a Biosimilar to Xgeva (denosumab)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>riauone.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/region/2026093009552052417</t>
+          <t>https://www.riauone.com/global/sub/GlobeNewswire/Teva-Continues-Biosimilar-Momentum-with-U-S--FDA-Approval-of-DEGEVMA--denosumab-adet---a-Biosimilar-to-Xgeva--denosumab-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30-09-2026 06:12 UTC</t>
+          <t>29-09-2026 20:19 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (groundbreaking for biotech hub, supporting biologics R&amp;D/manufacturing)</t>
+          <t>Biosimilars &amp; biologics (US FDA approval of denosumab biosimilar by a monitored company).</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Integrated Development and Manufacturing for Complex Bioconjugation</t>
+          <t>Construction Begins on 'K-Bio Lab Hub' in Songdo, Incheon...Support for Bio Startup Growth</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/premium/webinar/1383673</t>
+          <t>https://www.asiae.co.kr/en/article/region/2026093009552052417</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30-09-2026 02:49 UTC</t>
+          <t>30-09-2026 06:12 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (integrated development and manufacturing for biologics)</t>
+          <t>Industry meetings &amp; conferences (Construction begins on K-Bio Lab Hub, relevant to biologics industry).</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -987,7 +987,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -999,33 +999,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Integrated Development and Manufacturing for Complex Bioconjugation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fierce Pharma</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.fiercepharma.com/premium/webinar/1383673</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>30-09-2026 02:49 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Manufacturing, supply chain &amp; capacity (Integrated development &amp; manufacturing for bioconjugation by a monitored company).</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Samsung Biologics union, management resume talks as strike prep escalates in Korea - CHOSUNBIZ</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Chosunbiz</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://biz.chosun.com/en/en-science/2026/09/30/4V6WP7PXMRBWVEC5UMXWWNAKV4/?outputType=amp</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>30-09-2026 06:52 UTC</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Manufacturing, Supply Chain &amp; Capacity (labor dispute affecting biologic manufacturing supply)</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Manufacturing, supply chain &amp; capacity (Labor talks/strike prep at a monitored biologic manufacturing company).</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1055,7 +1095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30-09-2026 14:56:09</t>
+          <t>30-09-2026 22:40:25</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manufacturing, supply chain &amp; capacity (Technology transfer for biologics by a monitored company).</t>
+          <t>Monitored company news, relevant to biologic manufacturing/CDMO (Category 5, 6, 8).</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amgen reveals 6-point drop in lupus severity behind phase 2 win for Horizon antibody</t>
+          <t>amgen weight loss drug trial update</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fierce Biotech</t>
+          <t>polskieradio.pl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.fiercebiotech.com/biotech/amgen-reveals-6-point-drop-lupus-severity-behind-phase-2-win-horizon-antibody</t>
+          <t>https://www.polskieradio.pl/healthy-living/hr/amgen-weight-loss-drug-trial-update</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30-09-2026 08:26 UTC</t>
+          <t>30-09-2026 17:15 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news (Monitored company's biologic antibody for autoimmune disease).</t>
+          <t>Monitored company's clinical pipeline news (biologic for weight loss) (Category 7, 8).</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -579,7 +579,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news (Monitored company's biologic pipeline in autoimmune disease).</t>
+          <t>Monitored company's clinical trial news for an autoimmune biologic (Category 7, 8).</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -599,27 +599,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Experimental therapy rapidly lowers disease activity in Sjögren’s trial</t>
+          <t>Amgen's GIP Blocker Mirrors Lilly's Zepbound</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sjogren's Disease News</t>
+          <t>Briefs Finance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://sjogrenssyndromenews.com/news/experimental-therapy-lowers-disease-activity-sjogrens-trial/</t>
+          <t>https://www.briefs.co/news/amgen-s-gip-blocker-might-end-up-doing-what-lilly-s-gip-acti/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30-09-2026 14:32 UTC</t>
+          <t>30-09-2026 19:40 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news (Monitored company's therapy in autoimmune disease).</t>
+          <t>Monitored company's clinical pipeline news (biologic for weight loss) (Category 7, 8).</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aurobindo's CuraTeQ Biologics Reports Positive Phase 3 Results for Omalizumab Biosimilar</t>
+          <t>Experimental therapy rapidly lowers disease activity in Sjögren’s trial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Sjogren's Disease News</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/curateq-biologics-achieves-positive-phase-3-results-for-omalizumab-biosimilar-bp11/37029552</t>
+          <t>https://sjogrenssyndromenews.com/news/experimental-therapy-lowers-disease-activity-sjogrens-trial/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29-09-2026 23:00 UTC</t>
+          <t>30-09-2026 14:32 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics (Phase 3 results for omalizumab biosimilar by a monitored company).</t>
+          <t>Monitored company's clinical trial news for an autoimmune therapy (Category 7, 8).</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -674,32 +674,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals unveils new gene to GMP manufacturing platform SB HiMax for biotechs</t>
+          <t>Therapeutic Antibody Market Is Going to Boom |• Roche • AbbVie • Amgen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BioSpectrum India</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.biospectrumindia.com/news/16/28580/shilpa-biologicals-unveils-new-gene-to-gmp-manufacturing-platform-sb-himax-for-biotechs-.html</t>
+          <t>https://www.openpr.com/news/4649306/therapeutic-antibody-market-is-going-to-boom-roche</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30-09-2026 12:18 UTC</t>
+          <t>01-10-2026 03:36 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Manufacturing, supply chain &amp; capacity (New GMP manufacturing platform for biologics by a monitored company).</t>
+          <t>Monitored company mentioned in therapeutic antibody market news (Category 2, 4, 8).</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I-DXd withdrawal thins October PDUFA calendar</t>
+          <t>Sun Pharma Eyes Rs 10,000 Crore Bond Sale to Fund Organon Acquisition Loan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>biocentury.com</t>
+          <t>medicaldialogues.in</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.biocentury.com/article/660934/i-dxd-withdrawal-thins-october-pdufa-calendar</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/sun-pharma-eyes-rs-10000-crore-bond-sale-to-fund-organon-acquisition-loan-180353</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30-09-2026 01:27 UTC</t>
+          <t>30-09-2026 13:24 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions (PDUFA calendar change for a biologic/monoclonal antibody from a monitored company).</t>
+          <t>Monitored company acquisition/financing news (Category 6, 8).</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Turbine Deepens ADC Discovery Collaboration With Daiichi Sankyo</t>
+          <t>pfizer stops weight loss drug</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>polskieradio.pl</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/private-companies/turbine-deepens-adc-discovery-collaboration-with-daiichi-sankyo</t>
+          <t>https://www.polskieradio.pl/bonusesr/en-FI/crash-bet365-guia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30-09-2026 09:00 UTC</t>
+          <t>01-10-2026 07:35 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Partnerships, deals, licensing &amp; acquisition (Monitored company deepens ADC/biologic discovery collaboration).</t>
+          <t>Monitored company's clinical pipeline news (Category 7, 8).</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kyowa Kirin, Knight agree Latin American distribution deal for mogamulizumab</t>
+          <t>Pfizer’s Phase II Atopic Dermatitis Data Push Tilrekimig Into Pivotal AD, Asthma Trials</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pharmaceutical Business review -</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-business-review.com/news/kyowa-kirin-knight-latin-american-distribution-mogamulizumab/</t>
+          <t>https://insights.citeline.com/scrip/r-and-d/clinical-trials/pfizers-phase-ii-atopic-dermatitis-data-push-tilrekimig-into-pivotal-ad-asthma-trials-KDJR2KQ4CZFCBFKLIMLADRSHAA/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30-09-2026 09:49 UTC</t>
+          <t>01-10-2026 06:41 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Partnerships, deals, licensing &amp; acquisition (Monitored company's distribution deal for a biologic).</t>
+          <t>Monitored company's clinical trial news for an immunology biologic (Category 7, 8).</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FDA warns Fresenius Kabi over sterile manufacturing violations</t>
+          <t>Aurobindo Pharma launches ADQUEY™ in US and establishes dedicated dermatology biz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>biospectrumindia.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://manufacturingchemist.com/fda-warns-fresenius-kabi-over-sterile-manufacturing-violations</t>
+          <t>https://www.biospectrumindia.com/news/16/28581/aurobindo-pharma-launches-adquey-in-us-and-establishes-dedicated-dermatology-biz.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30-09-2026 14:30 UTC</t>
+          <t>30-09-2026 17:47 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FDA / Regulatory Actions (FDA warning letter for sterile manufacturing violations by a monitored company).</t>
+          <t>Monitored company market launch and strategic business expansion in dermatology (Category 4, 8).</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Waltz Health, Fresenius Kabi partner for direct-to-payer biosimilar program</t>
+          <t>Shilpa Biologicals launches SB HiMax platform at CPHI Milan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fierce Healthcare</t>
+          <t>Pharmabiz.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fiercehealthcare.com/payers/waltz-health-fresenius-kabi-partner-direct-payer-biosimilar-program</t>
+          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=190988&amp;sid=2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29-09-2026 19:18 UTC</t>
+          <t>01-10-2026 05:46 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics (Monitored company partners for direct-to-payer biosimilar program).</t>
+          <t>Monitored company launches biologic manufacturing platform at industry conference (Category 5, 8, 10).</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,32 +914,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teva Continues Biosimilar Momentum with U.S. FDA Approval of DEGEVMA (denosumab-adet), a Biosimilar to Xgeva (denosumab)</t>
+          <t>Samsung Bioepis and Teva Expand Strategic Partnership to Advance Up to Six Potential Biosimilar Candidates</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>riauone.com</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.riauone.com/global/sub/GlobeNewswire/Teva-Continues-Biosimilar-Momentum-with-U-S--FDA-Approval-of-DEGEVMA--denosumab-adet---a-Biosimilar-to-Xgeva--denosumab-</t>
+          <t>https://www.businesswire.com/news/home/20261001835078/en/Samsung-Bioepis-and-Teva-Expand-Strategic-Partnership-to-Advance-Up-to-Six-Potential-Biosimilar-Candidates</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29-09-2026 20:19 UTC</t>
+          <t>01-10-2026 08:30 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Biosimilars &amp; biologics (US FDA approval of denosumab biosimilar by a monitored company).</t>
+          <t>Monitored companies' biosimilar partnership expansion (Category 2, 6, 8).</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Construction Begins on 'K-Bio Lab Hub' in Songdo, Incheon...Support for Bio Startup Growth</t>
+          <t>Celltrion Secures Successive New Biosimilar Contracts in Northern Europe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/region/2026093009552052417</t>
+          <t>https://finance.biggo.com/news/bec1c7bc-2ee2-4434-bfdf-ff5f4f986775</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30-09-2026 06:12 UTC</t>
+          <t>01-10-2026 06:55 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Industry meetings &amp; conferences (Construction begins on K-Bio Lab Hub, relevant to biologics industry).</t>
+          <t>Monitored company's biosimilar market access/commercial news (Category 2, 4, 8).</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -994,32 +994,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Integrated Development and Manufacturing for Complex Bioconjugation</t>
+          <t>Is Daiichi Sankyo Company (TSE:4568) Undervalued On Its Ifinatamab Filing Withdrawal?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/premium/webinar/1383673</t>
+          <t>https://finance.yahoo.com/markets/stocks/articles/daiichi-sankyo-company-tse-4568-060732771.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30-09-2026 02:49 UTC</t>
+          <t>01-10-2026 06:07 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manufacturing, supply chain &amp; capacity (Integrated development &amp; manufacturing for bioconjugation by a monitored company).</t>
+          <t>Monitored company's biologic regulatory/pipeline news (Category 3, 7, 8).</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1027,45 +1027,325 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin, Knight agree Latin American distribution deal for mogamulizumab</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pharmaceutical Business review -</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.pharmaceutical-business-review.com/news/kyowa-kirin-knight-latin-american-distribution-mogamulizumab/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>30-09-2026 09:49 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Monitored company's biologic distribution deal (Category 6, 8).</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FDA hits 2nd Fresenius site with contamination-related warning letter in less than a month</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fiercepharma.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.fiercepharma.com/ai-and-machine-learning/second-fresenius-site-hit-fda-warning-letter-citing-contamination-concerns</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>30-09-2026 19:55 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Monitored company's manufacturing FDA warning letter (Category 3, 5, 8).</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fresenius completes acquisition of mAbxience, creating a stronger platform for future portfolio expansion</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BioSpace</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/fresenius-completes-acquisition-of-mabxience-creating-a-stronger-platform-for-future-portfolio-expansion</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>01-10-2026 06:08 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Monitored company's acquisition of a biosimilar platform (Category 2, 6, 8).</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuji Pharma</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fujifilm to Showcase Manufacturing Innovation and Leadership at CPHI 2026 Amid Three Award Shortlist Nominations</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/news/fujifilm-to-showcase-manufacturing-innovation-and-leadership-at-cphi-2026-amid-three-award-shortlist-ce785ad3df88f424</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>01-10-2026 08:18 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Monitored company's biologic manufacturing news at industry conference (Category 5, 8, 10).</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis and Teva Expand Strategic Partnership to Advance Up to Six Potential Biosimilar Candidates</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20261001835078/en/Samsung-Bioepis-and-Teva-Expand-Strategic-Partnership-to-Advance-Up-to-Six-Potential-Biosimilar-Candidates</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>01-10-2026 08:30 UTC</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Monitored companies' biosimilar partnership expansion (Category 2, 6, 8).</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Teva's Denosumab-Adet (Degevma) Approved as Xgeva Biosimilar</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BioPharm International</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.biopharminternational.com/view/teva-denosumab-adet-degevma-approved-xgeva-biosimilar</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>30-09-2026 16:39 UTC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Monitored company's biosimilar FDA approval (Category 2, 3, 8).</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Samsung Biologics union, management resume talks as strike prep escalates in Korea - CHOSUNBIZ</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/30/4V6WP7PXMRBWVEC5UMXWWNAKV4/?outputType=amp</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>30-09-2026 06:52 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Manufacturing, supply chain &amp; capacity (Labor talks/strike prep at a monitored biologic manufacturing company).</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Samsung Biologics takes ADC, next-generation CDMO push to 4 global industry events</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Korea Biomedical Review</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33359</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>01-10-2026 04:28 UTC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Monitored company's biologic CDMO strategy and industry event news (Category 5, 8, 10).</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Samsung Biologics Wage Talks Collapse Again, Raising Strike Risk</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/culture/2026/10/01/samsung-biologics-wage-talks-collapse-again-raising-strike</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>01-10-2026 07:59 UTC</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Monitored company's manufacturing/operations news (Category 5, 8).</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1095,7 +1375,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30-09-2026 22:40:25</t>
+          <t>01-10-2026 15:20:40</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology transfer expert insights | BioXcellence</t>
+          <t>Attorney General James Secures $400 Million From Sandoz for Illegal Scheme to Inflate Drug Prices</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>LongIsland.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.boehringer-ingelheim.com/partnering/boehringer-ingelheim-bioxcellence/newsroom/technology-transfer-expert-insights-bioxcellence</t>
+          <t>https://www.longisland.com/articles/10-01-26/attorney-general-james-secures-400-million-from-sandoz-for-illegal-scheme-to-inflate-drug-prices.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30-09-2026 13:50 UTC</t>
+          <t>01-10-2026 17:18 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company news, relevant to biologic manufacturing/CDMO (Category 5, 6, 8).</t>
+          <t>Monitored company commercial event (drug pricing litigation)</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>amgen weight loss drug trial update</t>
+          <t>Numab Therapeutics Appoints Dr. Rajesh Chopra as Chief Scientific Officer to Advance its Proprietary Multispecific Antibody Pipeline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>polskieradio.pl</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.polskieradio.pl/healthy-living/hr/amgen-weight-loss-drug-trial-update</t>
+          <t>https://www.manilatimes.net/2026/10/01/tmt-newswire/globenewswire/numab-therapeutics-appoints-dr-rajesh-chopra-as-chief-scientific-officer-to-advance-its-proprietary-multispecific-antibody-pipeline/2436826/amp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30-09-2026 17:15 UTC</t>
+          <t>01-10-2026 07:37 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company's clinical pipeline news (biologic for weight loss) (Category 7, 8).</t>
+          <t>Clinical trials &amp; pipeline news (multispecific antibody pipeline)</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amgen Readies Daxdilimab For Phase III In Discoid Lupus After Mid-Stage Trial</t>
+          <t>DaltonTx, the decision engine for drug discovery, launches advanced AI-powered antibody discovery platform</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/scrip/r-and-d/clinical-trials/amgen-readies-daxdilimab-for-phase-iii-in-discoid-lupus-after-mid-stage-trial-O7Z3KNGGKVCK5FUZYCMDYG3FNQ/</t>
+          <t>https://www.manilatimes.net/2026/10/01/tmt-newswire/globenewswire/daltontx-the-decision-engine-for-drug-discovery-launches-advanced-ai-powered-antibody-discovery-platform/2436827/amp</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30-09-2026 10:40 UTC</t>
+          <t>01-10-2026 07:37 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company's clinical trial news for an autoimmune biologic (Category 7, 8).</t>
+          <t>Clinical trials &amp; pipeline news (antibody discovery platform)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,7 +587,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -599,27 +599,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amgen's GIP Blocker Mirrors Lilly's Zepbound</t>
+          <t>Imdelltra extends survival in relapsed small cell lung cancer, Korean investigator says</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Briefs Finance</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.briefs.co/news/amgen-s-gip-blocker-might-end-up-doing-what-lilly-s-gip-acti/</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33373</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30-09-2026 19:40 UTC</t>
+          <t>01-10-2026 09:22 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company's clinical pipeline news (biologic for weight loss) (Category 7, 8).</t>
+          <t>Monitored company clinical trials &amp; pipeline news (biologic)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -639,27 +639,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Experimental therapy rapidly lowers disease activity in Sjögren’s trial</t>
+          <t>Amgen's GIP Blocker Mirrors Lilly's Zepbound</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sjogren's Disease News</t>
+          <t>Briefs Finance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://sjogrenssyndromenews.com/news/experimental-therapy-lowers-disease-activity-sjogrens-trial/</t>
+          <t>https://www.briefs.co/news/amgen-s-gip-blocker-might-end-up-doing-what-lilly-s-gip-acti/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30-09-2026 14:32 UTC</t>
+          <t>30-09-2026 19:40 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company's clinical trial news for an autoimmune therapy (Category 7, 8).</t>
+          <t>Monitored company clinical trials &amp; pipeline news (biologic weight loss drug)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,7 +667,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -679,27 +679,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Therapeutic Antibody Market Is Going to Boom |• Roche • AbbVie • Amgen</t>
+          <t>CDA Issues Positive Reimbursement Recommendation for Uplizna in IgG4-RD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>NAVLIN DAILY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4649306/therapeutic-antibody-market-is-going-to-boom-roche</t>
+          <t>https://www.navlindaily.com/article/32020/cda-issues-positive-reimbursement-recommendation-for-uplizna-in-igg4-rd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-10-2026 03:36 UTC</t>
+          <t>30-09-2026 21:06 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company mentioned in therapeutic antibody market news (Category 2, 4, 8).</t>
+          <t>Monitored company market access news (biologic)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sun Pharma Eyes Rs 10,000 Crore Bond Sale to Fund Organon Acquisition Loan</t>
+          <t>Pfizer's Tilrekimig Shows Significant Skin Clearance in Phase 2 Atopic Dermatitis Study</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>medicaldialogues.in</t>
+          <t>businesswire.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/sun-pharma-eyes-rs-10000-crore-bond-sale-to-fund-organon-acquisition-loan-180353</t>
+          <t>https://www.businesswire.com/news/home/20260930032966/en/Pfizers-Tilrekimig-Shows-Significant-Skin-Clearance-in-Phase-2-Atopic-Dermatitis-Study</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30-09-2026 13:24 UTC</t>
+          <t>01-10-2026 06:30 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company acquisition/financing news (Category 6, 8).</t>
+          <t>Monitored company clinical trial results (biologic for immunology disease)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pfizer stops weight loss drug</t>
+          <t>Biogen Taps Olympics Gymnast Suni Lee For Rare Kidney Disease Campaign 09/29/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>polskieradio.pl</t>
+          <t>MediaPost</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.polskieradio.pl/bonusesr/en-FI/crash-bet365-guia</t>
+          <t>https://www.mediapost.com/publications/article/418346/biogen-taps-olympics-gymnast-suni-lee-for-rare-kid.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-10-2026 07:35 UTC</t>
+          <t>30-09-2026 22:38 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored company's clinical pipeline news (Category 7, 8).</t>
+          <t>Monitored company commercial event (rare disease drug)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pfizer’s Phase II Atopic Dermatitis Data Push Tilrekimig Into Pivotal AD, Asthma Trials</t>
+          <t>Shilpa Biologicals unveils new gene to GMP manufacturing platform SB HiMax for biotechs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>BioSpectrum India</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/scrip/r-and-d/clinical-trials/pfizers-phase-ii-atopic-dermatitis-data-push-tilrekimig-into-pivotal-ad-asthma-trials-KDJR2KQ4CZFCBFKLIMLADRSHAA/</t>
+          <t>https://www.biospectrumindia.com/news/16/28580/shilpa-biologicals-unveils-new-gene-to-gmp-manufacturing-platform-sb-himax-for-biotechs-.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-10-2026 06:41 UTC</t>
+          <t>30-09-2026 17:52 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored company's clinical trial news for an immunology biologic (Category 7, 8).</t>
+          <t>Monitored company manufacturing platform launch (biologics development)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma launches ADQUEY™ in US and establishes dedicated dermatology biz</t>
+          <t>Celltrion expands European reach with tender wins for 3 new products</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>biospectrumindia.com</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.biospectrumindia.com/news/16/28581/aurobindo-pharma-launches-adquey-in-us-and-establishes-dedicated-dermatology-biz.html</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33355</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30-09-2026 17:47 UTC</t>
+          <t>01-10-2026 01:10 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitored company market launch and strategic business expansion in dermatology (Category 4, 8).</t>
+          <t>Monitored company biosimilar market expansion (tender wins)</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals launches SB HiMax platform at CPHI Milan</t>
+          <t>FDA Discussion Prompts Voluntary Withdrawal of BLA for I-DXd in ES-SCLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pharmabiz.com</t>
+          <t>cancernetwork.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=190988&amp;sid=2</t>
+          <t>https://www.cancernetwork.com/view/fda-discussion-prompts-voluntary-withdrawal-of-bla-for-i-dxd-in-es-sclc</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-10-2026 05:46 UTC</t>
+          <t>01-10-2026 16:06 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitored company launches biologic manufacturing platform at industry conference (Category 5, 8, 10).</t>
+          <t>Monitored company FDA regulatory action (biologic BLA withdrawal)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -914,32 +914,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsung Bioepis and Teva Expand Strategic Partnership to Advance Up to Six Potential Biosimilar Candidates</t>
+          <t>Vanflyta and Minjuvi Receive Favorable Reimbursement Signals, While Janssen's Carvykti Suffers a Setback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>헬스조선</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20261001835078/en/Samsung-Bioepis-and-Teva-Expand-Strategic-Partnership-to-Advance-Up-to-Six-Potential-Biosimilar-Candidates</t>
+          <t>https://health.chosun.com/english/site/data/html_dir/2026/10/01/2026100101207.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01-10-2026 08:30 UTC</t>
+          <t>01-10-2026 01:27 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monitored companies' biosimilar partnership expansion (Category 2, 6, 8).</t>
+          <t>Market launches &amp; commercial events (biologic reimbursement)</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -947,39 +947,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Celltrion Secures Successive New Biosimilar Contracts in Northern Europe</t>
+          <t>Daiichi Sankyo Advances Dual Antibody-Drug Combo in Tough-to-Treat Breast Cancer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/bec1c7bc-2ee2-4434-bfdf-ff5f4f986775</t>
+          <t>https://www.tipranks.com/news/company-announcements/daiichi-sankyo-advances-dual-antibody-drug-combo-in-tough-to-treat-breast-cancer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>01-10-2026 06:55 UTC</t>
+          <t>01-10-2026 16:55 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monitored company's biosimilar market access/commercial news (Category 2, 4, 8).</t>
+          <t>Monitored company clinical trials &amp; pipeline news (biologic antibody-drug conjugate)</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -994,32 +994,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Is Daiichi Sankyo Company (TSE:4568) Undervalued On Its Ifinatamab Filing Withdrawal?</t>
+          <t>Is Kyowa Kirin (TSE:4151) Cheap As Its Knight Therapeutics Deal Opens Latin America?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Simply Wall Street</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/markets/stocks/articles/daiichi-sankyo-company-tse-4568-060732771.html</t>
+          <t>https://simplywall.st/stocks/jp/pharmaceuticals-biotech/tse-4151/kyowa-kirin-shares/news/is-kyowa-kirin-tse4151-cheap-as-its-knight-therapeutics-deal/amp</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>01-10-2026 06:07 UTC</t>
+          <t>01-10-2026 09:19 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monitored company's biologic regulatory/pipeline news (Category 3, 7, 8).</t>
+          <t>Monitored company partnerships &amp; deals (market expansion)</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1027,39 +1027,39 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kyowa Kirin, Knight agree Latin American distribution deal for mogamulizumab</t>
+          <t>Cellular Origins VP on Fresenius Kabi collaboration</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pharmaceutical Business review -</t>
+          <t>Cleanroom Technology</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-business-review.com/news/kyowa-kirin-knight-latin-american-distribution-mogamulizumab/</t>
+          <t>https://www.cleanroomtechnology.com/cellular-origins-vp-on-fresenius-kabi-collaboration</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30-09-2026 09:49 UTC</t>
+          <t>01-10-2026 14:15 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monitored company's biologic distribution deal (Category 6, 8).</t>
+          <t>Monitored company manufacturing partnership (cell therapy biomanufacturing)</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>fiercepharma.com</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monitored company's manufacturing FDA warning letter (Category 3, 5, 8).</t>
+          <t>Monitored company FDA warning letter (manufacturing)</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monitored company's acquisition of a biosimilar platform (Category 2, 6, 8).</t>
+          <t>Monitored company acquisition (biosimilar company)</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1154,32 +1154,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fuji Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fujifilm to Showcase Manufacturing Innovation and Leadership at CPHI 2026 Amid Three Award Shortlist Nominations</t>
+          <t>Waltz Health And Fresenius Kabi Bring Biosimilars Directly To Payers, Cutting Out Wholesalers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>londoninsider.co.uk</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/fujifilm-to-showcase-manufacturing-innovation-and-leadership-at-cphi-2026-amid-three-award-shortlist-ce785ad3df88f424</t>
+          <t>https://londoninsider.co.uk/waltz-health-and-fresenius-kabi-bring-biosimilars-directly-to-payers-cutting-out-wholesalers/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>01-10-2026 08:18 UTC</t>
+          <t>01-10-2026 15:15 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monitored company's biologic manufacturing news at industry conference (Category 5, 8, 10).</t>
+          <t>Biosimilars market access (payer strategy)</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1194,32 +1194,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Advanz Pharma</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Samsung Bioepis and Teva Expand Strategic Partnership to Advance Up to Six Potential Biosimilar Candidates</t>
+          <t>PolyPid Regains European Commercialization Rights for</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20261001835078/en/Samsung-Bioepis-and-Teva-Expand-Strategic-Partnership-to-Advance-Up-to-Six-Potential-Biosimilar-Candidates</t>
+          <t>https://www.globenewswire.com/news-release/2026/10/01/3372922/0/en/polypid-regains-european-commercialization-rights-for-d-plex-expanding-global-commercialization-opportunities.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>01-10-2026 08:30 UTC</t>
+          <t>01-10-2026 12:56 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monitored companies' biosimilar partnership expansion (Category 2, 6, 8).</t>
+          <t>Monitored company partnership (commercialization agreement termination)</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1227,39 +1227,39 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fuji Pharma</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Teva's Denosumab-Adet (Degevma) Approved as Xgeva Biosimilar</t>
+          <t>Fujifilm to Showcase Manufacturing Innovation and Leadership at CPHI 2026 Amid Three Award Shortlist Nominations</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.biopharminternational.com/view/teva-denosumab-adet-degevma-approved-xgeva-biosimilar</t>
+          <t>https://www.marketscreener.com/news/fujifilm-to-showcase-manufacturing-innovation-and-leadership-at-cphi-2026-amid-three-award-shortlist-ce785ad3df88f424</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30-09-2026 16:39 UTC</t>
+          <t>01-10-2026 08:18 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monitored company's biosimilar FDA approval (Category 2, 3, 8).</t>
+          <t>Monitored company manufacturing innovation at industry conference</t>
         </is>
       </c>
       <c r="G21" t="b">
@@ -1267,39 +1267,39 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Samsung Biologics takes ADC, next-generation CDMO push to 4 global industry events</t>
+          <t>Samsung Bioepis and Teva Expand Strategic Partnership to Advance Up to Six Potential Biosimilar Candidates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33359</t>
+          <t>https://www.biospace.com/press-releases/samsung-bioepis-and-teva-expand-strategic-partnership-to-advance-up-to-six-potential-biosimilar-candidates</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>01-10-2026 04:28 UTC</t>
+          <t>01-10-2026 11:52 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monitored company's biologic CDMO strategy and industry event news (Category 5, 8, 10).</t>
+          <t>Monitored companies biosimilar partnership (licensing and commercialization)</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1307,47 +1307,87 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Eli Lilly Loses Full Fed. Circ. Bid To Nix Teva's $177M IP Win</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Law360</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.law360.com/articles/2532310/eli-lilly-loses-full-fed-circ-bid-to-nix-teva-s-177m-ip-win</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>01-10-2026 03:38 UTC</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Monitored company patent litigation</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Samsung Biologics Wage Talks Collapse Again, Raising Strike Risk</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Seoul Economic Daily</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://en.sedaily.com/culture/2026/10/01/samsung-biologics-wage-talks-collapse-again-raising-strike</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>01-10-2026 07:59 UTC</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Monitored company's manufacturing/operations news (Category 5, 8).</t>
-        </is>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Other</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Samsung Biologics takes ADC, next-generation CDMO push to 4 global industry events</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Korea Biomedical Review</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33359</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>01-10-2026 04:28 UTC</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Monitored company manufacturing (CDMO expansion, ADC)</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1415,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-10-2026 15:20:40</t>
+          <t>01-10-2026 23:09:21</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Attorney General James Secures $400 Million From Sandoz for Illegal Scheme to Inflate Drug Prices</t>
+          <t>SDZ: Biosimilar Ambitions Support The Case, Patent Risks Keep Upside In Check</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LongIsland.com</t>
+          <t>Simply Wall Street</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.longisland.com/articles/10-01-26/attorney-general-james-secures-400-million-from-sandoz-for-illegal-scheme-to-inflate-drug-prices.html</t>
+          <t>https://simplywall.st/community/narratives/ch/pharmaceuticals-biotech/vtx-sdz/sandoz-group-shares/0hy9xma4-future-opportunities-will-be-unlocked-through-expanding-pipeline-and-global-market-reach/updates/15-sandoz-groups-analyst-fair-value-has-been-adjusted-higher-f</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-10-2026 17:18 UTC</t>
+          <t>01-10-2026 18:46 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company commercial event (drug pricing litigation)</t>
+          <t>Monitored company earnings/analyst report with biosimilar strategy mention</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,32 +514,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Numab Therapeutics Appoints Dr. Rajesh Chopra as Chief Scientific Officer to Advance its Proprietary Multispecific Antibody Pipeline</t>
+          <t>Imdelltra extends survival in relapsed small cell lung cancer, Korean investigator says</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/10/01/tmt-newswire/globenewswire/numab-therapeutics-appoints-dr-rajesh-chopra-as-chief-scientific-officer-to-advance-its-proprietary-multispecific-antibody-pipeline/2436826/amp</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33373</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-10-2026 07:37 UTC</t>
+          <t>01-10-2026 09:22 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news (multispecific antibody pipeline)</t>
+          <t>Monitored company clinical news for a biologic product</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -547,39 +547,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DaltonTx, the decision engine for drug discovery, launches advanced AI-powered antibody discovery platform</t>
+          <t>Pfizer details Phase II data for Dupixent challenger in atopic dermatitis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/10/01/tmt-newswire/globenewswire/daltontx-the-decision-engine-for-drug-discovery-launches-advanced-ai-powered-antibody-discovery-platform/2436827/amp</t>
+          <t>https://firstwordpharma.com/story/8148039</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-10-2026 07:37 UTC</t>
+          <t>01-10-2026 19:32 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clinical trials &amp; pipeline news (antibody discovery platform)</t>
+          <t>Monitored company clinical data for an immunology/dermatology biologic</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Imdelltra extends survival in relapsed small cell lung cancer, Korean investigator says</t>
+          <t>AstraZeneca and Daiichi Sankyo announce clinical collaboration with Summit Therapeutics to evaluate Datroway in combination with ivonescimab across multiple tumour types</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>astrazeneca.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33373</t>
+          <t>https://www.astrazeneca.com/media-centre/press-releases/2026/az-ds-collaboration-with-summit-for-datroway.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-10-2026 09:22 UTC</t>
+          <t>02-10-2026 06:30 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company clinical trials &amp; pipeline news (biologic)</t>
+          <t>Monitored company clinical collaboration for biologic oncology product</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amgen's GIP Blocker Mirrors Lilly's Zepbound</t>
+          <t>Italfarmaco and JCR Pharmaceuticals Enter into Exclusive License Agreement for the Development and Potential Commercialization of Novel Investigational Therapy for Hunter Syndrome in the United States, Europe, and Latin America</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Briefs Finance</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.briefs.co/news/amgen-s-gip-blocker-might-end-up-doing-what-lilly-s-gip-acti/</t>
+          <t>https://finance.yahoo.com/healthcare/articles/italfarmaco-jcr-pharmaceuticals-enter-exclusive-063000528.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30-09-2026 19:40 UTC</t>
+          <t>02-10-2026 06:30 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company clinical trials &amp; pipeline news (biologic weight loss drug)</t>
+          <t>Monitored company licensing deal for a novel investigational therapy (likely biologic) for a rare disease</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CDA Issues Positive Reimbursement Recommendation for Uplizna in IgG4-RD</t>
+          <t>FDA Warns Fresenius Kabi Over Sterile Injectable Contamination</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NAVLIN DAILY</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.navlindaily.com/article/32020/cda-issues-positive-reimbursement-recommendation-for-uplizna-in-igg4-rd</t>
+          <t>https://www.biopharminternational.com/view/fda-warns-fresenius-kabi-sterile-injectable-contamination</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30-09-2026 21:06 UTC</t>
+          <t>01-10-2026 16:24 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitored company market access news (biologic)</t>
+          <t>Biologic manufacturing FDA warning letter for sterile injectables</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pfizer's Tilrekimig Shows Significant Skin Clearance in Phase 2 Atopic Dermatitis Study</t>
+          <t>Fresenius Acquires Remaining 45% Of mAbxience For Up To €750 Million</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>businesswire.com</t>
+          <t>Pulse 2.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260930032966/en/Pfizers-Tilrekimig-Shows-Significant-Skin-Clearance-in-Phase-2-Atopic-Dermatitis-Study</t>
+          <t>https://pulse2.com/fresenius-acquires-remaining-45-of-mabxience-for-up-to-e750-million/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-10-2026 06:30 UTC</t>
+          <t>01-10-2026 19:34 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company clinical trial results (biologic for immunology disease)</t>
+          <t>Monitored company acquisition of a biosimilar company</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Biogen Taps Olympics Gymnast Suni Lee For Rare Kidney Disease Campaign 09/29/2026</t>
+          <t>Waltz Health And Fresenius Kabi Bring Biosimilars Directly To Payers, Cutting Out Wholesalers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MediaPost</t>
+          <t>londoninsider.co.uk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.mediapost.com/publications/article/418346/biogen-taps-olympics-gymnast-suni-lee-for-rare-kid.html</t>
+          <t>https://londoninsider.co.uk/waltz-health-and-fresenius-kabi-bring-biosimilars-directly-to-payers-cutting-out-wholesalers/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30-09-2026 22:38 UTC</t>
+          <t>01-10-2026 15:15 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored company commercial event (rare disease drug)</t>
+          <t>Monitored company market access strategy for biosimilars</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -794,32 +794,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals unveils new gene to GMP manufacturing platform SB HiMax for biotechs</t>
+          <t>Samsung Bioepis and Teva Expand Strategic Partnership to Advance Up to Six Potential Biosimilar Candidates</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BioSpectrum India</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.biospectrumindia.com/news/16/28580/shilpa-biologicals-unveils-new-gene-to-gmp-manufacturing-platform-sb-himax-for-biotechs-.html</t>
+          <t>https://www.biospace.com/press-releases/samsung-bioepis-and-teva-expand-strategic-partnership-to-advance-up-to-six-potential-biosimilar-candidates</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30-09-2026 17:52 UTC</t>
+          <t>01-10-2026 11:52 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored company manufacturing platform launch (biologics development)</t>
+          <t>Monitored companies expand biosimilar partnership for pipeline candidates</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Celltrion expands European reach with tender wins for 3 new products</t>
+          <t>Teva's Degevma Wins FDA Approval, Joining a Crowded Field of Xgeva Biosimilars for Cancer That Reaches Bone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Medical Daily</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33355</t>
+          <t>https://www.medicaldaily.com/teva-degevma-xgeva-biosimilar-fda-approval-479373</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-10-2026 01:10 UTC</t>
+          <t>02-10-2026 00:10 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitored company biosimilar market expansion (tender wins)</t>
+          <t>FDA approval of biosimilar from a monitored company</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,39 +867,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FDA Discussion Prompts Voluntary Withdrawal of BLA for I-DXd in ES-SCLC</t>
+          <t>Samsung Biologics Union Announces 3-Week General Strike from Oct. 26; Management Says Demands "Unacceptable"</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cancernetwork.com</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.cancernetwork.com/view/fda-discussion-prompts-voluntary-withdrawal-of-bla-for-i-dxd-in-es-sclc</t>
+          <t>https://finance.biggo.com/news/19f2c552-d400-4fe8-be9c-eaaec9ce4666</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-10-2026 16:06 UTC</t>
+          <t>02-10-2026 06:55 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitored company FDA regulatory action (biologic BLA withdrawal)</t>
+          <t>Monitored company manufacturing/supply chain event (union strike)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -908,486 +908,6 @@
       <c r="H12" t="inlineStr">
         <is>
           <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Vanflyta and Minjuvi Receive Favorable Reimbursement Signals, While Janssen's Carvykti Suffers a Setback</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>헬스조선</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://health.chosun.com/english/site/data/html_dir/2026/10/01/2026100101207.html</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>01-10-2026 01:27 UTC</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Market launches &amp; commercial events (biologic reimbursement)</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo Advances Dual Antibody-Drug Combo in Tough-to-Treat Breast Cancer</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.tipranks.com/news/company-announcements/daiichi-sankyo-advances-dual-antibody-drug-combo-in-tough-to-treat-breast-cancer</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>01-10-2026 16:55 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Monitored company clinical trials &amp; pipeline news (biologic antibody-drug conjugate)</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Is Kyowa Kirin (TSE:4151) Cheap As Its Knight Therapeutics Deal Opens Latin America?</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://simplywall.st/stocks/jp/pharmaceuticals-biotech/tse-4151/kyowa-kirin-shares/news/is-kyowa-kirin-tse4151-cheap-as-its-knight-therapeutics-deal/amp</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>01-10-2026 09:19 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Monitored company partnerships &amp; deals (market expansion)</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cellular Origins VP on Fresenius Kabi collaboration</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cleanroom Technology</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.cleanroomtechnology.com/cellular-origins-vp-on-fresenius-kabi-collaboration</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>01-10-2026 14:15 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Monitored company manufacturing partnership (cell therapy biomanufacturing)</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>FDA hits 2nd Fresenius site with contamination-related warning letter in less than a month</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Fierce Pharma</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.fiercepharma.com/ai-and-machine-learning/second-fresenius-site-hit-fda-warning-letter-citing-contamination-concerns</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>30-09-2026 19:55 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Monitored company FDA warning letter (manufacturing)</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Fresenius completes acquisition of mAbxience, creating a stronger platform for future portfolio expansion</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BioSpace</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.biospace.com/press-releases/fresenius-completes-acquisition-of-mabxience-creating-a-stronger-platform-for-future-portfolio-expansion</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>01-10-2026 06:08 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Monitored company acquisition (biosimilar company)</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Waltz Health And Fresenius Kabi Bring Biosimilars Directly To Payers, Cutting Out Wholesalers</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>londoninsider.co.uk</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://londoninsider.co.uk/waltz-health-and-fresenius-kabi-bring-biosimilars-directly-to-payers-cutting-out-wholesalers/</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>01-10-2026 15:15 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Biosimilars market access (payer strategy)</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Advanz Pharma</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PolyPid Regains European Commercialization Rights for</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.globenewswire.com/news-release/2026/10/01/3372922/0/en/polypid-regains-european-commercialization-rights-for-d-plex-expanding-global-commercialization-opportunities.html</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>01-10-2026 12:56 UTC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Monitored company partnership (commercialization agreement termination)</t>
-        </is>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fuji Pharma</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fujifilm to Showcase Manufacturing Innovation and Leadership at CPHI 2026 Amid Three Award Shortlist Nominations</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/news/fujifilm-to-showcase-manufacturing-innovation-and-leadership-at-cphi-2026-amid-three-award-shortlist-ce785ad3df88f424</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>01-10-2026 08:18 UTC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Monitored company manufacturing innovation at industry conference</t>
-        </is>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis and Teva Expand Strategic Partnership to Advance Up to Six Potential Biosimilar Candidates</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BioSpace</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://www.biospace.com/press-releases/samsung-bioepis-and-teva-expand-strategic-partnership-to-advance-up-to-six-potential-biosimilar-candidates</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>01-10-2026 11:52 UTC</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Monitored companies biosimilar partnership (licensing and commercialization)</t>
-        </is>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Eli Lilly Loses Full Fed. Circ. Bid To Nix Teva's $177M IP Win</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Law360</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.law360.com/articles/2532310/eli-lilly-loses-full-fed-circ-bid-to-nix-teva-s-177m-ip-win</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>01-10-2026 03:38 UTC</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Monitored company patent litigation</t>
-        </is>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Samsung Biologics takes ADC, next-generation CDMO push to 4 global industry events</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Korea Biomedical Review</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33359</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>01-10-2026 04:28 UTC</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Monitored company manufacturing (CDMO expansion, ADC)</t>
-        </is>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -1415,7 +935,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-10-2026 23:09:21</t>
+          <t>02-10-2026 14:54:00</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SDZ: Biosimilar Ambitions Support The Case, Patent Risks Keep Upside In Check</t>
+          <t>Formycon and the Patent Cliff: Why Expiring Patents at Novartis and Merck Present an Opportunity for the German Biotech Industry</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Simply Wall Street</t>
+          <t>Stockhouse</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://simplywall.st/community/narratives/ch/pharmaceuticals-biotech/vtx-sdz/sandoz-group-shares/0hy9xma4-future-opportunities-will-be-unlocked-through-expanding-pipeline-and-global-market-reach/updates/15-sandoz-groups-analyst-fair-value-has-been-adjusted-higher-f</t>
+          <t>https://stockhouse.com/opinion/contributors/2026/10/02/formycon-and-patent-cliff-why-expiring-patents-novartis-and-merck-present-an</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-10-2026 18:46 UTC</t>
+          <t>02-10-2026 07:55 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitored company earnings/analyst report with biosimilar strategy mention</t>
+          <t>monitored company (Formycon), biosimilars &amp; biologics patent events</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Imdelltra extends survival in relapsed small cell lung cancer, Korean investigator says</t>
+          <t>More Than Skin Deep: Understanding Discoid Lupus Erythematosus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33373</t>
+          <t>https://www.amgen.com/stories/2026/10/more-than-skin-deep-understanding-discoid-lupus-erythematosus</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-10-2026 09:22 UTC</t>
+          <t>01-10-2026 17:43 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitored company clinical news for a biologic product</t>
+          <t>monitored company (Amgen), immunology disease awareness</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pfizer details Phase II data for Dupixent challenger in atopic dermatitis</t>
+          <t>Teva gains FDA nod for Xgeva biosimilar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>drugstorenews.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/8148039</t>
+          <t>https://drugstorenews.com/teva-gains-fda-nod-xgeva-biosimilar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-10-2026 19:32 UTC</t>
+          <t>02-10-2026 12:54 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitored company clinical data for an immunology/dermatology biologic</t>
+          <t>biosimilar FDA approval (Xgeva biosimilar), monitored company</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -587,39 +587,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AstraZeneca and Daiichi Sankyo announce clinical collaboration with Summit Therapeutics to evaluate Datroway in combination with ivonescimab across multiple tumour types</t>
+          <t>Pfizer touts 'dermatology momentum' as it paints fuller picture of Litfulo's vitiligo potential</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>astrazeneca.com</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.astrazeneca.com/media-centre/press-releases/2026/az-ds-collaboration-with-summit-for-datroway.html</t>
+          <t>https://www.fiercepharma.com/pharma/pfizer-funnels-dermatology-momentum-immunology-expansion</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02-10-2026 06:30 UTC</t>
+          <t>02-10-2026 15:15 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitored company clinical collaboration for biologic oncology product</t>
+          <t>monitored company (Pfizer), immunology clinical/pipeline news</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Italfarmaco and JCR Pharmaceuticals Enter into Exclusive License Agreement for the Development and Potential Commercialization of Novel Investigational Therapy for Hunter Syndrome in the United States, Europe, and Latin America</t>
+          <t>Pfizer’s LITFULO Significantly Improved Facial and Total Body Repigmentation in Patients with Nonsegmental Vitiligo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/italfarmaco-jcr-pharmaceuticals-enter-exclusive-063000528.html</t>
+          <t>https://www.businesswire.com/news/home/20261002026421/en/Pfizers-LITFULO-Significantly-Improved-Facial-and-Total-Body-Repigmentation-in-Patients-with-Nonsegmental-Vitiligo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-10-2026 06:30 UTC</t>
+          <t>02-10-2026 15:15 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitored company licensing deal for a novel investigational therapy (likely biologic) for a rare disease</t>
+          <t>monitored company (Pfizer), immunology clinical/pipeline news (Vitiligo)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FDA Warns Fresenius Kabi Over Sterile Injectable Contamination</t>
+          <t>Pfizer’s Trispecific Antibody Shows Significant Skin Clearance in Phase 2 AD Trial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>The Dermatology Digest</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.biopharminternational.com/view/fda-warns-fresenius-kabi-sterile-injectable-contamination</t>
+          <t>https://thedermdigest.com/pfizers-trispecific-antibody-shows-significant-skin-clearance-in-phase-2-ad-trial/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-10-2026 16:24 UTC</t>
+          <t>02-10-2026 16:24 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biologic manufacturing FDA warning letter for sterile injectables</t>
+          <t>monitored company (Pfizer), biologics clinical trial (trispecific antibody), immunology (Atopic Dermatitis)</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fresenius Acquires Remaining 45% Of mAbxience For Up To €750 Million</t>
+          <t>Biogen's experimental lupus drug shows benefit against skin symptoms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pulse 2.0</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pulse2.com/fresenius-acquires-remaining-45-of-mabxience-for-up-to-e750-million/</t>
+          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/biogens-experimental-lupus-drug-shows-benefit-against-skin-symptoms-2026-10-02/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-10-2026 19:34 UTC</t>
+          <t>02-10-2026 16:42 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitored company acquisition of a biosimilar company</t>
+          <t>monitored company (Biogen), immunology clinical/pipeline news (Lupus)</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Waltz Health And Fresenius Kabi Bring Biosimilars Directly To Payers, Cutting Out Wholesalers</t>
+          <t>Biogen’s Litifilimab Demonstrates Rapid and Durable Efficacy in New 52-Week Phase 2 Data from Ongoing Phase 2/3 AMETHYST Study, Reinforcing Its Potential as a First-in-Class Therapy for Cutaneous Lupus Erythematosus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>londoninsider.co.uk</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://londoninsider.co.uk/waltz-health-and-fresenius-kabi-bring-biosimilars-directly-to-payers-cutting-out-wholesalers/</t>
+          <t>https://www.globenewswire.com/news-release/2026/10/02/3373899/0/en/biogen-s-litifilimab-demonstrates-rapid-and-durable-efficacy-in-new-52-week-phase-2-data-from-ongoing-phase-2-3-amethyst-study-reinforcing-its-potential-as-a-first-in-class-therapy.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-10-2026 15:15 UTC</t>
+          <t>02-10-2026 15:20 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitored company market access strategy for biosimilars</t>
+          <t>monitored company (Biogen), immunology clinical/pipeline news (Lupus)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samsung Bioepis and Teva Expand Strategic Partnership to Advance Up to Six Potential Biosimilar Candidates</t>
+          <t>Shilpa Biologicals launches gene-to-GMP platform for faster biologics development</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>manufacturingchemist.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/samsung-bioepis-and-teva-expand-strategic-partnership-to-advance-up-to-six-potential-biosimilar-candidates</t>
+          <t>https://manufacturingchemist.com/shilpa-biologicals-gene-gmp-platform-biologics-sb-himax</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-10-2026 11:52 UTC</t>
+          <t>02-10-2026 10:02 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitored companies expand biosimilar partnership for pipeline candidates</t>
+          <t>monitored company (Shilpa Biologicals), biologics manufacturing/development capacity</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Teva's Degevma Wins FDA Approval, Joining a Crowded Field of Xgeva Biosimilars for Cancer That Reaches Bone</t>
+          <t>Teva, Samsung Bioepis deepen bonds in pact for up to 6 new biosimilars</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medical Daily</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.medicaldaily.com/teva-degevma-xgeva-biosimilar-fda-approval-479373</t>
+          <t>https://www.fiercepharma.com/pharma/teva-samsung-bioepis-deepen-bonds-pact-6-new-biosimilars</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-10-2026 00:10 UTC</t>
+          <t>02-10-2026 14:00 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FDA approval of biosimilar from a monitored company</t>
+          <t>monitored companies (Teva, Samsung Bioepis), biosimilars partnership/deal</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -867,45 +867,325 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AstraZeneca and Daiichi Sankyo announce clinical collaboration with Summit Therapeutics to evaluate Datroway in combination with ivonescimab across multiple tumour types</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>astrazeneca.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.astrazeneca.com/media-centre/press-releases/2026/az-ds-collaboration-with-summit-for-datroway.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02-10-2026 06:30 UTC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>monitored company (Daiichi Sankyo), biologics clinical trial (ADC), partnership</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JCR Pharma</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Italfarmaco and JCR Pharmaceuticals Enter into Exclusive License Agreement for the Development and Potential Commercialization of Novel Investigational Therapy for Hunter Syndrome in the United States, Europe, and Latin America</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/italfarmaco-jcr-pharmaceuticals-enter-exclusive-063000528.html</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>02-10-2026 06:30 UTC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>monitored company (JCR Pharma), biologics licensing deal (for rare disease ERP)</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FDA upbraids Fresenius Kabi over injectable drugs contamination</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ICLG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://iclg.com/news/fda-upbraids-fresenius-kabi-over-injectable-drugs-contamination/</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02-10-2026 10:22 UTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>monitored company (Fresenius Kabi), FDA manufacturing/quality issues (injectable drugs)</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fresenius Acquires Remaining 45% Of mAbxience For Up To €750 Million</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pulse 2.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://pulse2.com/fresenius-acquires-remaining-45-of-mabxience-for-up-to-e750-million/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:34 UTC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>monitored company (Fresenius Kabi), biologics company acquisition (mAbxience)</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CaseBioscience® Joins Team Awarded Up to $7.3 Million by ARPA-H to Advance Ambient Preservation of Cell Therapies</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BioSpace</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/casebioscience-joins-team-awarded-up-to-7-3-million-by-arpa-h-to-advance-ambient-preservation-of-cell-therapies</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02-10-2026 04:41 UTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>monitored company (Fresenius Kabi), advanced therapies/biologics development (cell therapies grant)</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lipid Emulsions Market Forecast to 2035: Bioprocessing Demand Drives 6-8% CAGR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/lipid-emulsions-market-forecast-to-2035-bioprocessing-demand-drives-6-8-cagr/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02-10-2026 04:31 UTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>manufacturing/supply chain (bioprocessing demand forecast)</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Samsung Biologics Union Announces 3-Week General Strike from Oct. 26; Management Says Demands "Unacceptable"</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>finance.biggo.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://finance.biggo.com/news/19f2c552-d400-4fe8-be9c-eaaec9ce4666</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>02-10-2026 06:55 UTC</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Monitored company manufacturing/supply chain event (union strike)</t>
-        </is>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Samsung Biologics Union Plans General Strike</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>businesskorea.co.kr</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=278182</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>02-10-2026 10:45 UTC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>monitored company (Samsung Biologics), manufacturing supply chain impact (union strike)</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Samsung Biologics, Lotte Biologics head to Bio Japan to expand K-biotech contracts</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>헤럴드경제</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://mbiz.heraldcorp.com/article/10891318</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>02-10-2026 00:11 UTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>monitored company (Samsung Biologics), manufacturing deals/partnerships, industry meeting</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -935,7 +1215,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02-10-2026 14:54:00</t>
+          <t>02-10-2026 22:28:48</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,32 +474,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Formycon and the Patent Cliff: Why Expiring Patents at Novartis and Merck Present an Opportunity for the German Biotech Industry</t>
+          <t>Sandoz reorganises ahead of 'golden decade' for biosimilars</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stockhouse</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://stockhouse.com/opinion/contributors/2026/10/02/formycon-and-patent-cliff-why-expiring-patents-novartis-and-merck-present-an</t>
+          <t>https://firstwordpharma.com/story/7131922</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02-10-2026 07:55 UTC</t>
+          <t>03-10-2026 02:10 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>monitored company (Formycon), biosimilars &amp; biologics patent events</t>
+          <t>monitored company Sandoz biosimilars strategy</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>More Than Skin Deep: Understanding Discoid Lupus Erythematosus</t>
+          <t>Teva gains FDA nod for Xgeva biosimilar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Drug Store News</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.amgen.com/stories/2026/10/more-than-skin-deep-understanding-discoid-lupus-erythematosus</t>
+          <t>https://drugstorenews.com/teva-gains-fda-nod-xgeva-biosimilar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-10-2026 17:43 UTC</t>
+          <t>02-10-2026 12:54 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>monitored company (Amgen), immunology disease awareness</t>
+          <t>biosimilar FDA approval for monitored company Teva, Amgen originator</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -559,27 +559,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Teva gains FDA nod for Xgeva biosimilar</t>
+          <t>Amgen’s Evolocumab Study Signals Quiet Efficiency Gains for Cholesterol Franchise</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>drugstorenews.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://drugstorenews.com/teva-gains-fda-nod-xgeva-biosimilar</t>
+          <t>https://www.tipranks.com/news/company-announcements/amgens-evolocumab-study-signals-quiet-efficiency-gains-for-cholesterol-franchise</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-10-2026 12:54 UTC</t>
+          <t>02-10-2026 16:42 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>biosimilar FDA approval (Xgeva biosimilar), monitored company</t>
+          <t>monitored company Amgen biologic clinical news</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -619,7 +619,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>monitored company (Pfizer), immunology clinical/pipeline news</t>
+          <t>monitored company's advanced therapy in autoimmune/immunology market</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -634,32 +634,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pfizer’s LITFULO Significantly Improved Facial and Total Body Repigmentation in Patients with Nonsegmental Vitiligo</t>
+          <t>Biogen’s Litifilimab Demonstrates Rapid and Durable Efficacy in New 52-Week Phase 2 Data from Ongoing Phase 2/3 AMETHYST Study, Reinforcing Its Potential as a First-in-Class Therapy for Cutaneous Lupus Erythematosus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20261002026421/en/Pfizers-LITFULO-Significantly-Improved-Facial-and-Total-Body-Repigmentation-in-Patients-with-Nonsegmental-Vitiligo</t>
+          <t>https://investors.biogen.com/news-releases/news-release-details/biogens-litifilimab-demonstrates-rapid-and-durable-efficacy-new</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-10-2026 15:15 UTC</t>
+          <t>02-10-2026 15:20 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>monitored company (Pfizer), immunology clinical/pipeline news (Vitiligo)</t>
+          <t>monitored company's biologic clinical news for autoimmune disease</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pfizer’s Trispecific Antibody Shows Significant Skin Clearance in Phase 2 AD Trial</t>
+          <t>US FDA extends review of Novo Nordisk's hemophilia drug over facility issues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Dermatology Digest</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://thedermdigest.com/pfizers-trispecific-antibody-shows-significant-skin-clearance-in-phase-2-ad-trial/</t>
+          <t>https://sg.finance.yahoo.com/news/us-fda-extends-review-novo-215156085.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-10-2026 16:24 UTC</t>
+          <t>02-10-2026 21:51 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>monitored company (Pfizer), biologics clinical trial (trispecific antibody), immunology (Atopic Dermatitis)</t>
+          <t>FDA/manufacturing news for a biologic product</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -707,39 +707,39 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Biogen's experimental lupus drug shows benefit against skin symptoms</t>
+          <t>Aurobindo Pharma Completes Acquisition Of A1 Biochem Labs LLC For $15.247 Million</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/biogens-experimental-lupus-drug-shows-benefit-against-skin-symptoms-2026-10-02/</t>
+          <t>https://www.sahi.com/news/aurobindo-pharma-completes-acquisition-of-a1-biochem-labs-llc-for-15-247-million</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-10-2026 16:42 UTC</t>
+          <t>02-10-2026 13:53 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>monitored company (Biogen), immunology clinical/pipeline news (Lupus)</t>
+          <t>monitored company acquisition in bioconjugates/biologics related services</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Biogen’s Litifilimab Demonstrates Rapid and Durable Efficacy in New 52-Week Phase 2 Data from Ongoing Phase 2/3 AMETHYST Study, Reinforcing Its Potential as a First-in-Class Therapy for Cutaneous Lupus Erythematosus</t>
+          <t>Shilpa Biologicals launches gene-to-GMP platform for faster biologics development</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/10/02/3373899/0/en/biogen-s-litifilimab-demonstrates-rapid-and-durable-efficacy-in-new-52-week-phase-2-data-from-ongoing-phase-2-3-amethyst-study-reinforcing-its-potential-as-a-first-in-class-therapy.html</t>
+          <t>https://manufacturingchemist.com/shilpa-biologicals-gene-gmp-platform-biologics-sb-himax</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-10-2026 15:20 UTC</t>
+          <t>02-10-2026 10:02 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>monitored company (Biogen), immunology clinical/pipeline news (Lupus)</t>
+          <t>monitored company's biologic manufacturing/development platform news</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,39 +787,39 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals launches gene-to-GMP platform for faster biologics development</t>
+          <t>AstraZeneca, Daiichi Sankyo, and Summit to Combine Datroway, Ivonescimab</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manufacturingchemist.com</t>
+          <t>biopharminternational.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://manufacturingchemist.com/shilpa-biologicals-gene-gmp-platform-biologics-sb-himax</t>
+          <t>https://www.biopharminternational.com/view/astrazeneca-daiichi-sankyo-summit-combine-datroway-ivonescimab</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-10-2026 10:02 UTC</t>
+          <t>02-10-2026 16:23 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>monitored company (Shilpa Biologicals), biologics manufacturing/development capacity</t>
+          <t>monitored company biologic clinical collaboration</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -827,39 +827,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Teva, Samsung Bioepis deepen bonds in pact for up to 6 new biosimilars</t>
+          <t>FDA upbraids Fresenius Kabi over injectable drugs contamination</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>ICLG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/teva-samsung-bioepis-deepen-bonds-pact-6-new-biosimilars</t>
+          <t>https://iclg.com/news/fda-upbraids-fresenius-kabi-over-injectable-drugs-contamination/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-10-2026 14:00 UTC</t>
+          <t>02-10-2026 10:22 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>monitored companies (Teva, Samsung Bioepis), biosimilars partnership/deal</t>
+          <t>FDA/manufacturing warning for monitored company's injectable drugs</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -874,32 +874,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AstraZeneca and Daiichi Sankyo announce clinical collaboration with Summit Therapeutics to evaluate Datroway in combination with ivonescimab across multiple tumour types</t>
+          <t>Teva, Samsung Bioepis deepen bonds in pact for up to 6 new biosimilars</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>astrazeneca.com</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.astrazeneca.com/media-centre/press-releases/2026/az-ds-collaboration-with-summit-for-datroway.html</t>
+          <t>https://www.fiercepharma.com/pharma/teva-samsung-bioepis-deepen-bonds-pact-6-new-biosimilars</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02-10-2026 06:30 UTC</t>
+          <t>02-10-2026 14:00 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>monitored company (Daiichi Sankyo), biologics clinical trial (ADC), partnership</t>
+          <t>monitored companies biosimilar collaboration deal</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -907,285 +907,45 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Italfarmaco and JCR Pharmaceuticals Enter into Exclusive License Agreement for the Development and Potential Commercialization of Novel Investigational Therapy for Hunter Syndrome in the United States, Europe, and Latin America</t>
+          <t>Samsung Biologics Union Plans General Strike</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/italfarmaco-jcr-pharmaceuticals-enter-exclusive-063000528.html</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=278182</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>02-10-2026 06:30 UTC</t>
+          <t>02-10-2026 10:45 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>monitored company (JCR Pharma), biologics licensing deal (for rare disease ERP)</t>
+          <t>monitored company manufacturing/supply chain event</t>
         </is>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FDA upbraids Fresenius Kabi over injectable drugs contamination</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ICLG</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://iclg.com/news/fda-upbraids-fresenius-kabi-over-injectable-drugs-contamination/</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>02-10-2026 10:22 UTC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>monitored company (Fresenius Kabi), FDA manufacturing/quality issues (injectable drugs)</t>
-        </is>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Fresenius Acquires Remaining 45% Of mAbxience For Up To €750 Million</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Pulse 2.0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://pulse2.com/fresenius-acquires-remaining-45-of-mabxience-for-up-to-e750-million/</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>01-10-2026 19:34 UTC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>monitored company (Fresenius Kabi), biologics company acquisition (mAbxience)</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CaseBioscience® Joins Team Awarded Up to $7.3 Million by ARPA-H to Advance Ambient Preservation of Cell Therapies</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BioSpace</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.biospace.com/press-releases/casebioscience-joins-team-awarded-up-to-7-3-million-by-arpa-h-to-advance-ambient-preservation-of-cell-therapies</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>02-10-2026 04:41 UTC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>monitored company (Fresenius Kabi), advanced therapies/biologics development (cell therapies grant)</t>
-        </is>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Lipid Emulsions Market Forecast to 2035: Bioprocessing Demand Drives 6-8% CAGR</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>IndexBox</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/lipid-emulsions-market-forecast-to-2035-bioprocessing-demand-drives-6-8-cagr/</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>02-10-2026 04:31 UTC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>manufacturing/supply chain (bioprocessing demand forecast)</t>
-        </is>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Samsung Biologics Union Plans General Strike</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>businesskorea.co.kr</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=278182</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>02-10-2026 10:45 UTC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>monitored company (Samsung Biologics), manufacturing supply chain impact (union strike)</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Samsung Biologics, Lotte Biologics head to Bio Japan to expand K-biotech contracts</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10891318</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>02-10-2026 00:11 UTC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>monitored company (Samsung Biologics), manufacturing deals/partnerships, industry meeting</t>
-        </is>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1215,7 +975,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02-10-2026 22:28:48</t>
+          <t>03-10-2026 14:27:33</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -479,27 +479,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz reorganises ahead of 'golden decade' for biosimilars</t>
+          <t>Sandoz creates new global biosimilar development, manufacturing and supply unit, appoints industry veteran Armin Metzger to lead next phase of growth</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7131922</t>
+          <t>https://www.sandoz.com/sandoz-creates-new-global-biosimilar-development-manufacturing-and-supply-unit-appoints-industry/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>03-10-2026 02:10 UTC</t>
+          <t>03-10-2026 10:53 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>monitored company Sandoz biosimilars strategy</t>
+          <t>Monitored company Sandoz creates new global biosimilar development, manufacturing and supply unit</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Teva gains FDA nod for Xgeva biosimilar</t>
+          <t>Amgen’s Evolocumab Study Signals Quiet Efficiency Gains for Cholesterol Franchise</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Drug Store News</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://drugstorenews.com/teva-gains-fda-nod-xgeva-biosimilar</t>
+          <t>https://www.tipranks.com/news/company-announcements/amgens-evolocumab-study-signals-quiet-efficiency-gains-for-cholesterol-franchise</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02-10-2026 12:54 UTC</t>
+          <t>02-10-2026 16:42 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>biosimilar FDA approval for monitored company Teva, Amgen originator</t>
+          <t>Amgen biologic (Evolocumab) clinical study</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -554,32 +554,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amgen’s Evolocumab Study Signals Quiet Efficiency Gains for Cholesterol Franchise</t>
+          <t>Pfizer’s LITFULO Significantly Improved Facial and Total Body Repigmentation in Patients with Nonsegmental Vitiligo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/amgens-evolocumab-study-signals-quiet-efficiency-gains-for-cholesterol-franchise</t>
+          <t>https://www.businesswire.com/news/home/20261002026421/en/Pfizers-LITFULO-Significantly-Improved-Facial-and-Total-Body-Repigmentation-in-Patients-with-Nonsegmental-Vitiligo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-10-2026 16:42 UTC</t>
+          <t>02-10-2026 15:15 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>monitored company Amgen biologic clinical news</t>
+          <t>Pfizer clinical data for Litfulo in autoimmune disease (vitiligo)</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -594,32 +594,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pfizer touts 'dermatology momentum' as it paints fuller picture of Litfulo's vitiligo potential</t>
+          <t>Biogen’s Litifilimab Demonstrates Rapid and Durable Efficacy in New 52-Week Phase 2 Data from Ongoing Phase 2/3 AMETHYST Study, Reinforcing Its Potential as a First-in-Class Therapy for Cutaneous Lupus Erythematosus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/pfizer-funnels-dermatology-momentum-immunology-expansion</t>
+          <t>https://investors.biogen.com/news-releases/news-release-details/biogens-litifilimab-demonstrates-rapid-and-durable-efficacy-new</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02-10-2026 15:15 UTC</t>
+          <t>02-10-2026 15:20 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>monitored company's advanced therapy in autoimmune/immunology market</t>
+          <t>Biogen clinical data for biologic (Litifilimab) in autoimmune disease (lupus)</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -627,39 +627,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Biogen’s Litifilimab Demonstrates Rapid and Durable Efficacy in New 52-Week Phase 2 Data from Ongoing Phase 2/3 AMETHYST Study, Reinforcing Its Potential as a First-in-Class Therapy for Cutaneous Lupus Erythematosus</t>
+          <t>HIPRA Biotech Services Expands Integrated Biologics Capabilities</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://investors.biogen.com/news-releases/news-release-details/biogens-litifilimab-demonstrates-rapid-and-durable-efficacy-new</t>
+          <t>https://www.contractpharma.com/live_from_shows/hipra-biotech-services-expands-integrated-biologics-capabilities/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-10-2026 15:20 UTC</t>
+          <t>03-10-2026 03:22 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>monitored company's biologic clinical news for autoimmune disease</t>
+          <t>Biologic manufacturing capacity expansion</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -667,39 +667,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>US FDA extends review of Novo Nordisk's hemophilia drug over facility issues</t>
+          <t>Insights from GRAM at CPHI Milan 2026: Navigating the Future of Sterile Manufacturing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/us-fda-extends-review-novo-215156085.html</t>
+          <t>https://www.contractpharma.com/live_from_shows/insights-from-gram-at-cphi-milan-2026-navigating-the-future-of-sterile-manufacturing/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-10-2026 21:51 UTC</t>
+          <t>03-10-2026 03:22 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FDA/manufacturing news for a biologic product</t>
+          <t>Sterile manufacturing for biologics, industry meeting</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -714,32 +714,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Completes Acquisition Of A1 Biochem Labs LLC For $15.247 Million</t>
+          <t>AstraZeneca, Daiichi Sankyo, and Summit to Combine Datroway, Ivonescimab</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/aurobindo-pharma-completes-acquisition-of-a1-biochem-labs-llc-for-15-247-million</t>
+          <t>https://www.biopharminternational.com/view/astrazeneca-daiichi-sankyo-summit-combine-datroway-ivonescimab</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-10-2026 13:53 UTC</t>
+          <t>02-10-2026 16:23 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>monitored company acquisition in bioconjugates/biologics related services</t>
+          <t>Daiichi Sankyo partnership involving biologics (Datroway, Ivonescimab) for oncology</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -747,39 +747,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals launches gene-to-GMP platform for faster biologics development</t>
+          <t>Italfarmaco and JCR Pharma ink license deal for JR-141</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://manufacturingchemist.com/shilpa-biologicals-gene-gmp-platform-biologics-sb-himax</t>
+          <t>http://www.thepharmaletter.com/biotech-news/italfarmaco-and-jcr-pharma-ink-license-deal-for-jr-141</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-10-2026 10:02 UTC</t>
+          <t>03-10-2026 14:39 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>monitored company's biologic manufacturing/development platform news</t>
+          <t>JCR Pharma licensing deal for biologic (JR-141)</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -787,29 +787,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo, and Summit to Combine Datroway, Ivonescimab</t>
+          <t>Amino Acid Count Determines Retatrutide's Biologic or Drug Classification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>biopharminternational.com</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.biopharminternational.com/view/astrazeneca-daiichi-sankyo-summit-combine-datroway-ivonescimab</t>
+          <t>https://www.biopharminternational.com/view/amino-acid-count-retatrutide-biologic-drug-classification</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>monitored company biologic clinical collaboration</t>
+          <t>Biologic classification discussion for Retatrutide</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -834,32 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FDA upbraids Fresenius Kabi over injectable drugs contamination</t>
+          <t>Russians attacked the warehouses of the pharmaceutical distributor «Venta» near Kyiv: medicines from Bayer, Pfizer, Sanofi, Teva and Ukrainian manufacturers are burning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICLG</t>
+          <t>АНТИКОР</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://iclg.com/news/fda-upbraids-fresenius-kabi-over-injectable-drugs-contamination/</t>
+          <t>https://antikor.info/en/articles/866822-rossijane_atakovali_sklady_farmdistribjjutora_venta_pod_kievom_gorjat_lekarstva_bayer_pfizer_sanofi_teva_i_ukrainskih_proizvoditelej</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-10-2026 10:22 UTC</t>
+          <t>02-10-2026 20:01 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FDA/manufacturing warning for monitored company's injectable drugs</t>
+          <t>Supply chain disruption (warehouse fire) affecting monitored companies (Teva, Pfizer) and potentially biologics/biosimilars</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -879,27 +879,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teva, Samsung Bioepis deepen bonds in pact for up to 6 new biosimilars</t>
+          <t>Split Federal Circuit Won’t Reconsider Antibody Patent JMOL Reversal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Mealey's</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/teva-samsung-bioepis-deepen-bonds-pact-6-new-biosimilars</t>
+          <t>https://www.mealeys.com/mealeys/mealeys-intellectual-property/articles/2533325/split-federal-circuit-won-t-reconsider-antibody-patent-jmol-reversal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02-10-2026 14:00 UTC</t>
+          <t>02-10-2026 15:28 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>monitored companies biosimilar collaboration deal</t>
+          <t>Teva patent litigation involving antibodies (biologics)</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -919,27 +919,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsung Biologics Union Plans General Strike</t>
+          <t>A Flexible Manufacturing and Workforce Modernization Q&amp;A With Sebastián Arana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=278182</t>
+          <t>https://www.biopharminternational.com/view/flexible-manufacturing-workforce-modernization-sebastian-arana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>02-10-2026 10:45 UTC</t>
+          <t>03-10-2026 01:01 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>monitored company manufacturing/supply chain event</t>
+          <t>Samsung Biologics manufacturing strategy discussion (CDMO for biologics)</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -975,7 +975,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03-10-2026 14:27:33</t>
+          <t>03-10-2026 20:52:04</t>
         </is>
       </c>
     </row>
